--- a/output/Data and Chart Outputs/colombia_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/colombia_hydro_reservoirs.xlsx
@@ -157,6 +157,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <areaChart>
@@ -176,7 +177,7 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Water year chart'!$A$2:$A$366</f>
+              <f>'Water year chart'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -202,7 +203,7 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Water year chart'!$A$2:$A$366</f>
+              <f>'Water year chart'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -242,7 +243,7 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Water year chart'!$A$2:$A$366</f>
+              <f>'Water year chart'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -278,7 +279,7 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Water year chart'!$A$2:$A$366</f>
+              <f>'Water year chart'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -314,7 +315,7 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Water year chart'!$A$2:$A$366</f>
+              <f>'Water year chart'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -333,21 +334,21 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="30"/>
-        <tickMarkSkip val="30"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="91.22399999999999"/>
-          <min val="25.576"/>
+          <max val="100"/>
+          <min val="0"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -366,10 +367,12 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <majorUnit val="20"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -380,6 +383,7 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -819,7 +823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G366"/>
+  <dimension ref="A1:H366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -867,6 +871,11 @@
           <t>WY 2025/26</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Axis label</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -892,6 +901,11 @@
       <c r="G2" t="n">
         <v>81.15000000000001</v>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>01-Oct</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1667,6 +1681,11 @@
       <c r="G33" t="n">
         <v>83.55</v>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>01-Nov</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2417,6 +2436,11 @@
       <c r="G63" t="n">
         <v>85.45</v>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>01-Dec</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3192,6 +3216,11 @@
       <c r="G94" t="n">
         <v>80.23</v>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>01-Jan</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3967,6 +3996,11 @@
       <c r="G125" t="n">
         <v>76.84</v>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>01-Feb</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4667,6 +4701,11 @@
       <c r="G153" t="n">
         <v>72.69</v>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>01-Mar</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5442,6 +5481,11 @@
       <c r="G184" t="n">
         <v>63.27</v>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>01-Apr</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6192,6 +6236,11 @@
       <c r="G214" t="n">
         <v>63.88</v>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>01-May</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -6967,6 +7016,11 @@
       <c r="G245" t="n">
         <v>69.11</v>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>01-Jun</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -7717,6 +7771,11 @@
       <c r="G275" t="n">
         <v>76.45999999999999</v>
       </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>01-Jul</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -8492,6 +8551,11 @@
       <c r="G306" t="n">
         <v>79.72</v>
       </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>01-Aug</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -9266,6 +9330,11 @@
       </c>
       <c r="G337" t="n">
         <v>79.52</v>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>01-Sep</t>
+        </is>
       </c>
     </row>
     <row r="338">
@@ -17928,7 +17997,7 @@
         <v>40743</v>
       </c>
       <c r="B566" t="n">
-        <v>84.88849999999999</v>
+        <v>84.8886</v>
       </c>
       <c r="C566" t="n">
         <v>13397.8447</v>
@@ -45844,7 +45913,7 @@
         <v>42737</v>
       </c>
       <c r="B2560" t="n">
-        <v>73.7193</v>
+        <v>73.71939999999999</v>
       </c>
       <c r="C2560" t="n">
         <v>12563.829</v>
@@ -53278,7 +53347,7 @@
         <v>43268</v>
       </c>
       <c r="B3091" t="n">
-        <v>75.6195</v>
+        <v>75.61960000000001</v>
       </c>
       <c r="C3091" t="n">
         <v>13014.0339</v>

--- a/output/Data and Chart Outputs/colombia_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/colombia_hydro_reservoirs.xlsx
@@ -152,7 +152,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Colombia reservoirs (national) - water year (Oct-Sep), data to 2026-09-29</a:t>
+              <a:t>Colombia reservoirs (national) - water year (Oct-Sep), data to 2026-09-30</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -338,6 +338,18 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
@@ -801,7 +813,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Daily, from 2010-01-01 to 2026-09-29. Updated daily by .github/workflows/colombia_hydro_reservoirs.yml;</t>
+          <t>Daily, from 2010-01-01 to 2026-09-30. Updated daily by .github/workflows/colombia_hydro_reservoirs.yml;</t>
         </is>
       </c>
     </row>
@@ -10058,6 +10070,9 @@
       <c r="F366" t="n">
         <v>81.37</v>
       </c>
+      <c r="G366" t="n">
+        <v>8.369999999999999</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10071,7 +10086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6117"/>
+  <dimension ref="A1:D6118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95720,6 +95735,20 @@
         <v>17483.2455</v>
       </c>
     </row>
+    <row r="6118">
+      <c r="A6118" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B6118" t="n">
+        <v>8.368399999999999</v>
+      </c>
+      <c r="C6118" t="n">
+        <v>1463.0745</v>
+      </c>
+      <c r="D6118" t="n">
+        <v>17483.2455</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/colombia_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/colombia_hydro_reservoirs.xlsx
@@ -152,7 +152,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Colombia reservoirs (national) - water year (Oct-Sep), data to 2026-09-30</a:t>
+              <a:t>Colombia reservoirs (national) - water year (Oct-Sep), data to 2026-10-01</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -190,7 +190,7 @@
           <idx val="1"/>
           <order val="1"/>
           <tx>
-            <v>5-year range (2020/21-2024/25)</v>
+            <v>5-year range (2021/22-2025/26)</v>
           </tx>
           <spPr>
             <a:solidFill>
@@ -813,7 +813,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Daily, from 2010-01-01 to 2026-09-30. Updated daily by .github/workflows/colombia_hydro_reservoirs.yml;</t>
+          <t>Daily, from 2010-01-01 to 2026-10-01. Updated daily by .github/workflows/colombia_hydro_reservoirs.yml;</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>WY 2024/25</t>
+          <t>WY 2025/26</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>WY 2025/26</t>
+          <t>WY 2026/27</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -905,13 +905,13 @@
         <v>84.48</v>
       </c>
       <c r="E2" t="n">
-        <v>72.15000000000001</v>
+        <v>74.61</v>
       </c>
       <c r="F2" t="n">
-        <v>50.35</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>81.15000000000001</v>
+        <v>76.12</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -935,12 +935,9 @@
         <v>84.55</v>
       </c>
       <c r="E3" t="n">
-        <v>72.11</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>50.51</v>
-      </c>
-      <c r="G3" t="n">
         <v>81.13</v>
       </c>
     </row>
@@ -960,12 +957,9 @@
         <v>84.56</v>
       </c>
       <c r="E4" t="n">
-        <v>71.95</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>50.61</v>
-      </c>
-      <c r="G4" t="n">
         <v>81.17</v>
       </c>
     </row>
@@ -985,12 +979,9 @@
         <v>84.26000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>71.92</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>50.64</v>
-      </c>
-      <c r="G5" t="n">
         <v>80.97</v>
       </c>
     </row>
@@ -1010,12 +1001,9 @@
         <v>84.08</v>
       </c>
       <c r="E6" t="n">
-        <v>71.88</v>
+        <v>74.25</v>
       </c>
       <c r="F6" t="n">
-        <v>50.82</v>
-      </c>
-      <c r="G6" t="n">
         <v>81.03</v>
       </c>
     </row>
@@ -1035,12 +1023,9 @@
         <v>84.31</v>
       </c>
       <c r="E7" t="n">
-        <v>71.95999999999999</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>50.97</v>
-      </c>
-      <c r="G7" t="n">
         <v>81.04000000000001</v>
       </c>
     </row>
@@ -1060,12 +1045,9 @@
         <v>84.44</v>
       </c>
       <c r="E8" t="n">
-        <v>72.05</v>
+        <v>74.39</v>
       </c>
       <c r="F8" t="n">
-        <v>51.19</v>
-      </c>
-      <c r="G8" t="n">
         <v>80.95999999999999</v>
       </c>
     </row>
@@ -1085,12 +1067,9 @@
         <v>84.28</v>
       </c>
       <c r="E9" t="n">
-        <v>72.23999999999999</v>
+        <v>74.62</v>
       </c>
       <c r="F9" t="n">
-        <v>51.53</v>
-      </c>
-      <c r="G9" t="n">
         <v>81.14</v>
       </c>
     </row>
@@ -1110,12 +1089,9 @@
         <v>84.08</v>
       </c>
       <c r="E10" t="n">
-        <v>72.28</v>
+        <v>74.64</v>
       </c>
       <c r="F10" t="n">
-        <v>51.98</v>
-      </c>
-      <c r="G10" t="n">
         <v>81.02</v>
       </c>
     </row>
@@ -1135,12 +1111,9 @@
         <v>84.08</v>
       </c>
       <c r="E11" t="n">
-        <v>72.36</v>
+        <v>74.8</v>
       </c>
       <c r="F11" t="n">
-        <v>52.65</v>
-      </c>
-      <c r="G11" t="n">
         <v>81.26000000000001</v>
       </c>
     </row>
@@ -1160,12 +1133,9 @@
         <v>84.16</v>
       </c>
       <c r="E12" t="n">
-        <v>72.29000000000001</v>
+        <v>74.81</v>
       </c>
       <c r="F12" t="n">
-        <v>52.79</v>
-      </c>
-      <c r="G12" t="n">
         <v>81.45999999999999</v>
       </c>
     </row>
@@ -1185,12 +1155,9 @@
         <v>83.88</v>
       </c>
       <c r="E13" t="n">
-        <v>72.08</v>
+        <v>74.78</v>
       </c>
       <c r="F13" t="n">
-        <v>52.77</v>
-      </c>
-      <c r="G13" t="n">
         <v>82.28</v>
       </c>
     </row>
@@ -1210,12 +1177,9 @@
         <v>83.73</v>
       </c>
       <c r="E14" t="n">
-        <v>72</v>
+        <v>74.72</v>
       </c>
       <c r="F14" t="n">
-        <v>53.11</v>
-      </c>
-      <c r="G14" t="n">
         <v>82.45999999999999</v>
       </c>
     </row>
@@ -1235,12 +1199,9 @@
         <v>83.66</v>
       </c>
       <c r="E15" t="n">
-        <v>71.95</v>
+        <v>74.64</v>
       </c>
       <c r="F15" t="n">
-        <v>53.17</v>
-      </c>
-      <c r="G15" t="n">
         <v>82.37</v>
       </c>
     </row>
@@ -1260,12 +1221,9 @@
         <v>83.55</v>
       </c>
       <c r="E16" t="n">
-        <v>71.84999999999999</v>
+        <v>74.55</v>
       </c>
       <c r="F16" t="n">
-        <v>53.14</v>
-      </c>
-      <c r="G16" t="n">
         <v>82.23999999999999</v>
       </c>
     </row>
@@ -1285,12 +1243,9 @@
         <v>83.89</v>
       </c>
       <c r="E17" t="n">
-        <v>71.91</v>
+        <v>74.67</v>
       </c>
       <c r="F17" t="n">
-        <v>53.16</v>
-      </c>
-      <c r="G17" t="n">
         <v>82.34999999999999</v>
       </c>
     </row>
@@ -1310,12 +1265,9 @@
         <v>84.20999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>71.95</v>
+        <v>74.81</v>
       </c>
       <c r="F18" t="n">
-        <v>53.21</v>
-      </c>
-      <c r="G18" t="n">
         <v>82.58</v>
       </c>
     </row>
@@ -1335,12 +1287,9 @@
         <v>84.06</v>
       </c>
       <c r="E19" t="n">
-        <v>71.92</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>53.16</v>
-      </c>
-      <c r="G19" t="n">
         <v>82.91</v>
       </c>
     </row>
@@ -1360,12 +1309,9 @@
         <v>83.95</v>
       </c>
       <c r="E20" t="n">
-        <v>71.94</v>
+        <v>74.95</v>
       </c>
       <c r="F20" t="n">
-        <v>53.38</v>
-      </c>
-      <c r="G20" t="n">
         <v>83.25</v>
       </c>
     </row>
@@ -1385,12 +1331,9 @@
         <v>83.86</v>
       </c>
       <c r="E21" t="n">
-        <v>72</v>
+        <v>75.08</v>
       </c>
       <c r="F21" t="n">
-        <v>53.64</v>
-      </c>
-      <c r="G21" t="n">
         <v>83.36</v>
       </c>
     </row>
@@ -1410,12 +1353,9 @@
         <v>83.79000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>71.95</v>
+        <v>75.09</v>
       </c>
       <c r="F22" t="n">
-        <v>53.72</v>
-      </c>
-      <c r="G22" t="n">
         <v>83.44</v>
       </c>
     </row>
@@ -1435,12 +1375,9 @@
         <v>83.81999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>72.09</v>
+        <v>75.22</v>
       </c>
       <c r="F23" t="n">
-        <v>54.02</v>
-      </c>
-      <c r="G23" t="n">
         <v>83.48</v>
       </c>
     </row>
@@ -1460,12 +1397,9 @@
         <v>84.15000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>72.20999999999999</v>
+        <v>75.34</v>
       </c>
       <c r="F24" t="n">
-        <v>54.29</v>
-      </c>
-      <c r="G24" t="n">
         <v>83.43000000000001</v>
       </c>
     </row>
@@ -1485,12 +1419,9 @@
         <v>84.40000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>72.43000000000001</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>54.64</v>
-      </c>
-      <c r="G25" t="n">
         <v>83.51000000000001</v>
       </c>
     </row>
@@ -1510,12 +1441,9 @@
         <v>84.55</v>
       </c>
       <c r="E26" t="n">
-        <v>72.45</v>
+        <v>75.55</v>
       </c>
       <c r="F26" t="n">
-        <v>54.79</v>
-      </c>
-      <c r="G26" t="n">
         <v>83.59999999999999</v>
       </c>
     </row>
@@ -1535,12 +1463,9 @@
         <v>84.70999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>72.61</v>
+        <v>75.78</v>
       </c>
       <c r="F27" t="n">
-        <v>54.86</v>
-      </c>
-      <c r="G27" t="n">
         <v>83.8</v>
       </c>
     </row>
@@ -1560,12 +1485,9 @@
         <v>85.02</v>
       </c>
       <c r="E28" t="n">
-        <v>72.81</v>
+        <v>76.09</v>
       </c>
       <c r="F28" t="n">
-        <v>55.09</v>
-      </c>
-      <c r="G28" t="n">
         <v>84.12</v>
       </c>
     </row>
@@ -1585,12 +1507,9 @@
         <v>85.73999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>72.98999999999999</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="G29" t="n">
         <v>83.94</v>
       </c>
     </row>
@@ -1610,12 +1529,9 @@
         <v>86.18000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>73.14</v>
+        <v>76.42</v>
       </c>
       <c r="F30" t="n">
-        <v>55.19</v>
-      </c>
-      <c r="G30" t="n">
         <v>83.87</v>
       </c>
     </row>
@@ -1635,12 +1551,9 @@
         <v>86.04000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>73.12</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>55.24</v>
-      </c>
-      <c r="G31" t="n">
         <v>83.73999999999999</v>
       </c>
     </row>
@@ -1660,12 +1573,9 @@
         <v>85.67</v>
       </c>
       <c r="E32" t="n">
-        <v>73.29000000000001</v>
+        <v>76.47</v>
       </c>
       <c r="F32" t="n">
-        <v>55.29</v>
-      </c>
-      <c r="G32" t="n">
         <v>83.75</v>
       </c>
     </row>
@@ -1685,12 +1595,9 @@
         <v>85.26000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>73.44</v>
+        <v>76.37</v>
       </c>
       <c r="F33" t="n">
-        <v>55.34</v>
-      </c>
-      <c r="G33" t="n">
         <v>83.55</v>
       </c>
       <c r="H33" t="inlineStr">
@@ -1715,12 +1622,9 @@
         <v>85.31</v>
       </c>
       <c r="E34" t="n">
-        <v>73.76000000000001</v>
+        <v>76.64</v>
       </c>
       <c r="F34" t="n">
-        <v>56.09</v>
-      </c>
-      <c r="G34" t="n">
         <v>83.48</v>
       </c>
     </row>
@@ -1740,12 +1644,9 @@
         <v>85.40000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>73.98</v>
+        <v>76.86</v>
       </c>
       <c r="F35" t="n">
-        <v>56.28</v>
-      </c>
-      <c r="G35" t="n">
         <v>83.55</v>
       </c>
     </row>
@@ -1765,12 +1666,9 @@
         <v>85.44</v>
       </c>
       <c r="E36" t="n">
-        <v>74.25</v>
+        <v>77.12</v>
       </c>
       <c r="F36" t="n">
-        <v>56.77</v>
-      </c>
-      <c r="G36" t="n">
         <v>83.40000000000001</v>
       </c>
     </row>
@@ -1790,12 +1688,9 @@
         <v>85.41</v>
       </c>
       <c r="E37" t="n">
-        <v>74.31999999999999</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>57.01</v>
-      </c>
-      <c r="G37" t="n">
         <v>83.31</v>
       </c>
     </row>
@@ -1815,12 +1710,9 @@
         <v>85.63</v>
       </c>
       <c r="E38" t="n">
-        <v>74.42</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>57.23</v>
-      </c>
-      <c r="G38" t="n">
         <v>83.44</v>
       </c>
     </row>
@@ -1840,12 +1732,9 @@
         <v>85.76000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>74.54000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="F39" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="G39" t="n">
         <v>83.20999999999999</v>
       </c>
     </row>
@@ -1865,12 +1754,9 @@
         <v>86.17</v>
       </c>
       <c r="E40" t="n">
-        <v>74.70999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>58.17</v>
-      </c>
-      <c r="G40" t="n">
         <v>83.03</v>
       </c>
     </row>
@@ -1890,12 +1776,9 @@
         <v>86.64</v>
       </c>
       <c r="E41" t="n">
-        <v>74.93000000000001</v>
+        <v>77.63</v>
       </c>
       <c r="F41" t="n">
-        <v>58.94</v>
-      </c>
-      <c r="G41" t="n">
         <v>83.09</v>
       </c>
     </row>
@@ -1915,12 +1798,9 @@
         <v>87.13</v>
       </c>
       <c r="E42" t="n">
-        <v>75.40000000000001</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>60.39</v>
-      </c>
-      <c r="G42" t="n">
         <v>83.20999999999999</v>
       </c>
     </row>
@@ -1940,12 +1820,9 @@
         <v>87.13</v>
       </c>
       <c r="E43" t="n">
-        <v>75.8</v>
+        <v>78.23</v>
       </c>
       <c r="F43" t="n">
-        <v>61.41</v>
-      </c>
-      <c r="G43" t="n">
         <v>83.09999999999999</v>
       </c>
     </row>
@@ -1965,12 +1842,9 @@
         <v>87.36</v>
       </c>
       <c r="E44" t="n">
-        <v>76.09</v>
+        <v>78.37</v>
       </c>
       <c r="F44" t="n">
-        <v>62.01</v>
-      </c>
-      <c r="G44" t="n">
         <v>82.83</v>
       </c>
     </row>
@@ -1990,12 +1864,9 @@
         <v>87.70999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>76.55</v>
+        <v>78.59</v>
       </c>
       <c r="F45" t="n">
-        <v>62.71</v>
-      </c>
-      <c r="G45" t="n">
         <v>82.84999999999999</v>
       </c>
     </row>
@@ -2015,12 +1886,9 @@
         <v>87.8</v>
       </c>
       <c r="E46" t="n">
-        <v>76.90000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F46" t="n">
-        <v>63.53</v>
-      </c>
-      <c r="G46" t="n">
         <v>83.39</v>
       </c>
     </row>
@@ -2040,12 +1908,9 @@
         <v>87.64</v>
       </c>
       <c r="E47" t="n">
-        <v>77.16</v>
+        <v>79.11</v>
       </c>
       <c r="F47" t="n">
-        <v>64.09</v>
-      </c>
-      <c r="G47" t="n">
         <v>83.72</v>
       </c>
     </row>
@@ -2065,12 +1930,9 @@
         <v>87.37</v>
       </c>
       <c r="E48" t="n">
-        <v>77.22</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>64.37</v>
-      </c>
-      <c r="G48" t="n">
         <v>84.72</v>
       </c>
     </row>
@@ -2090,12 +1952,9 @@
         <v>87</v>
       </c>
       <c r="E49" t="n">
-        <v>77.23</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>64.66</v>
-      </c>
-      <c r="G49" t="n">
         <v>85.68000000000001</v>
       </c>
     </row>
@@ -2115,12 +1974,9 @@
         <v>86.92</v>
       </c>
       <c r="E50" t="n">
-        <v>77.38</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>64.81</v>
-      </c>
-      <c r="G50" t="n">
         <v>85.79000000000001</v>
       </c>
     </row>
@@ -2140,12 +1996,9 @@
         <v>86.67</v>
       </c>
       <c r="E51" t="n">
-        <v>77.48</v>
+        <v>79.48</v>
       </c>
       <c r="F51" t="n">
-        <v>65.11</v>
-      </c>
-      <c r="G51" t="n">
         <v>85.95999999999999</v>
       </c>
     </row>
@@ -2165,12 +2018,9 @@
         <v>86.55</v>
       </c>
       <c r="E52" t="n">
-        <v>77.52</v>
+        <v>79.52</v>
       </c>
       <c r="F52" t="n">
-        <v>65.20999999999999</v>
-      </c>
-      <c r="G52" t="n">
         <v>85.95</v>
       </c>
     </row>
@@ -2190,12 +2040,9 @@
         <v>86.3</v>
       </c>
       <c r="E53" t="n">
-        <v>77.62</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="F53" t="n">
-        <v>65.79000000000001</v>
-      </c>
-      <c r="G53" t="n">
         <v>85.90000000000001</v>
       </c>
     </row>
@@ -2215,12 +2062,9 @@
         <v>86.29000000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>77.67</v>
+        <v>79.58</v>
       </c>
       <c r="F54" t="n">
-        <v>66.26000000000001</v>
-      </c>
-      <c r="G54" t="n">
         <v>85.78</v>
       </c>
     </row>
@@ -2240,12 +2084,9 @@
         <v>86.27</v>
       </c>
       <c r="E55" t="n">
-        <v>77.7</v>
+        <v>79.63</v>
       </c>
       <c r="F55" t="n">
-        <v>66.66</v>
-      </c>
-      <c r="G55" t="n">
         <v>85.83</v>
       </c>
     </row>
@@ -2265,12 +2106,9 @@
         <v>86.27</v>
       </c>
       <c r="E56" t="n">
-        <v>77.77</v>
+        <v>79.7</v>
       </c>
       <c r="F56" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="G56" t="n">
         <v>85.73999999999999</v>
       </c>
     </row>
@@ -2290,12 +2128,9 @@
         <v>86.12</v>
       </c>
       <c r="E57" t="n">
-        <v>77.78</v>
+        <v>79.69</v>
       </c>
       <c r="F57" t="n">
-        <v>66.78</v>
-      </c>
-      <c r="G57" t="n">
         <v>85.53</v>
       </c>
     </row>
@@ -2315,12 +2150,9 @@
         <v>86.16</v>
       </c>
       <c r="E58" t="n">
-        <v>77.83</v>
+        <v>79.7</v>
       </c>
       <c r="F58" t="n">
-        <v>66.77</v>
-      </c>
-      <c r="G58" t="n">
         <v>85.23999999999999</v>
       </c>
     </row>
@@ -2340,12 +2172,9 @@
         <v>86.31</v>
       </c>
       <c r="E59" t="n">
-        <v>77.81999999999999</v>
+        <v>79.72</v>
       </c>
       <c r="F59" t="n">
-        <v>66.95</v>
-      </c>
-      <c r="G59" t="n">
         <v>84.98</v>
       </c>
     </row>
@@ -2365,12 +2194,9 @@
         <v>86.59999999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>78.01000000000001</v>
+        <v>79.73</v>
       </c>
       <c r="F60" t="n">
-        <v>67.15000000000001</v>
-      </c>
-      <c r="G60" t="n">
         <v>84.90000000000001</v>
       </c>
     </row>
@@ -2390,12 +2216,9 @@
         <v>86.98999999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>78.09999999999999</v>
+        <v>79.78</v>
       </c>
       <c r="F61" t="n">
-        <v>67.15000000000001</v>
-      </c>
-      <c r="G61" t="n">
         <v>85.06</v>
       </c>
     </row>
@@ -2415,12 +2238,9 @@
         <v>87.14</v>
       </c>
       <c r="E62" t="n">
-        <v>78.03</v>
+        <v>79.8</v>
       </c>
       <c r="F62" t="n">
-        <v>67.02</v>
-      </c>
-      <c r="G62" t="n">
         <v>85.40000000000001</v>
       </c>
     </row>
@@ -2440,12 +2260,9 @@
         <v>85.93000000000001</v>
       </c>
       <c r="E63" t="n">
-        <v>77.70999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="F63" t="n">
-        <v>66.93000000000001</v>
-      </c>
-      <c r="G63" t="n">
         <v>85.45</v>
       </c>
       <c r="H63" t="inlineStr">
@@ -2470,12 +2287,9 @@
         <v>85.64</v>
       </c>
       <c r="E64" t="n">
-        <v>77.56</v>
+        <v>79.38</v>
       </c>
       <c r="F64" t="n">
-        <v>66.87</v>
-      </c>
-      <c r="G64" t="n">
         <v>85.61</v>
       </c>
     </row>
@@ -2495,12 +2309,9 @@
         <v>85.5</v>
       </c>
       <c r="E65" t="n">
-        <v>77.53</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="F65" t="n">
-        <v>66.73</v>
-      </c>
-      <c r="G65" t="n">
         <v>85.48</v>
       </c>
     </row>
@@ -2520,12 +2331,9 @@
         <v>85.48999999999999</v>
       </c>
       <c r="E66" t="n">
-        <v>77.38</v>
+        <v>79.11</v>
       </c>
       <c r="F66" t="n">
-        <v>66.55</v>
-      </c>
-      <c r="G66" t="n">
         <v>85.48999999999999</v>
       </c>
     </row>
@@ -2539,18 +2347,15 @@
         <v>66.44</v>
       </c>
       <c r="C67" t="n">
-        <v>18.92</v>
+        <v>19.1</v>
       </c>
       <c r="D67" t="n">
-        <v>85.37</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="E67" t="n">
-        <v>77.22</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="F67" t="n">
-        <v>66.44</v>
-      </c>
-      <c r="G67" t="n">
         <v>85.54000000000001</v>
       </c>
     </row>
@@ -2564,18 +2369,15 @@
         <v>66.3</v>
       </c>
       <c r="C68" t="n">
-        <v>18.93</v>
+        <v>19.15</v>
       </c>
       <c r="D68" t="n">
-        <v>85.23</v>
+        <v>85.45999999999999</v>
       </c>
       <c r="E68" t="n">
-        <v>77.06</v>
+        <v>78.8</v>
       </c>
       <c r="F68" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="G68" t="n">
         <v>85.45999999999999</v>
       </c>
     </row>
@@ -2589,18 +2391,15 @@
         <v>66.19</v>
       </c>
       <c r="C69" t="n">
-        <v>18.95</v>
+        <v>19.33</v>
       </c>
       <c r="D69" t="n">
-        <v>85.14</v>
+        <v>85.52</v>
       </c>
       <c r="E69" t="n">
-        <v>76.88</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="F69" t="n">
-        <v>66.19</v>
-      </c>
-      <c r="G69" t="n">
         <v>85.52</v>
       </c>
     </row>
@@ -2614,18 +2413,15 @@
         <v>66.14</v>
       </c>
       <c r="C70" t="n">
-        <v>19.07</v>
+        <v>19.47</v>
       </c>
       <c r="D70" t="n">
-        <v>85.20999999999999</v>
+        <v>85.61</v>
       </c>
       <c r="E70" t="n">
-        <v>76.78</v>
+        <v>78.59</v>
       </c>
       <c r="F70" t="n">
-        <v>66.14</v>
-      </c>
-      <c r="G70" t="n">
         <v>85.61</v>
       </c>
     </row>
@@ -2639,18 +2435,15 @@
         <v>66</v>
       </c>
       <c r="C71" t="n">
-        <v>19</v>
+        <v>19.4</v>
       </c>
       <c r="D71" t="n">
-        <v>85</v>
+        <v>85.41</v>
       </c>
       <c r="E71" t="n">
-        <v>76.5</v>
+        <v>78.36</v>
       </c>
       <c r="F71" t="n">
-        <v>66</v>
-      </c>
-      <c r="G71" t="n">
         <v>85.41</v>
       </c>
     </row>
@@ -2664,18 +2457,15 @@
         <v>65.8</v>
       </c>
       <c r="C72" t="n">
-        <v>18.96</v>
+        <v>19.31</v>
       </c>
       <c r="D72" t="n">
-        <v>84.77</v>
+        <v>85.11</v>
       </c>
       <c r="E72" t="n">
-        <v>76.3</v>
+        <v>78.14</v>
       </c>
       <c r="F72" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="G72" t="n">
         <v>85.11</v>
       </c>
     </row>
@@ -2689,18 +2479,15 @@
         <v>65.65000000000001</v>
       </c>
       <c r="C73" t="n">
-        <v>19.04</v>
+        <v>19.08</v>
       </c>
       <c r="D73" t="n">
-        <v>84.69</v>
+        <v>84.73</v>
       </c>
       <c r="E73" t="n">
-        <v>76.13</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="F73" t="n">
-        <v>65.65000000000001</v>
-      </c>
-      <c r="G73" t="n">
         <v>84.73</v>
       </c>
     </row>
@@ -2720,12 +2507,9 @@
         <v>84.59</v>
       </c>
       <c r="E74" t="n">
-        <v>75.90000000000001</v>
+        <v>77.78</v>
       </c>
       <c r="F74" t="n">
-        <v>65.53</v>
-      </c>
-      <c r="G74" t="n">
         <v>84.52</v>
       </c>
     </row>
@@ -2745,12 +2529,9 @@
         <v>84.33</v>
       </c>
       <c r="E75" t="n">
-        <v>75.68000000000001</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="F75" t="n">
-        <v>65.48</v>
-      </c>
-      <c r="G75" t="n">
         <v>84.15000000000001</v>
       </c>
     </row>
@@ -2770,12 +2551,9 @@
         <v>84.03</v>
       </c>
       <c r="E76" t="n">
-        <v>75.41</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="F76" t="n">
-        <v>65.45999999999999</v>
-      </c>
-      <c r="G76" t="n">
         <v>83.89</v>
       </c>
     </row>
@@ -2795,12 +2573,9 @@
         <v>83.73999999999999</v>
       </c>
       <c r="E77" t="n">
-        <v>75.23999999999999</v>
+        <v>77.11</v>
       </c>
       <c r="F77" t="n">
-        <v>65.70999999999999</v>
-      </c>
-      <c r="G77" t="n">
         <v>83.54000000000001</v>
       </c>
     </row>
@@ -2820,12 +2595,9 @@
         <v>83.41</v>
       </c>
       <c r="E78" t="n">
-        <v>75.09</v>
+        <v>76.98</v>
       </c>
       <c r="F78" t="n">
-        <v>65.83</v>
-      </c>
-      <c r="G78" t="n">
         <v>83.40000000000001</v>
       </c>
     </row>
@@ -2839,18 +2611,15 @@
         <v>65.86</v>
       </c>
       <c r="C79" t="n">
-        <v>17.29</v>
+        <v>17.41</v>
       </c>
       <c r="D79" t="n">
-        <v>83.15000000000001</v>
+        <v>83.27</v>
       </c>
       <c r="E79" t="n">
-        <v>74.98999999999999</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="F79" t="n">
-        <v>65.86</v>
-      </c>
-      <c r="G79" t="n">
         <v>83.27</v>
       </c>
     </row>
@@ -2864,18 +2633,15 @@
         <v>65.76000000000001</v>
       </c>
       <c r="C80" t="n">
-        <v>17.22</v>
+        <v>17.3</v>
       </c>
       <c r="D80" t="n">
-        <v>82.98</v>
+        <v>83.05</v>
       </c>
       <c r="E80" t="n">
-        <v>74.84</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="F80" t="n">
-        <v>65.76000000000001</v>
-      </c>
-      <c r="G80" t="n">
         <v>83.05</v>
       </c>
     </row>
@@ -2889,18 +2655,15 @@
         <v>65.67</v>
       </c>
       <c r="C81" t="n">
-        <v>17</v>
+        <v>17.18</v>
       </c>
       <c r="D81" t="n">
-        <v>82.67</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="E81" t="n">
-        <v>74.67</v>
+        <v>76.62</v>
       </c>
       <c r="F81" t="n">
-        <v>65.67</v>
-      </c>
-      <c r="G81" t="n">
         <v>82.84999999999999</v>
       </c>
     </row>
@@ -2914,18 +2677,15 @@
         <v>65.61</v>
       </c>
       <c r="C82" t="n">
-        <v>16.66</v>
+        <v>17.18</v>
       </c>
       <c r="D82" t="n">
-        <v>82.27</v>
+        <v>82.79000000000001</v>
       </c>
       <c r="E82" t="n">
-        <v>74.48</v>
+        <v>76.42</v>
       </c>
       <c r="F82" t="n">
-        <v>65.61</v>
-      </c>
-      <c r="G82" t="n">
         <v>82.79000000000001</v>
       </c>
     </row>
@@ -2939,18 +2699,15 @@
         <v>65.86</v>
       </c>
       <c r="C83" t="n">
-        <v>16.07</v>
+        <v>16.81</v>
       </c>
       <c r="D83" t="n">
-        <v>81.93000000000001</v>
+        <v>82.67</v>
       </c>
       <c r="E83" t="n">
-        <v>74.29000000000001</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="F83" t="n">
-        <v>65.86</v>
-      </c>
-      <c r="G83" t="n">
         <v>82.67</v>
       </c>
     </row>
@@ -2964,18 +2721,15 @@
         <v>66.25</v>
       </c>
       <c r="C84" t="n">
-        <v>15.24</v>
+        <v>16.27</v>
       </c>
       <c r="D84" t="n">
-        <v>81.48999999999999</v>
+        <v>82.52</v>
       </c>
       <c r="E84" t="n">
-        <v>74.19</v>
+        <v>76.19</v>
       </c>
       <c r="F84" t="n">
-        <v>66.25</v>
-      </c>
-      <c r="G84" t="n">
         <v>82.52</v>
       </c>
     </row>
@@ -2989,18 +2743,15 @@
         <v>66.72</v>
       </c>
       <c r="C85" t="n">
-        <v>14.31</v>
+        <v>15.52</v>
       </c>
       <c r="D85" t="n">
-        <v>81.03</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="E85" t="n">
-        <v>74.06999999999999</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="F85" t="n">
-        <v>66.72</v>
-      </c>
-      <c r="G85" t="n">
         <v>82.23999999999999</v>
       </c>
     </row>
@@ -3014,18 +2765,15 @@
         <v>66.86</v>
       </c>
       <c r="C86" t="n">
-        <v>13.88</v>
+        <v>15.16</v>
       </c>
       <c r="D86" t="n">
-        <v>80.73999999999999</v>
+        <v>82.02</v>
       </c>
       <c r="E86" t="n">
-        <v>73.98</v>
+        <v>75.95</v>
       </c>
       <c r="F86" t="n">
-        <v>66.86</v>
-      </c>
-      <c r="G86" t="n">
         <v>82.02</v>
       </c>
     </row>
@@ -3039,18 +2787,15 @@
         <v>66.93000000000001</v>
       </c>
       <c r="C87" t="n">
-        <v>13.71</v>
+        <v>15.07</v>
       </c>
       <c r="D87" t="n">
-        <v>80.64</v>
+        <v>82</v>
       </c>
       <c r="E87" t="n">
-        <v>74.01000000000001</v>
+        <v>75.92</v>
       </c>
       <c r="F87" t="n">
-        <v>66.93000000000001</v>
-      </c>
-      <c r="G87" t="n">
         <v>82</v>
       </c>
     </row>
@@ -3064,18 +2809,15 @@
         <v>67.03</v>
       </c>
       <c r="C88" t="n">
-        <v>13.35</v>
+        <v>14.7</v>
       </c>
       <c r="D88" t="n">
-        <v>80.38</v>
+        <v>81.73</v>
       </c>
       <c r="E88" t="n">
-        <v>73.98999999999999</v>
+        <v>75.83</v>
       </c>
       <c r="F88" t="n">
-        <v>67.03</v>
-      </c>
-      <c r="G88" t="n">
         <v>81.73</v>
       </c>
     </row>
@@ -3089,18 +2831,15 @@
         <v>67.2</v>
       </c>
       <c r="C89" t="n">
-        <v>12.95</v>
+        <v>14.3</v>
       </c>
       <c r="D89" t="n">
-        <v>80.16</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="E89" t="n">
-        <v>73.94</v>
+        <v>75.75</v>
       </c>
       <c r="F89" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="G89" t="n">
         <v>81.51000000000001</v>
       </c>
     </row>
@@ -3114,18 +2853,15 @@
         <v>67.31</v>
       </c>
       <c r="C90" t="n">
-        <v>12.55</v>
+        <v>14.01</v>
       </c>
       <c r="D90" t="n">
-        <v>79.86</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="E90" t="n">
-        <v>73.88</v>
+        <v>75.67</v>
       </c>
       <c r="F90" t="n">
-        <v>67.31</v>
-      </c>
-      <c r="G90" t="n">
         <v>81.31999999999999</v>
       </c>
     </row>
@@ -3139,18 +2875,15 @@
         <v>67.59</v>
       </c>
       <c r="C91" t="n">
-        <v>11.88</v>
+        <v>13.32</v>
       </c>
       <c r="D91" t="n">
-        <v>79.45999999999999</v>
+        <v>80.91</v>
       </c>
       <c r="E91" t="n">
-        <v>73.81999999999999</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="F91" t="n">
-        <v>67.59</v>
-      </c>
-      <c r="G91" t="n">
         <v>80.91</v>
       </c>
     </row>
@@ -3164,18 +2897,15 @@
         <v>67.83</v>
       </c>
       <c r="C92" t="n">
-        <v>11.39</v>
+        <v>12.71</v>
       </c>
       <c r="D92" t="n">
-        <v>79.22</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="E92" t="n">
-        <v>73.72</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="F92" t="n">
-        <v>67.83</v>
-      </c>
-      <c r="G92" t="n">
         <v>80.54000000000001</v>
       </c>
     </row>
@@ -3189,18 +2919,15 @@
         <v>68.02</v>
       </c>
       <c r="C93" t="n">
-        <v>11.03</v>
+        <v>12.27</v>
       </c>
       <c r="D93" t="n">
-        <v>79.05</v>
+        <v>80.29000000000001</v>
       </c>
       <c r="E93" t="n">
-        <v>73.64</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="F93" t="n">
-        <v>68.02</v>
-      </c>
-      <c r="G93" t="n">
         <v>80.29000000000001</v>
       </c>
     </row>
@@ -3214,18 +2941,15 @@
         <v>68.22</v>
       </c>
       <c r="C94" t="n">
-        <v>10.84</v>
+        <v>12</v>
       </c>
       <c r="D94" t="n">
-        <v>79.06999999999999</v>
+        <v>80.23</v>
       </c>
       <c r="E94" t="n">
-        <v>73.65000000000001</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="F94" t="n">
-        <v>68.22</v>
-      </c>
-      <c r="G94" t="n">
         <v>80.23</v>
       </c>
       <c r="H94" t="inlineStr">
@@ -3244,18 +2968,15 @@
         <v>68.34</v>
       </c>
       <c r="C95" t="n">
-        <v>10.67</v>
+        <v>11.71</v>
       </c>
       <c r="D95" t="n">
-        <v>79.01000000000001</v>
+        <v>80.05</v>
       </c>
       <c r="E95" t="n">
-        <v>73.55</v>
+        <v>75.19</v>
       </c>
       <c r="F95" t="n">
-        <v>68.34</v>
-      </c>
-      <c r="G95" t="n">
         <v>80.05</v>
       </c>
     </row>
@@ -3269,18 +2990,15 @@
         <v>68.58</v>
       </c>
       <c r="C96" t="n">
-        <v>10.2</v>
+        <v>11.38</v>
       </c>
       <c r="D96" t="n">
-        <v>78.79000000000001</v>
+        <v>79.95999999999999</v>
       </c>
       <c r="E96" t="n">
-        <v>73.45</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="F96" t="n">
-        <v>68.58</v>
-      </c>
-      <c r="G96" t="n">
         <v>79.95999999999999</v>
       </c>
     </row>
@@ -3294,18 +3012,15 @@
         <v>68.93000000000001</v>
       </c>
       <c r="C97" t="n">
-        <v>9.51</v>
+        <v>10.99</v>
       </c>
       <c r="D97" t="n">
-        <v>78.44</v>
+        <v>79.92</v>
       </c>
       <c r="E97" t="n">
-        <v>73.26000000000001</v>
+        <v>74.92</v>
       </c>
       <c r="F97" t="n">
-        <v>68.94</v>
-      </c>
-      <c r="G97" t="n">
         <v>79.92</v>
       </c>
     </row>
@@ -3319,18 +3034,15 @@
         <v>68.47</v>
       </c>
       <c r="C98" t="n">
-        <v>9.6</v>
+        <v>11.34</v>
       </c>
       <c r="D98" t="n">
-        <v>78.06999999999999</v>
+        <v>79.81</v>
       </c>
       <c r="E98" t="n">
-        <v>73.03</v>
+        <v>74.72</v>
       </c>
       <c r="F98" t="n">
-        <v>69.37</v>
-      </c>
-      <c r="G98" t="n">
         <v>79.81</v>
       </c>
     </row>
@@ -3344,18 +3056,15 @@
         <v>68.13</v>
       </c>
       <c r="C99" t="n">
-        <v>9.75</v>
+        <v>11.81</v>
       </c>
       <c r="D99" t="n">
-        <v>77.88</v>
+        <v>79.94</v>
       </c>
       <c r="E99" t="n">
-        <v>72.84</v>
+        <v>74.62</v>
       </c>
       <c r="F99" t="n">
-        <v>69.53</v>
-      </c>
-      <c r="G99" t="n">
         <v>79.94</v>
       </c>
     </row>
@@ -3369,18 +3078,15 @@
         <v>67.81</v>
       </c>
       <c r="C100" t="n">
-        <v>10.16</v>
+        <v>12.35</v>
       </c>
       <c r="D100" t="n">
-        <v>77.95999999999999</v>
+        <v>80.15000000000001</v>
       </c>
       <c r="E100" t="n">
-        <v>72.68000000000001</v>
+        <v>74.56</v>
       </c>
       <c r="F100" t="n">
-        <v>69.47</v>
-      </c>
-      <c r="G100" t="n">
         <v>80.15000000000001</v>
       </c>
     </row>
@@ -3394,18 +3100,15 @@
         <v>67.45</v>
       </c>
       <c r="C101" t="n">
-        <v>10.66</v>
+        <v>12.46</v>
       </c>
       <c r="D101" t="n">
-        <v>78.11</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="E101" t="n">
-        <v>72.5</v>
+        <v>74.34</v>
       </c>
       <c r="F101" t="n">
-        <v>69.28</v>
-      </c>
-      <c r="G101" t="n">
         <v>79.90000000000001</v>
       </c>
     </row>
@@ -3419,18 +3122,15 @@
         <v>66.98999999999999</v>
       </c>
       <c r="C102" t="n">
-        <v>11.1</v>
+        <v>12.65</v>
       </c>
       <c r="D102" t="n">
-        <v>78.09</v>
+        <v>79.64</v>
       </c>
       <c r="E102" t="n">
-        <v>72.26000000000001</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="F102" t="n">
-        <v>69</v>
-      </c>
-      <c r="G102" t="n">
         <v>79.64</v>
       </c>
     </row>
@@ -3444,18 +3144,15 @@
         <v>66.58</v>
       </c>
       <c r="C103" t="n">
-        <v>11.64</v>
+        <v>13</v>
       </c>
       <c r="D103" t="n">
-        <v>78.22</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="E103" t="n">
-        <v>72.08</v>
+        <v>73.86</v>
       </c>
       <c r="F103" t="n">
-        <v>68.66</v>
-      </c>
-      <c r="G103" t="n">
         <v>79.56999999999999</v>
       </c>
     </row>
@@ -3469,18 +3166,15 @@
         <v>66.06999999999999</v>
       </c>
       <c r="C104" t="n">
-        <v>12.36</v>
+        <v>13.66</v>
       </c>
       <c r="D104" t="n">
-        <v>78.44</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="E104" t="n">
-        <v>71.95</v>
+        <v>73.69</v>
       </c>
       <c r="F104" t="n">
-        <v>68.39</v>
-      </c>
-      <c r="G104" t="n">
         <v>79.73999999999999</v>
       </c>
     </row>
@@ -3494,18 +3188,15 @@
         <v>65.66</v>
       </c>
       <c r="C105" t="n">
-        <v>12.96</v>
+        <v>14.44</v>
       </c>
       <c r="D105" t="n">
-        <v>78.62</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="E105" t="n">
-        <v>71.76000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F105" t="n">
-        <v>68.18000000000001</v>
-      </c>
-      <c r="G105" t="n">
         <v>80.09999999999999</v>
       </c>
     </row>
@@ -3519,18 +3210,15 @@
         <v>65.37</v>
       </c>
       <c r="C106" t="n">
-        <v>13.21</v>
+        <v>14.84</v>
       </c>
       <c r="D106" t="n">
-        <v>78.58</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="E106" t="n">
-        <v>71.48</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F106" t="n">
-        <v>67.73999999999999</v>
-      </c>
-      <c r="G106" t="n">
         <v>80.20999999999999</v>
       </c>
     </row>
@@ -3544,18 +3232,15 @@
         <v>65.18000000000001</v>
       </c>
       <c r="C107" t="n">
-        <v>13.34</v>
+        <v>15.14</v>
       </c>
       <c r="D107" t="n">
-        <v>78.52</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="E107" t="n">
-        <v>71.25</v>
+        <v>73.28</v>
       </c>
       <c r="F107" t="n">
-        <v>67.31</v>
-      </c>
-      <c r="G107" t="n">
         <v>80.31999999999999</v>
       </c>
     </row>
@@ -3569,18 +3254,15 @@
         <v>64.78</v>
       </c>
       <c r="C108" t="n">
-        <v>13.67</v>
+        <v>15.54</v>
       </c>
       <c r="D108" t="n">
-        <v>78.44</v>
+        <v>80.31</v>
       </c>
       <c r="E108" t="n">
-        <v>70.89</v>
+        <v>73.03</v>
       </c>
       <c r="F108" t="n">
-        <v>66.84999999999999</v>
-      </c>
-      <c r="G108" t="n">
         <v>80.31</v>
       </c>
     </row>
@@ -3594,18 +3276,15 @@
         <v>64.31</v>
       </c>
       <c r="C109" t="n">
-        <v>13.87</v>
+        <v>15.9</v>
       </c>
       <c r="D109" t="n">
-        <v>78.17</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="E109" t="n">
-        <v>70.48</v>
+        <v>72.7</v>
       </c>
       <c r="F109" t="n">
-        <v>66.31999999999999</v>
-      </c>
-      <c r="G109" t="n">
         <v>80.20999999999999</v>
       </c>
     </row>
@@ -3619,18 +3298,15 @@
         <v>63.74</v>
       </c>
       <c r="C110" t="n">
-        <v>14.08</v>
+        <v>16.3</v>
       </c>
       <c r="D110" t="n">
-        <v>77.81999999999999</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="E110" t="n">
-        <v>70.04000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="F110" t="n">
-        <v>65.86</v>
-      </c>
-      <c r="G110" t="n">
         <v>80.04000000000001</v>
       </c>
     </row>
@@ -3644,18 +3320,15 @@
         <v>63.12</v>
       </c>
       <c r="C111" t="n">
-        <v>14.53</v>
+        <v>16.73</v>
       </c>
       <c r="D111" t="n">
-        <v>77.65000000000001</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="E111" t="n">
-        <v>69.59999999999999</v>
+        <v>71.94</v>
       </c>
       <c r="F111" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="G111" t="n">
         <v>79.84999999999999</v>
       </c>
     </row>
@@ -3669,18 +3342,15 @@
         <v>62.49</v>
       </c>
       <c r="C112" t="n">
-        <v>14.86</v>
+        <v>16.95</v>
       </c>
       <c r="D112" t="n">
-        <v>77.34999999999999</v>
+        <v>79.44</v>
       </c>
       <c r="E112" t="n">
-        <v>69.15000000000001</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="F112" t="n">
-        <v>65.22</v>
-      </c>
-      <c r="G112" t="n">
         <v>79.44</v>
       </c>
     </row>
@@ -3694,18 +3364,15 @@
         <v>62.01</v>
       </c>
       <c r="C113" t="n">
-        <v>14.98</v>
+        <v>16.98</v>
       </c>
       <c r="D113" t="n">
-        <v>76.98</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="E113" t="n">
-        <v>68.66</v>
+        <v>71.03</v>
       </c>
       <c r="F113" t="n">
-        <v>64.69</v>
-      </c>
-      <c r="G113" t="n">
         <v>78.98999999999999</v>
       </c>
     </row>
@@ -3719,18 +3386,15 @@
         <v>61.6</v>
       </c>
       <c r="C114" t="n">
-        <v>15.01</v>
+        <v>16.92</v>
       </c>
       <c r="D114" t="n">
-        <v>76.61</v>
+        <v>78.52</v>
       </c>
       <c r="E114" t="n">
-        <v>68.17</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="F114" t="n">
-        <v>64.18000000000001</v>
-      </c>
-      <c r="G114" t="n">
         <v>78.52</v>
       </c>
     </row>
@@ -3744,18 +3408,15 @@
         <v>61.12</v>
       </c>
       <c r="C115" t="n">
-        <v>15.22</v>
+        <v>16.92</v>
       </c>
       <c r="D115" t="n">
-        <v>76.34</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="E115" t="n">
-        <v>67.76000000000001</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="F115" t="n">
-        <v>63.64</v>
-      </c>
-      <c r="G115" t="n">
         <v>78.04000000000001</v>
       </c>
     </row>
@@ -3769,18 +3430,15 @@
         <v>60.6</v>
       </c>
       <c r="C116" t="n">
-        <v>15.22</v>
+        <v>17.01</v>
       </c>
       <c r="D116" t="n">
-        <v>75.83</v>
+        <v>77.62</v>
       </c>
       <c r="E116" t="n">
-        <v>67.33</v>
+        <v>69.69</v>
       </c>
       <c r="F116" t="n">
-        <v>63.15</v>
-      </c>
-      <c r="G116" t="n">
         <v>77.62</v>
       </c>
     </row>
@@ -3794,18 +3452,15 @@
         <v>60.07</v>
       </c>
       <c r="C117" t="n">
-        <v>15.19</v>
+        <v>17.28</v>
       </c>
       <c r="D117" t="n">
-        <v>75.27</v>
+        <v>77.36</v>
       </c>
       <c r="E117" t="n">
-        <v>66.87</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="F117" t="n">
-        <v>62.58</v>
-      </c>
-      <c r="G117" t="n">
         <v>77.36</v>
       </c>
     </row>
@@ -3819,18 +3474,15 @@
         <v>59.55</v>
       </c>
       <c r="C118" t="n">
-        <v>15.12</v>
+        <v>17.49</v>
       </c>
       <c r="D118" t="n">
-        <v>74.67</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="E118" t="n">
-        <v>66.45</v>
+        <v>68.77</v>
       </c>
       <c r="F118" t="n">
-        <v>62.09</v>
-      </c>
-      <c r="G118" t="n">
         <v>77.04000000000001</v>
       </c>
     </row>
@@ -3844,18 +3496,15 @@
         <v>58.94</v>
       </c>
       <c r="C119" t="n">
-        <v>15.12</v>
+        <v>17.86</v>
       </c>
       <c r="D119" t="n">
-        <v>74.05</v>
+        <v>76.8</v>
       </c>
       <c r="E119" t="n">
-        <v>66.01000000000001</v>
+        <v>68.36</v>
       </c>
       <c r="F119" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="G119" t="n">
         <v>76.8</v>
       </c>
     </row>
@@ -3869,18 +3518,15 @@
         <v>58.34</v>
       </c>
       <c r="C120" t="n">
-        <v>15.15</v>
+        <v>18.31</v>
       </c>
       <c r="D120" t="n">
-        <v>73.48999999999999</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="E120" t="n">
-        <v>65.55</v>
+        <v>67.95</v>
       </c>
       <c r="F120" t="n">
-        <v>61.63</v>
-      </c>
-      <c r="G120" t="n">
         <v>76.65000000000001</v>
       </c>
     </row>
@@ -3894,18 +3540,15 @@
         <v>57.8</v>
       </c>
       <c r="C121" t="n">
-        <v>15.1</v>
+        <v>18.71</v>
       </c>
       <c r="D121" t="n">
-        <v>72.91</v>
+        <v>76.52</v>
       </c>
       <c r="E121" t="n">
-        <v>65.06999999999999</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="F121" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="G121" t="n">
         <v>76.52</v>
       </c>
     </row>
@@ -3919,18 +3562,15 @@
         <v>57.1</v>
       </c>
       <c r="C122" t="n">
-        <v>15.4</v>
+        <v>19.41</v>
       </c>
       <c r="D122" t="n">
-        <v>72.5</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="E122" t="n">
-        <v>64.58</v>
+        <v>67.16</v>
       </c>
       <c r="F122" t="n">
-        <v>60.99</v>
-      </c>
-      <c r="G122" t="n">
         <v>76.51000000000001</v>
       </c>
     </row>
@@ -3944,18 +3584,15 @@
         <v>56.44</v>
       </c>
       <c r="C123" t="n">
-        <v>15.48</v>
+        <v>19.89</v>
       </c>
       <c r="D123" t="n">
-        <v>71.92</v>
+        <v>76.33</v>
       </c>
       <c r="E123" t="n">
-        <v>64.12</v>
+        <v>66.75</v>
       </c>
       <c r="F123" t="n">
-        <v>60.78</v>
-      </c>
-      <c r="G123" t="n">
         <v>76.33</v>
       </c>
     </row>
@@ -3969,18 +3606,15 @@
         <v>55.79</v>
       </c>
       <c r="C124" t="n">
-        <v>15.54</v>
+        <v>20.56</v>
       </c>
       <c r="D124" t="n">
-        <v>71.33</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="E124" t="n">
-        <v>63.62</v>
+        <v>66.33</v>
       </c>
       <c r="F124" t="n">
-        <v>60.39</v>
-      </c>
-      <c r="G124" t="n">
         <v>76.34999999999999</v>
       </c>
     </row>
@@ -3994,18 +3628,15 @@
         <v>55.33</v>
       </c>
       <c r="C125" t="n">
-        <v>15.5</v>
+        <v>21.52</v>
       </c>
       <c r="D125" t="n">
-        <v>70.81999999999999</v>
+        <v>76.84</v>
       </c>
       <c r="E125" t="n">
-        <v>63.14</v>
+        <v>66.06</v>
       </c>
       <c r="F125" t="n">
-        <v>60.04</v>
-      </c>
-      <c r="G125" t="n">
         <v>76.84</v>
       </c>
       <c r="H125" t="inlineStr">
@@ -4024,18 +3655,15 @@
         <v>55</v>
       </c>
       <c r="C126" t="n">
-        <v>15.39</v>
+        <v>22.39</v>
       </c>
       <c r="D126" t="n">
-        <v>70.39</v>
+        <v>77.39</v>
       </c>
       <c r="E126" t="n">
-        <v>62.7</v>
+        <v>65.83</v>
       </c>
       <c r="F126" t="n">
-        <v>59.71</v>
-      </c>
-      <c r="G126" t="n">
         <v>77.39</v>
       </c>
     </row>
@@ -4049,18 +3677,15 @@
         <v>54.95</v>
       </c>
       <c r="C127" t="n">
-        <v>15.01</v>
+        <v>22.35</v>
       </c>
       <c r="D127" t="n">
-        <v>69.95999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="E127" t="n">
-        <v>62.34</v>
+        <v>65.52</v>
       </c>
       <c r="F127" t="n">
-        <v>59.27</v>
-      </c>
-      <c r="G127" t="n">
         <v>77.3</v>
       </c>
     </row>
@@ -4074,18 +3699,15 @@
         <v>54.97</v>
       </c>
       <c r="C128" t="n">
-        <v>14.67</v>
+        <v>22.12</v>
       </c>
       <c r="D128" t="n">
-        <v>69.64</v>
+        <v>77.09</v>
       </c>
       <c r="E128" t="n">
-        <v>61.99</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="F128" t="n">
-        <v>58.92</v>
-      </c>
-      <c r="G128" t="n">
         <v>77.09</v>
       </c>
     </row>
@@ -4099,18 +3721,15 @@
         <v>54.76</v>
       </c>
       <c r="C129" t="n">
-        <v>14.56</v>
+        <v>21.88</v>
       </c>
       <c r="D129" t="n">
-        <v>69.31999999999999</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="E129" t="n">
-        <v>61.66</v>
+        <v>64.89</v>
       </c>
       <c r="F129" t="n">
-        <v>58.51</v>
-      </c>
-      <c r="G129" t="n">
         <v>76.65000000000001</v>
       </c>
     </row>
@@ -4124,18 +3743,15 @@
         <v>54.46</v>
       </c>
       <c r="C130" t="n">
-        <v>14.28</v>
+        <v>22.27</v>
       </c>
       <c r="D130" t="n">
-        <v>68.75</v>
+        <v>76.73</v>
       </c>
       <c r="E130" t="n">
-        <v>61.28</v>
+        <v>64.61</v>
       </c>
       <c r="F130" t="n">
-        <v>58.07</v>
-      </c>
-      <c r="G130" t="n">
         <v>76.73</v>
       </c>
     </row>
@@ -4149,18 +3765,15 @@
         <v>54.12</v>
       </c>
       <c r="C131" t="n">
-        <v>14.15</v>
+        <v>22.55</v>
       </c>
       <c r="D131" t="n">
-        <v>68.27</v>
+        <v>76.67</v>
       </c>
       <c r="E131" t="n">
-        <v>60.91</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="F131" t="n">
-        <v>57.67</v>
-      </c>
-      <c r="G131" t="n">
         <v>76.67</v>
       </c>
     </row>
@@ -4174,18 +3787,15 @@
         <v>53.69</v>
       </c>
       <c r="C132" t="n">
-        <v>14.12</v>
+        <v>22.9</v>
       </c>
       <c r="D132" t="n">
-        <v>67.81</v>
+        <v>76.59</v>
       </c>
       <c r="E132" t="n">
-        <v>60.54</v>
+        <v>64</v>
       </c>
       <c r="F132" t="n">
-        <v>57.39</v>
-      </c>
-      <c r="G132" t="n">
         <v>76.59</v>
       </c>
     </row>
@@ -4199,18 +3809,15 @@
         <v>53.19</v>
       </c>
       <c r="C133" t="n">
-        <v>14.13</v>
+        <v>23.1</v>
       </c>
       <c r="D133" t="n">
-        <v>67.31999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="E133" t="n">
-        <v>60.28</v>
+        <v>63.73</v>
       </c>
       <c r="F133" t="n">
-        <v>57.48</v>
-      </c>
-      <c r="G133" t="n">
         <v>76.3</v>
       </c>
     </row>
@@ -4224,18 +3831,15 @@
         <v>52.83</v>
       </c>
       <c r="C134" t="n">
-        <v>13.93</v>
+        <v>23.05</v>
       </c>
       <c r="D134" t="n">
-        <v>66.76000000000001</v>
+        <v>75.87</v>
       </c>
       <c r="E134" t="n">
-        <v>59.89</v>
+        <v>63.33</v>
       </c>
       <c r="F134" t="n">
-        <v>57.23</v>
-      </c>
-      <c r="G134" t="n">
         <v>75.87</v>
       </c>
     </row>
@@ -4249,18 +3853,15 @@
         <v>52.45</v>
       </c>
       <c r="C135" t="n">
-        <v>13.89</v>
+        <v>22.94</v>
       </c>
       <c r="D135" t="n">
-        <v>66.34</v>
+        <v>75.39</v>
       </c>
       <c r="E135" t="n">
-        <v>59.4</v>
+        <v>62.82</v>
       </c>
       <c r="F135" t="n">
-        <v>56.91</v>
-      </c>
-      <c r="G135" t="n">
         <v>75.39</v>
       </c>
     </row>
@@ -4274,18 +3875,15 @@
         <v>51.89</v>
       </c>
       <c r="C136" t="n">
-        <v>14.09</v>
+        <v>23.05</v>
       </c>
       <c r="D136" t="n">
-        <v>65.98999999999999</v>
+        <v>74.95</v>
       </c>
       <c r="E136" t="n">
-        <v>59</v>
+        <v>62.41</v>
       </c>
       <c r="F136" t="n">
-        <v>56.61</v>
-      </c>
-      <c r="G136" t="n">
         <v>74.95</v>
       </c>
     </row>
@@ -4299,18 +3897,15 @@
         <v>51.33</v>
       </c>
       <c r="C137" t="n">
-        <v>14.38</v>
+        <v>23.21</v>
       </c>
       <c r="D137" t="n">
-        <v>65.70999999999999</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="E137" t="n">
-        <v>58.64</v>
+        <v>62.05</v>
       </c>
       <c r="F137" t="n">
-        <v>56.33</v>
-      </c>
-      <c r="G137" t="n">
         <v>74.54000000000001</v>
       </c>
     </row>
@@ -4324,18 +3919,15 @@
         <v>50.8</v>
       </c>
       <c r="C138" t="n">
-        <v>14.47</v>
+        <v>23.43</v>
       </c>
       <c r="D138" t="n">
-        <v>65.26000000000001</v>
+        <v>74.22</v>
       </c>
       <c r="E138" t="n">
-        <v>58.29</v>
+        <v>61.69</v>
       </c>
       <c r="F138" t="n">
-        <v>56.23</v>
-      </c>
-      <c r="G138" t="n">
         <v>74.22</v>
       </c>
     </row>
@@ -4349,18 +3941,15 @@
         <v>50.32</v>
       </c>
       <c r="C139" t="n">
-        <v>14.88</v>
+        <v>23.83</v>
       </c>
       <c r="D139" t="n">
-        <v>65.19</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="E139" t="n">
-        <v>58.05</v>
+        <v>61.49</v>
       </c>
       <c r="F139" t="n">
-        <v>56.23</v>
-      </c>
-      <c r="G139" t="n">
         <v>74.15000000000001</v>
       </c>
     </row>
@@ -4374,18 +3963,15 @@
         <v>49.84</v>
       </c>
       <c r="C140" t="n">
-        <v>15</v>
+        <v>24.18</v>
       </c>
       <c r="D140" t="n">
-        <v>64.84</v>
+        <v>74.02</v>
       </c>
       <c r="E140" t="n">
-        <v>57.73</v>
+        <v>61.24</v>
       </c>
       <c r="F140" t="n">
-        <v>56.35</v>
-      </c>
-      <c r="G140" t="n">
         <v>74.02</v>
       </c>
     </row>
@@ -4399,18 +3985,15 @@
         <v>49.35</v>
       </c>
       <c r="C141" t="n">
-        <v>15.08</v>
+        <v>24.51</v>
       </c>
       <c r="D141" t="n">
-        <v>64.43000000000001</v>
+        <v>73.86</v>
       </c>
       <c r="E141" t="n">
-        <v>57.36</v>
+        <v>60.95</v>
       </c>
       <c r="F141" t="n">
-        <v>56.44</v>
-      </c>
-      <c r="G141" t="n">
         <v>73.86</v>
       </c>
     </row>
@@ -4424,18 +4007,15 @@
         <v>49</v>
       </c>
       <c r="C142" t="n">
-        <v>15.03</v>
+        <v>25.08</v>
       </c>
       <c r="D142" t="n">
-        <v>64.03</v>
+        <v>74.08</v>
       </c>
       <c r="E142" t="n">
-        <v>57.08</v>
+        <v>60.8</v>
       </c>
       <c r="F142" t="n">
-        <v>56.44</v>
-      </c>
-      <c r="G142" t="n">
         <v>74.08</v>
       </c>
     </row>
@@ -4449,18 +4029,15 @@
         <v>48.38</v>
       </c>
       <c r="C143" t="n">
-        <v>15.45</v>
+        <v>25.5</v>
       </c>
       <c r="D143" t="n">
-        <v>63.84</v>
+        <v>73.89</v>
       </c>
       <c r="E143" t="n">
-        <v>56.77</v>
+        <v>60.51</v>
       </c>
       <c r="F143" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="G143" t="n">
         <v>73.89</v>
       </c>
     </row>
@@ -4474,18 +4051,15 @@
         <v>47.78</v>
       </c>
       <c r="C144" t="n">
-        <v>15.76</v>
+        <v>26</v>
       </c>
       <c r="D144" t="n">
-        <v>63.55</v>
+        <v>73.78</v>
       </c>
       <c r="E144" t="n">
-        <v>56.47</v>
+        <v>60.26</v>
       </c>
       <c r="F144" t="n">
-        <v>55.91</v>
-      </c>
-      <c r="G144" t="n">
         <v>73.78</v>
       </c>
     </row>
@@ -4499,18 +4073,15 @@
         <v>47.27</v>
       </c>
       <c r="C145" t="n">
-        <v>15.94</v>
+        <v>26.37</v>
       </c>
       <c r="D145" t="n">
-        <v>63.21</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="E145" t="n">
-        <v>56.21</v>
+        <v>60</v>
       </c>
       <c r="F145" t="n">
-        <v>55.63</v>
-      </c>
-      <c r="G145" t="n">
         <v>73.65000000000001</v>
       </c>
     </row>
@@ -4524,18 +4095,15 @@
         <v>46.9</v>
       </c>
       <c r="C146" t="n">
-        <v>15.85</v>
+        <v>26.73</v>
       </c>
       <c r="D146" t="n">
-        <v>62.75</v>
+        <v>73.63</v>
       </c>
       <c r="E146" t="n">
-        <v>55.96</v>
+        <v>59.8</v>
       </c>
       <c r="F146" t="n">
-        <v>55.65</v>
-      </c>
-      <c r="G146" t="n">
         <v>73.63</v>
       </c>
     </row>
@@ -4549,18 +4117,15 @@
         <v>46.44</v>
       </c>
       <c r="C147" t="n">
-        <v>15.8</v>
+        <v>27.15</v>
       </c>
       <c r="D147" t="n">
-        <v>62.24</v>
+        <v>73.59</v>
       </c>
       <c r="E147" t="n">
-        <v>55.66</v>
+        <v>59.55</v>
       </c>
       <c r="F147" t="n">
-        <v>55.79</v>
-      </c>
-      <c r="G147" t="n">
         <v>73.59</v>
       </c>
     </row>
@@ -4574,18 +4139,15 @@
         <v>46.04</v>
       </c>
       <c r="C148" t="n">
-        <v>15.62</v>
+        <v>27.7</v>
       </c>
       <c r="D148" t="n">
-        <v>61.66</v>
+        <v>73.75</v>
       </c>
       <c r="E148" t="n">
-        <v>55.24</v>
+        <v>59.25</v>
       </c>
       <c r="F148" t="n">
-        <v>55.53</v>
-      </c>
-      <c r="G148" t="n">
         <v>73.75</v>
       </c>
     </row>
@@ -4599,18 +4161,15 @@
         <v>45.79</v>
       </c>
       <c r="C149" t="n">
-        <v>15.31</v>
+        <v>28</v>
       </c>
       <c r="D149" t="n">
-        <v>61.1</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="E149" t="n">
-        <v>54.99</v>
+        <v>59.04</v>
       </c>
       <c r="F149" t="n">
-        <v>55.51</v>
-      </c>
-      <c r="G149" t="n">
         <v>73.79000000000001</v>
       </c>
     </row>
@@ -4624,18 +4183,15 @@
         <v>45.32</v>
       </c>
       <c r="C150" t="n">
-        <v>15.28</v>
+        <v>28.39</v>
       </c>
       <c r="D150" t="n">
-        <v>60.6</v>
+        <v>73.7</v>
       </c>
       <c r="E150" t="n">
-        <v>54.68</v>
+        <v>58.73</v>
       </c>
       <c r="F150" t="n">
-        <v>55.23</v>
-      </c>
-      <c r="G150" t="n">
         <v>73.7</v>
       </c>
     </row>
@@ -4649,18 +4205,15 @@
         <v>44.85</v>
       </c>
       <c r="C151" t="n">
-        <v>15.15</v>
+        <v>28.53</v>
       </c>
       <c r="D151" t="n">
-        <v>60</v>
+        <v>73.37</v>
       </c>
       <c r="E151" t="n">
-        <v>54.45</v>
+        <v>58.42</v>
       </c>
       <c r="F151" t="n">
-        <v>54.97</v>
-      </c>
-      <c r="G151" t="n">
         <v>73.37</v>
       </c>
     </row>
@@ -4674,18 +4227,15 @@
         <v>44.32</v>
       </c>
       <c r="C152" t="n">
-        <v>15.17</v>
+        <v>28.68</v>
       </c>
       <c r="D152" t="n">
-        <v>59.49</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="E152" t="n">
-        <v>54.27</v>
+        <v>58.17</v>
       </c>
       <c r="F152" t="n">
-        <v>54.72</v>
-      </c>
-      <c r="G152" t="n">
         <v>73.01000000000001</v>
       </c>
     </row>
@@ -4699,18 +4249,15 @@
         <v>43.8</v>
       </c>
       <c r="C153" t="n">
-        <v>15.81</v>
+        <v>28.89</v>
       </c>
       <c r="D153" t="n">
-        <v>59.62</v>
+        <v>72.69</v>
       </c>
       <c r="E153" t="n">
-        <v>54.05</v>
+        <v>57.91</v>
       </c>
       <c r="F153" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="G153" t="n">
         <v>72.69</v>
       </c>
       <c r="H153" t="inlineStr">
@@ -4729,18 +4276,15 @@
         <v>43.29</v>
       </c>
       <c r="C154" t="n">
-        <v>16.63</v>
+        <v>28.97</v>
       </c>
       <c r="D154" t="n">
-        <v>59.91</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="E154" t="n">
-        <v>53.86</v>
+        <v>57.62</v>
       </c>
       <c r="F154" t="n">
-        <v>54.26</v>
-      </c>
-      <c r="G154" t="n">
         <v>72.26000000000001</v>
       </c>
     </row>
@@ -4754,18 +4298,15 @@
         <v>42.77</v>
       </c>
       <c r="C155" t="n">
-        <v>17.26</v>
+        <v>29.04</v>
       </c>
       <c r="D155" t="n">
-        <v>60.03</v>
+        <v>71.8</v>
       </c>
       <c r="E155" t="n">
-        <v>53.6</v>
+        <v>57.29</v>
       </c>
       <c r="F155" t="n">
-        <v>53.96</v>
-      </c>
-      <c r="G155" t="n">
         <v>71.8</v>
       </c>
     </row>
@@ -4779,18 +4320,15 @@
         <v>42.4</v>
       </c>
       <c r="C156" t="n">
-        <v>17.55</v>
+        <v>29</v>
       </c>
       <c r="D156" t="n">
-        <v>59.95</v>
+        <v>71.41</v>
       </c>
       <c r="E156" t="n">
-        <v>53.42</v>
+        <v>57.07</v>
       </c>
       <c r="F156" t="n">
-        <v>53.88</v>
-      </c>
-      <c r="G156" t="n">
         <v>71.41</v>
       </c>
     </row>
@@ -4804,18 +4342,15 @@
         <v>41.86</v>
       </c>
       <c r="C157" t="n">
-        <v>18.05</v>
+        <v>29.12</v>
       </c>
       <c r="D157" t="n">
-        <v>59.91</v>
+        <v>70.98</v>
       </c>
       <c r="E157" t="n">
-        <v>53.3</v>
+        <v>56.89</v>
       </c>
       <c r="F157" t="n">
-        <v>53.73</v>
-      </c>
-      <c r="G157" t="n">
         <v>70.98</v>
       </c>
     </row>
@@ -4829,18 +4364,15 @@
         <v>41.36</v>
       </c>
       <c r="C158" t="n">
-        <v>19.13</v>
+        <v>29.18</v>
       </c>
       <c r="D158" t="n">
-        <v>60.5</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="E158" t="n">
-        <v>53.27</v>
+        <v>56.79</v>
       </c>
       <c r="F158" t="n">
-        <v>53.59</v>
-      </c>
-      <c r="G158" t="n">
         <v>70.54000000000001</v>
       </c>
     </row>
@@ -4854,18 +4386,15 @@
         <v>40.88</v>
       </c>
       <c r="C159" t="n">
-        <v>19.83</v>
+        <v>29.3</v>
       </c>
       <c r="D159" t="n">
-        <v>60.72</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="E159" t="n">
-        <v>53.21</v>
+        <v>56.6</v>
       </c>
       <c r="F159" t="n">
-        <v>53.44</v>
-      </c>
-      <c r="G159" t="n">
         <v>70.18000000000001</v>
       </c>
     </row>
@@ -4879,18 +4408,15 @@
         <v>40.39</v>
       </c>
       <c r="C160" t="n">
-        <v>20.18</v>
+        <v>29.76</v>
       </c>
       <c r="D160" t="n">
-        <v>60.57</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="E160" t="n">
-        <v>53.14</v>
+        <v>56.44</v>
       </c>
       <c r="F160" t="n">
-        <v>53.23</v>
-      </c>
-      <c r="G160" t="n">
         <v>70.15000000000001</v>
       </c>
     </row>
@@ -4904,18 +4430,15 @@
         <v>39.9</v>
       </c>
       <c r="C161" t="n">
-        <v>20.32</v>
+        <v>29.88</v>
       </c>
       <c r="D161" t="n">
-        <v>60.22</v>
+        <v>69.78</v>
       </c>
       <c r="E161" t="n">
-        <v>52.99</v>
+        <v>56.24</v>
       </c>
       <c r="F161" t="n">
-        <v>52.98</v>
-      </c>
-      <c r="G161" t="n">
         <v>69.78</v>
       </c>
     </row>
@@ -4929,18 +4452,15 @@
         <v>39.57</v>
       </c>
       <c r="C162" t="n">
-        <v>20.35</v>
+        <v>29.84</v>
       </c>
       <c r="D162" t="n">
-        <v>59.92</v>
+        <v>69.42</v>
       </c>
       <c r="E162" t="n">
-        <v>52.72</v>
+        <v>55.93</v>
       </c>
       <c r="F162" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="G162" t="n">
         <v>69.42</v>
       </c>
     </row>
@@ -4954,18 +4474,15 @@
         <v>39.29</v>
       </c>
       <c r="C163" t="n">
-        <v>20.34</v>
+        <v>29.81</v>
       </c>
       <c r="D163" t="n">
-        <v>59.63</v>
+        <v>69.09</v>
       </c>
       <c r="E163" t="n">
-        <v>52.68</v>
+        <v>55.87</v>
       </c>
       <c r="F163" t="n">
-        <v>52.08</v>
-      </c>
-      <c r="G163" t="n">
         <v>69.09</v>
       </c>
     </row>
@@ -4979,18 +4496,15 @@
         <v>39</v>
       </c>
       <c r="C164" t="n">
-        <v>21.11</v>
+        <v>29.68</v>
       </c>
       <c r="D164" t="n">
-        <v>60.11</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="E164" t="n">
-        <v>52.8</v>
+        <v>55.86</v>
       </c>
       <c r="F164" t="n">
-        <v>51.91</v>
-      </c>
-      <c r="G164" t="n">
         <v>68.68000000000001</v>
       </c>
     </row>
@@ -5004,18 +4518,15 @@
         <v>38.6</v>
       </c>
       <c r="C165" t="n">
-        <v>22.23</v>
+        <v>29.68</v>
       </c>
       <c r="D165" t="n">
-        <v>60.83</v>
+        <v>68.28</v>
       </c>
       <c r="E165" t="n">
-        <v>52.84</v>
+        <v>55.77</v>
       </c>
       <c r="F165" t="n">
-        <v>51.64</v>
-      </c>
-      <c r="G165" t="n">
         <v>68.28</v>
       </c>
     </row>
@@ -5029,18 +4540,15 @@
         <v>38.03</v>
       </c>
       <c r="C166" t="n">
-        <v>23</v>
+        <v>29.86</v>
       </c>
       <c r="D166" t="n">
-        <v>61.03</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E166" t="n">
-        <v>52.7</v>
+        <v>55.53</v>
       </c>
       <c r="F166" t="n">
-        <v>51.33</v>
-      </c>
-      <c r="G166" t="n">
         <v>67.90000000000001</v>
       </c>
     </row>
@@ -5054,18 +4562,15 @@
         <v>37.66</v>
       </c>
       <c r="C167" t="n">
-        <v>23.54</v>
+        <v>29.93</v>
       </c>
       <c r="D167" t="n">
-        <v>61.2</v>
+        <v>67.59</v>
       </c>
       <c r="E167" t="n">
-        <v>52.6</v>
+        <v>55.33</v>
       </c>
       <c r="F167" t="n">
-        <v>50.99</v>
-      </c>
-      <c r="G167" t="n">
         <v>67.59</v>
       </c>
     </row>
@@ -5079,18 +4584,15 @@
         <v>37.11</v>
       </c>
       <c r="C168" t="n">
-        <v>24.25</v>
+        <v>30.03</v>
       </c>
       <c r="D168" t="n">
-        <v>61.35</v>
+        <v>67.14</v>
       </c>
       <c r="E168" t="n">
-        <v>52.55</v>
+        <v>55.11</v>
       </c>
       <c r="F168" t="n">
-        <v>50.98</v>
-      </c>
-      <c r="G168" t="n">
         <v>67.14</v>
       </c>
     </row>
@@ -5104,18 +4606,15 @@
         <v>36.61</v>
       </c>
       <c r="C169" t="n">
-        <v>24.91</v>
+        <v>30.08</v>
       </c>
       <c r="D169" t="n">
-        <v>61.52</v>
+        <v>66.69</v>
       </c>
       <c r="E169" t="n">
-        <v>52.55</v>
+        <v>54.96</v>
       </c>
       <c r="F169" t="n">
-        <v>51.19</v>
-      </c>
-      <c r="G169" t="n">
         <v>66.69</v>
       </c>
     </row>
@@ -5129,18 +4628,15 @@
         <v>36.29</v>
       </c>
       <c r="C170" t="n">
-        <v>25.37</v>
+        <v>30.33</v>
       </c>
       <c r="D170" t="n">
-        <v>61.66</v>
+        <v>66.62</v>
       </c>
       <c r="E170" t="n">
-        <v>52.62</v>
+        <v>54.89</v>
       </c>
       <c r="F170" t="n">
-        <v>51.45</v>
-      </c>
-      <c r="G170" t="n">
         <v>66.62</v>
       </c>
     </row>
@@ -5154,18 +4650,15 @@
         <v>35.74</v>
       </c>
       <c r="C171" t="n">
-        <v>26.02</v>
+        <v>30.62</v>
       </c>
       <c r="D171" t="n">
-        <v>61.76</v>
+        <v>66.36</v>
       </c>
       <c r="E171" t="n">
-        <v>52.48</v>
+        <v>54.66</v>
       </c>
       <c r="F171" t="n">
-        <v>51.26</v>
-      </c>
-      <c r="G171" t="n">
         <v>66.36</v>
       </c>
     </row>
@@ -5179,18 +4672,15 @@
         <v>35.33</v>
       </c>
       <c r="C172" t="n">
-        <v>26.37</v>
+        <v>30.6</v>
       </c>
       <c r="D172" t="n">
-        <v>61.7</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E172" t="n">
-        <v>52.43</v>
+        <v>54.44</v>
       </c>
       <c r="F172" t="n">
-        <v>51.08</v>
-      </c>
-      <c r="G172" t="n">
         <v>65.93000000000001</v>
       </c>
     </row>
@@ -5204,18 +4694,15 @@
         <v>34.83</v>
       </c>
       <c r="C173" t="n">
-        <v>26.58</v>
+        <v>30.79</v>
       </c>
       <c r="D173" t="n">
-        <v>61.41</v>
+        <v>65.62</v>
       </c>
       <c r="E173" t="n">
-        <v>52.33</v>
+        <v>54.21</v>
       </c>
       <c r="F173" t="n">
-        <v>51.09</v>
-      </c>
-      <c r="G173" t="n">
         <v>65.62</v>
       </c>
     </row>
@@ -5229,18 +4716,15 @@
         <v>34.44</v>
       </c>
       <c r="C174" t="n">
-        <v>26.61</v>
+        <v>31.1</v>
       </c>
       <c r="D174" t="n">
-        <v>61.05</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="E174" t="n">
-        <v>52.2</v>
+        <v>53.99</v>
       </c>
       <c r="F174" t="n">
-        <v>51.03</v>
-      </c>
-      <c r="G174" t="n">
         <v>65.54000000000001</v>
       </c>
     </row>
@@ -5254,18 +4738,15 @@
         <v>33.99</v>
       </c>
       <c r="C175" t="n">
-        <v>26.87</v>
+        <v>31.39</v>
       </c>
       <c r="D175" t="n">
-        <v>60.86</v>
+        <v>65.38</v>
       </c>
       <c r="E175" t="n">
-        <v>51.98</v>
+        <v>53.75</v>
       </c>
       <c r="F175" t="n">
-        <v>50.86</v>
-      </c>
-      <c r="G175" t="n">
         <v>65.38</v>
       </c>
     </row>
@@ -5279,18 +4760,15 @@
         <v>33.54</v>
       </c>
       <c r="C176" t="n">
-        <v>27.21</v>
+        <v>31.56</v>
       </c>
       <c r="D176" t="n">
-        <v>60.76</v>
+        <v>65.11</v>
       </c>
       <c r="E176" t="n">
-        <v>51.82</v>
+        <v>53.45</v>
       </c>
       <c r="F176" t="n">
-        <v>50.61</v>
-      </c>
-      <c r="G176" t="n">
         <v>65.11</v>
       </c>
     </row>
@@ -5304,18 +4782,15 @@
         <v>33.16</v>
       </c>
       <c r="C177" t="n">
-        <v>27.62</v>
+        <v>31.64</v>
       </c>
       <c r="D177" t="n">
-        <v>60.78</v>
+        <v>64.8</v>
       </c>
       <c r="E177" t="n">
-        <v>51.58</v>
+        <v>53.15</v>
       </c>
       <c r="F177" t="n">
-        <v>50.17</v>
-      </c>
-      <c r="G177" t="n">
         <v>64.8</v>
       </c>
     </row>
@@ -5329,18 +4804,15 @@
         <v>32.84</v>
       </c>
       <c r="C178" t="n">
-        <v>27.99</v>
+        <v>31.67</v>
       </c>
       <c r="D178" t="n">
-        <v>60.82</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="E178" t="n">
-        <v>51.42</v>
+        <v>52.91</v>
       </c>
       <c r="F178" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="G178" t="n">
         <v>64.51000000000001</v>
       </c>
     </row>
@@ -5354,18 +4826,15 @@
         <v>32.45</v>
       </c>
       <c r="C179" t="n">
-        <v>28.26</v>
+        <v>31.86</v>
       </c>
       <c r="D179" t="n">
-        <v>60.72</v>
+        <v>64.31</v>
       </c>
       <c r="E179" t="n">
-        <v>51.36</v>
+        <v>52.74</v>
       </c>
       <c r="F179" t="n">
-        <v>49.33</v>
-      </c>
-      <c r="G179" t="n">
         <v>64.31</v>
       </c>
     </row>
@@ -5379,18 +4848,15 @@
         <v>32.17</v>
       </c>
       <c r="C180" t="n">
-        <v>28.38</v>
+        <v>31.77</v>
       </c>
       <c r="D180" t="n">
-        <v>60.56</v>
+        <v>63.95</v>
       </c>
       <c r="E180" t="n">
-        <v>51.23</v>
+        <v>52.52</v>
       </c>
       <c r="F180" t="n">
-        <v>49.11</v>
-      </c>
-      <c r="G180" t="n">
         <v>63.95</v>
       </c>
     </row>
@@ -5404,18 +4870,15 @@
         <v>32</v>
       </c>
       <c r="C181" t="n">
-        <v>28.31</v>
+        <v>31.76</v>
       </c>
       <c r="D181" t="n">
-        <v>60.31</v>
+        <v>63.77</v>
       </c>
       <c r="E181" t="n">
-        <v>51.16</v>
+        <v>52.42</v>
       </c>
       <c r="F181" t="n">
-        <v>49.06</v>
-      </c>
-      <c r="G181" t="n">
         <v>63.77</v>
       </c>
     </row>
@@ -5429,18 +4892,15 @@
         <v>31.86</v>
       </c>
       <c r="C182" t="n">
-        <v>28.17</v>
+        <v>31.75</v>
       </c>
       <c r="D182" t="n">
-        <v>60.03</v>
+        <v>63.61</v>
       </c>
       <c r="E182" t="n">
-        <v>51.18</v>
+        <v>52.34</v>
       </c>
       <c r="F182" t="n">
-        <v>49.09</v>
-      </c>
-      <c r="G182" t="n">
         <v>63.61</v>
       </c>
     </row>
@@ -5454,18 +4914,15 @@
         <v>31.61</v>
       </c>
       <c r="C183" t="n">
-        <v>28.27</v>
+        <v>31.83</v>
       </c>
       <c r="D183" t="n">
-        <v>59.88</v>
+        <v>63.44</v>
       </c>
       <c r="E183" t="n">
-        <v>51.2</v>
+        <v>52.31</v>
       </c>
       <c r="F183" t="n">
-        <v>49.25</v>
-      </c>
-      <c r="G183" t="n">
         <v>63.44</v>
       </c>
     </row>
@@ -5479,18 +4936,15 @@
         <v>31.51</v>
       </c>
       <c r="C184" t="n">
-        <v>28.2</v>
+        <v>31.76</v>
       </c>
       <c r="D184" t="n">
-        <v>59.71</v>
+        <v>63.27</v>
       </c>
       <c r="E184" t="n">
-        <v>51.27</v>
+        <v>52.34</v>
       </c>
       <c r="F184" t="n">
-        <v>49.41</v>
-      </c>
-      <c r="G184" t="n">
         <v>63.27</v>
       </c>
       <c r="H184" t="inlineStr">
@@ -5509,18 +4963,15 @@
         <v>31.39</v>
       </c>
       <c r="C185" t="n">
-        <v>28.68</v>
+        <v>31.95</v>
       </c>
       <c r="D185" t="n">
-        <v>60.07</v>
+        <v>63.34</v>
       </c>
       <c r="E185" t="n">
-        <v>51.37</v>
+        <v>52.43</v>
       </c>
       <c r="F185" t="n">
-        <v>49.44</v>
-      </c>
-      <c r="G185" t="n">
         <v>63.34</v>
       </c>
     </row>
@@ -5534,18 +4985,15 @@
         <v>31.45</v>
       </c>
       <c r="C186" t="n">
-        <v>28.53</v>
+        <v>31.87</v>
       </c>
       <c r="D186" t="n">
-        <v>59.98</v>
+        <v>63.32</v>
       </c>
       <c r="E186" t="n">
-        <v>51.42</v>
+        <v>52.42</v>
       </c>
       <c r="F186" t="n">
-        <v>49.48</v>
-      </c>
-      <c r="G186" t="n">
         <v>63.32</v>
       </c>
     </row>
@@ -5559,18 +5007,15 @@
         <v>31.42</v>
       </c>
       <c r="C187" t="n">
-        <v>28.34</v>
+        <v>31.75</v>
       </c>
       <c r="D187" t="n">
-        <v>59.76</v>
+        <v>63.17</v>
       </c>
       <c r="E187" t="n">
-        <v>51.47</v>
+        <v>52.37</v>
       </c>
       <c r="F187" t="n">
-        <v>49.63</v>
-      </c>
-      <c r="G187" t="n">
         <v>63.17</v>
       </c>
     </row>
@@ -5584,18 +5029,15 @@
         <v>31.65</v>
       </c>
       <c r="C188" t="n">
-        <v>27.82</v>
+        <v>31.61</v>
       </c>
       <c r="D188" t="n">
-        <v>59.47</v>
+        <v>63.26</v>
       </c>
       <c r="E188" t="n">
-        <v>51.55</v>
+        <v>52.45</v>
       </c>
       <c r="F188" t="n">
-        <v>49.95</v>
-      </c>
-      <c r="G188" t="n">
         <v>63.26</v>
       </c>
     </row>
@@ -5609,18 +5051,15 @@
         <v>31.71</v>
       </c>
       <c r="C189" t="n">
-        <v>27.84</v>
+        <v>31.2</v>
       </c>
       <c r="D189" t="n">
-        <v>59.55</v>
+        <v>62.9</v>
       </c>
       <c r="E189" t="n">
-        <v>51.75</v>
+        <v>52.49</v>
       </c>
       <c r="F189" t="n">
-        <v>50.29</v>
-      </c>
-      <c r="G189" t="n">
         <v>62.9</v>
       </c>
     </row>
@@ -5634,18 +5073,15 @@
         <v>31.72</v>
       </c>
       <c r="C190" t="n">
-        <v>28.04</v>
+        <v>30.9</v>
       </c>
       <c r="D190" t="n">
-        <v>59.77</v>
+        <v>62.63</v>
       </c>
       <c r="E190" t="n">
-        <v>51.99</v>
+        <v>52.66</v>
       </c>
       <c r="F190" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="G190" t="n">
         <v>62.63</v>
       </c>
     </row>
@@ -5659,18 +5095,15 @@
         <v>31.63</v>
       </c>
       <c r="C191" t="n">
-        <v>28.25</v>
+        <v>31.18</v>
       </c>
       <c r="D191" t="n">
-        <v>59.88</v>
+        <v>62.81</v>
       </c>
       <c r="E191" t="n">
-        <v>52.13</v>
+        <v>52.83</v>
       </c>
       <c r="F191" t="n">
-        <v>51.05</v>
-      </c>
-      <c r="G191" t="n">
         <v>62.81</v>
       </c>
     </row>
@@ -5684,18 +5117,15 @@
         <v>31.48</v>
       </c>
       <c r="C192" t="n">
-        <v>28.49</v>
+        <v>31.13</v>
       </c>
       <c r="D192" t="n">
-        <v>59.97</v>
+        <v>62.61</v>
       </c>
       <c r="E192" t="n">
-        <v>52.3</v>
+        <v>52.82</v>
       </c>
       <c r="F192" t="n">
-        <v>51.29</v>
-      </c>
-      <c r="G192" t="n">
         <v>62.61</v>
       </c>
     </row>
@@ -5709,18 +5139,15 @@
         <v>31.27</v>
       </c>
       <c r="C193" t="n">
-        <v>28.79</v>
+        <v>30.99</v>
       </c>
       <c r="D193" t="n">
-        <v>60.07</v>
+        <v>62.26</v>
       </c>
       <c r="E193" t="n">
-        <v>52.42</v>
+        <v>52.86</v>
       </c>
       <c r="F193" t="n">
-        <v>52.26</v>
-      </c>
-      <c r="G193" t="n">
         <v>62.26</v>
       </c>
     </row>
@@ -5734,18 +5161,15 @@
         <v>31.02</v>
       </c>
       <c r="C194" t="n">
-        <v>29.14</v>
+        <v>31.1</v>
       </c>
       <c r="D194" t="n">
-        <v>60.15</v>
+        <v>62.12</v>
       </c>
       <c r="E194" t="n">
-        <v>52.56</v>
+        <v>52.95</v>
       </c>
       <c r="F194" t="n">
-        <v>53.47</v>
-      </c>
-      <c r="G194" t="n">
         <v>62.12</v>
       </c>
     </row>
@@ -5759,18 +5183,15 @@
         <v>30.64</v>
       </c>
       <c r="C195" t="n">
-        <v>30.46</v>
+        <v>31.28</v>
       </c>
       <c r="D195" t="n">
-        <v>61.1</v>
+        <v>61.92</v>
       </c>
       <c r="E195" t="n">
-        <v>52.74</v>
+        <v>52.91</v>
       </c>
       <c r="F195" t="n">
-        <v>54.04</v>
-      </c>
-      <c r="G195" t="n">
         <v>61.92</v>
       </c>
     </row>
@@ -5784,18 +5205,15 @@
         <v>30.24</v>
       </c>
       <c r="C196" t="n">
-        <v>30.85</v>
+        <v>31.33</v>
       </c>
       <c r="D196" t="n">
-        <v>61.09</v>
+        <v>61.57</v>
       </c>
       <c r="E196" t="n">
-        <v>52.63</v>
+        <v>52.73</v>
       </c>
       <c r="F196" t="n">
-        <v>54.28</v>
-      </c>
-      <c r="G196" t="n">
         <v>61.57</v>
       </c>
     </row>
@@ -5809,18 +5227,15 @@
         <v>29.97</v>
       </c>
       <c r="C197" t="n">
-        <v>30.99</v>
+        <v>31.34</v>
       </c>
       <c r="D197" t="n">
-        <v>60.96</v>
+        <v>61.32</v>
       </c>
       <c r="E197" t="n">
-        <v>52.41</v>
+        <v>52.48</v>
       </c>
       <c r="F197" t="n">
-        <v>54.22</v>
-      </c>
-      <c r="G197" t="n">
         <v>61.32</v>
       </c>
     </row>
@@ -5834,18 +5249,15 @@
         <v>29.79</v>
       </c>
       <c r="C198" t="n">
-        <v>31.16</v>
+        <v>31.43</v>
       </c>
       <c r="D198" t="n">
-        <v>60.96</v>
+        <v>61.22</v>
       </c>
       <c r="E198" t="n">
-        <v>52.22</v>
+        <v>52.27</v>
       </c>
       <c r="F198" t="n">
-        <v>53.99</v>
-      </c>
-      <c r="G198" t="n">
         <v>61.22</v>
       </c>
     </row>
@@ -5859,18 +5271,15 @@
         <v>29.47</v>
       </c>
       <c r="C199" t="n">
-        <v>31.58</v>
+        <v>32.17</v>
       </c>
       <c r="D199" t="n">
-        <v>61.05</v>
+        <v>61.63</v>
       </c>
       <c r="E199" t="n">
-        <v>52.12</v>
+        <v>52.24</v>
       </c>
       <c r="F199" t="n">
-        <v>53.7</v>
-      </c>
-      <c r="G199" t="n">
         <v>61.63</v>
       </c>
     </row>
@@ -5884,18 +5293,15 @@
         <v>29.09</v>
       </c>
       <c r="C200" t="n">
-        <v>32.22</v>
+        <v>33.26</v>
       </c>
       <c r="D200" t="n">
-        <v>61.31</v>
+        <v>62.35</v>
       </c>
       <c r="E200" t="n">
-        <v>52.2</v>
+        <v>52.4</v>
       </c>
       <c r="F200" t="n">
-        <v>53.69</v>
-      </c>
-      <c r="G200" t="n">
         <v>62.35</v>
       </c>
     </row>
@@ -5909,18 +5315,15 @@
         <v>28.74</v>
       </c>
       <c r="C201" t="n">
-        <v>32.74</v>
+        <v>33.93</v>
       </c>
       <c r="D201" t="n">
-        <v>61.47</v>
+        <v>62.66</v>
       </c>
       <c r="E201" t="n">
-        <v>52.25</v>
+        <v>52.48</v>
       </c>
       <c r="F201" t="n">
-        <v>53.66</v>
-      </c>
-      <c r="G201" t="n">
         <v>62.66</v>
       </c>
     </row>
@@ -5934,18 +5337,15 @@
         <v>28.56</v>
       </c>
       <c r="C202" t="n">
-        <v>32.87</v>
+        <v>34.24</v>
       </c>
       <c r="D202" t="n">
-        <v>61.43</v>
+        <v>62.8</v>
       </c>
       <c r="E202" t="n">
-        <v>52.28</v>
+        <v>52.56</v>
       </c>
       <c r="F202" t="n">
-        <v>53.77</v>
-      </c>
-      <c r="G202" t="n">
         <v>62.8</v>
       </c>
     </row>
@@ -5959,18 +5359,15 @@
         <v>28.65</v>
       </c>
       <c r="C203" t="n">
-        <v>32.48</v>
+        <v>34.08</v>
       </c>
       <c r="D203" t="n">
-        <v>61.13</v>
+        <v>62.73</v>
       </c>
       <c r="E203" t="n">
-        <v>52.49</v>
+        <v>52.82</v>
       </c>
       <c r="F203" t="n">
-        <v>54.55</v>
-      </c>
-      <c r="G203" t="n">
         <v>62.73</v>
       </c>
     </row>
@@ -5984,18 +5381,15 @@
         <v>28.88</v>
       </c>
       <c r="C204" t="n">
-        <v>32.06</v>
+        <v>33.77</v>
       </c>
       <c r="D204" t="n">
-        <v>60.94</v>
+        <v>62.64</v>
       </c>
       <c r="E204" t="n">
-        <v>52.72</v>
+        <v>53.07</v>
       </c>
       <c r="F204" t="n">
-        <v>54.75</v>
-      </c>
-      <c r="G204" t="n">
         <v>62.64</v>
       </c>
     </row>
@@ -6009,18 +5403,15 @@
         <v>29.4</v>
       </c>
       <c r="C205" t="n">
-        <v>31.57</v>
+        <v>33.07</v>
       </c>
       <c r="D205" t="n">
-        <v>60.97</v>
+        <v>62.47</v>
       </c>
       <c r="E205" t="n">
-        <v>52.99</v>
+        <v>53.36</v>
       </c>
       <c r="F205" t="n">
-        <v>54.77</v>
-      </c>
-      <c r="G205" t="n">
         <v>62.47</v>
       </c>
     </row>
@@ -6034,18 +5425,15 @@
         <v>30.02</v>
       </c>
       <c r="C206" t="n">
-        <v>31.59</v>
+        <v>32.44</v>
       </c>
       <c r="D206" t="n">
-        <v>61.61</v>
+        <v>62.47</v>
       </c>
       <c r="E206" t="n">
-        <v>53.35</v>
+        <v>53.7</v>
       </c>
       <c r="F206" t="n">
-        <v>54.93</v>
-      </c>
-      <c r="G206" t="n">
         <v>62.47</v>
       </c>
     </row>
@@ -6059,18 +5447,15 @@
         <v>30.37</v>
       </c>
       <c r="C207" t="n">
-        <v>31.6</v>
+        <v>32.18</v>
       </c>
       <c r="D207" t="n">
-        <v>61.96</v>
+        <v>62.54</v>
       </c>
       <c r="E207" t="n">
-        <v>53.6</v>
+        <v>53.99</v>
       </c>
       <c r="F207" t="n">
-        <v>55.39</v>
-      </c>
-      <c r="G207" t="n">
         <v>62.54</v>
       </c>
     </row>
@@ -6084,18 +5469,15 @@
         <v>30.48</v>
       </c>
       <c r="C208" t="n">
-        <v>32.22</v>
+        <v>32.55</v>
       </c>
       <c r="D208" t="n">
-        <v>62.7</v>
+        <v>63.03</v>
       </c>
       <c r="E208" t="n">
-        <v>53.85</v>
+        <v>54.35</v>
       </c>
       <c r="F208" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="G208" t="n">
         <v>63.03</v>
       </c>
     </row>
@@ -6109,18 +5491,15 @@
         <v>30.76</v>
       </c>
       <c r="C209" t="n">
-        <v>32.07</v>
+        <v>32.8</v>
       </c>
       <c r="D209" t="n">
-        <v>62.83</v>
+        <v>63.56</v>
       </c>
       <c r="E209" t="n">
-        <v>54.13</v>
+        <v>54.77</v>
       </c>
       <c r="F209" t="n">
-        <v>56.56</v>
-      </c>
-      <c r="G209" t="n">
         <v>63.56</v>
       </c>
     </row>
@@ -6134,18 +5513,15 @@
         <v>31.1</v>
       </c>
       <c r="C210" t="n">
-        <v>32.16</v>
+        <v>32.67</v>
       </c>
       <c r="D210" t="n">
-        <v>63.26</v>
+        <v>63.78</v>
       </c>
       <c r="E210" t="n">
-        <v>54.48</v>
+        <v>55.13</v>
       </c>
       <c r="F210" t="n">
-        <v>57.27</v>
-      </c>
-      <c r="G210" t="n">
         <v>63.78</v>
       </c>
     </row>
@@ -6159,18 +5535,15 @@
         <v>31.42</v>
       </c>
       <c r="C211" t="n">
-        <v>32.16</v>
+        <v>32.51</v>
       </c>
       <c r="D211" t="n">
-        <v>63.58</v>
+        <v>63.93</v>
       </c>
       <c r="E211" t="n">
-        <v>55</v>
+        <v>55.63</v>
       </c>
       <c r="F211" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="G211" t="n">
         <v>63.93</v>
       </c>
     </row>
@@ -6184,18 +5557,15 @@
         <v>32.02</v>
       </c>
       <c r="C212" t="n">
-        <v>31.98</v>
+        <v>32.21</v>
       </c>
       <c r="D212" t="n">
-        <v>63.99</v>
+        <v>64.23</v>
       </c>
       <c r="E212" t="n">
-        <v>55.56</v>
+        <v>56.11</v>
       </c>
       <c r="F212" t="n">
-        <v>58.93</v>
-      </c>
-      <c r="G212" t="n">
         <v>64.23</v>
       </c>
     </row>
@@ -6209,18 +5579,15 @@
         <v>32.68</v>
       </c>
       <c r="C213" t="n">
-        <v>31.3</v>
+        <v>31.35</v>
       </c>
       <c r="D213" t="n">
-        <v>63.97</v>
+        <v>64.03</v>
       </c>
       <c r="E213" t="n">
-        <v>56.32</v>
+        <v>56.56</v>
       </c>
       <c r="F213" t="n">
-        <v>60.01</v>
-      </c>
-      <c r="G213" t="n">
         <v>64.03</v>
       </c>
     </row>
@@ -6240,12 +5607,9 @@
         <v>64.01000000000001</v>
       </c>
       <c r="E214" t="n">
-        <v>56.61</v>
+        <v>56.72</v>
       </c>
       <c r="F214" t="n">
-        <v>60.58</v>
-      </c>
-      <c r="G214" t="n">
         <v>63.88</v>
       </c>
       <c r="H214" t="inlineStr">
@@ -6264,18 +5628,15 @@
         <v>33</v>
       </c>
       <c r="C215" t="n">
-        <v>31.36</v>
+        <v>31.38</v>
       </c>
       <c r="D215" t="n">
-        <v>64.36</v>
+        <v>64.38</v>
       </c>
       <c r="E215" t="n">
         <v>56.86</v>
       </c>
       <c r="F215" t="n">
-        <v>60.86</v>
-      </c>
-      <c r="G215" t="n">
         <v>64.38</v>
       </c>
     </row>
@@ -6289,18 +5650,15 @@
         <v>33.03</v>
       </c>
       <c r="C216" t="n">
-        <v>32.89</v>
+        <v>31.59</v>
       </c>
       <c r="D216" t="n">
-        <v>65.92</v>
+        <v>64.62</v>
       </c>
       <c r="E216" t="n">
-        <v>57.16</v>
+        <v>56.9</v>
       </c>
       <c r="F216" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="G216" t="n">
         <v>64.62</v>
       </c>
     </row>
@@ -6314,18 +5672,15 @@
         <v>32.95</v>
       </c>
       <c r="C217" t="n">
-        <v>34.06</v>
+        <v>32.02</v>
       </c>
       <c r="D217" t="n">
-        <v>67.01000000000001</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="E217" t="n">
-        <v>57.3</v>
+        <v>56.89</v>
       </c>
       <c r="F217" t="n">
-        <v>61.74</v>
-      </c>
-      <c r="G217" t="n">
         <v>64.95999999999999</v>
       </c>
     </row>
@@ -6339,18 +5694,15 @@
         <v>33.68</v>
       </c>
       <c r="C218" t="n">
-        <v>36.8</v>
+        <v>31.33</v>
       </c>
       <c r="D218" t="n">
-        <v>70.48</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="E218" t="n">
-        <v>58.26</v>
+        <v>57.17</v>
       </c>
       <c r="F218" t="n">
-        <v>62.54</v>
-      </c>
-      <c r="G218" t="n">
         <v>65.01000000000001</v>
       </c>
     </row>
@@ -6364,18 +5716,15 @@
         <v>34.42</v>
       </c>
       <c r="C219" t="n">
-        <v>34.11</v>
+        <v>30.91</v>
       </c>
       <c r="D219" t="n">
-        <v>68.53</v>
+        <v>65.33</v>
       </c>
       <c r="E219" t="n">
-        <v>58.13</v>
+        <v>57.49</v>
       </c>
       <c r="F219" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="G219" t="n">
         <v>65.33</v>
       </c>
     </row>
@@ -6389,18 +5738,15 @@
         <v>34.54</v>
       </c>
       <c r="C220" t="n">
-        <v>34.6</v>
+        <v>30.76</v>
       </c>
       <c r="D220" t="n">
-        <v>69.14</v>
+        <v>65.3</v>
       </c>
       <c r="E220" t="n">
-        <v>58.6</v>
+        <v>57.83</v>
       </c>
       <c r="F220" t="n">
-        <v>64.25</v>
-      </c>
-      <c r="G220" t="n">
         <v>65.3</v>
       </c>
     </row>
@@ -6414,18 +5760,15 @@
         <v>34.51</v>
       </c>
       <c r="C221" t="n">
-        <v>35.52</v>
+        <v>30.95</v>
       </c>
       <c r="D221" t="n">
-        <v>70.03</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="E221" t="n">
-        <v>58.88</v>
+        <v>57.91</v>
       </c>
       <c r="F221" t="n">
-        <v>64.66</v>
-      </c>
-      <c r="G221" t="n">
         <v>65.17</v>
       </c>
     </row>
@@ -6439,18 +5782,15 @@
         <v>34.91</v>
       </c>
       <c r="C222" t="n">
-        <v>36.13</v>
+        <v>30.69</v>
       </c>
       <c r="D222" t="n">
-        <v>71.03</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E222" t="n">
-        <v>59.16</v>
+        <v>57.95</v>
       </c>
       <c r="F222" t="n">
-        <v>64.92</v>
-      </c>
-      <c r="G222" t="n">
         <v>64.95999999999999</v>
       </c>
     </row>
@@ -6464,18 +5804,15 @@
         <v>36.04</v>
       </c>
       <c r="C223" t="n">
-        <v>36.33</v>
+        <v>29.62</v>
       </c>
       <c r="D223" t="n">
-        <v>72.37</v>
+        <v>65.67</v>
       </c>
       <c r="E223" t="n">
-        <v>59.65</v>
+        <v>58.12</v>
       </c>
       <c r="F223" t="n">
-        <v>65.05</v>
-      </c>
-      <c r="G223" t="n">
         <v>64.75</v>
       </c>
     </row>
@@ -6489,18 +5826,15 @@
         <v>36.85</v>
       </c>
       <c r="C224" t="n">
-        <v>36.05</v>
+        <v>29.08</v>
       </c>
       <c r="D224" t="n">
-        <v>72.90000000000001</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E224" t="n">
-        <v>59.98</v>
+        <v>58.29</v>
       </c>
       <c r="F224" t="n">
-        <v>65.31</v>
-      </c>
-      <c r="G224" t="n">
         <v>64.47</v>
       </c>
     </row>
@@ -6514,18 +5848,15 @@
         <v>37.15</v>
       </c>
       <c r="C225" t="n">
-        <v>36.2</v>
+        <v>28.92</v>
       </c>
       <c r="D225" t="n">
-        <v>73.34999999999999</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="E225" t="n">
-        <v>60.11</v>
+        <v>58.33</v>
       </c>
       <c r="F225" t="n">
-        <v>65.31</v>
-      </c>
-      <c r="G225" t="n">
         <v>64.45999999999999</v>
       </c>
     </row>
@@ -6539,18 +5870,15 @@
         <v>37.51</v>
       </c>
       <c r="C226" t="n">
-        <v>36.22</v>
+        <v>28.8</v>
       </c>
       <c r="D226" t="n">
-        <v>73.73</v>
+        <v>66.3</v>
       </c>
       <c r="E226" t="n">
-        <v>60.29</v>
+        <v>58.45</v>
       </c>
       <c r="F226" t="n">
-        <v>65.43000000000001</v>
-      </c>
-      <c r="G226" t="n">
         <v>64.56</v>
       </c>
     </row>
@@ -6564,18 +5892,15 @@
         <v>38.13</v>
       </c>
       <c r="C227" t="n">
-        <v>35.81</v>
+        <v>28.74</v>
       </c>
       <c r="D227" t="n">
-        <v>73.94</v>
+        <v>66.87</v>
       </c>
       <c r="E227" t="n">
-        <v>60.62</v>
+        <v>58.77</v>
       </c>
       <c r="F227" t="n">
-        <v>65.70999999999999</v>
-      </c>
-      <c r="G227" t="n">
         <v>64.68000000000001</v>
       </c>
     </row>
@@ -6589,18 +5914,15 @@
         <v>38.22</v>
       </c>
       <c r="C228" t="n">
-        <v>36.02</v>
+        <v>28.95</v>
       </c>
       <c r="D228" t="n">
-        <v>74.23999999999999</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="E228" t="n">
-        <v>60.85</v>
+        <v>58.91</v>
       </c>
       <c r="F228" t="n">
-        <v>66.22</v>
-      </c>
-      <c r="G228" t="n">
         <v>64.54000000000001</v>
       </c>
     </row>
@@ -6614,18 +5936,15 @@
         <v>38.95</v>
       </c>
       <c r="C229" t="n">
-        <v>36.01</v>
+        <v>28.64</v>
       </c>
       <c r="D229" t="n">
-        <v>74.95999999999999</v>
+        <v>67.59</v>
       </c>
       <c r="E229" t="n">
-        <v>61.23</v>
+        <v>59.15</v>
       </c>
       <c r="F229" t="n">
-        <v>66.42</v>
-      </c>
-      <c r="G229" t="n">
         <v>64.56</v>
       </c>
     </row>
@@ -6639,18 +5958,15 @@
         <v>39.4</v>
       </c>
       <c r="C230" t="n">
-        <v>37.04</v>
+        <v>28.54</v>
       </c>
       <c r="D230" t="n">
-        <v>76.44</v>
+        <v>67.94</v>
       </c>
       <c r="E230" t="n">
-        <v>61.95</v>
+        <v>59.6</v>
       </c>
       <c r="F230" t="n">
-        <v>67.48</v>
-      </c>
-      <c r="G230" t="n">
         <v>64.69</v>
       </c>
     </row>
@@ -6664,18 +5980,15 @@
         <v>39.46</v>
       </c>
       <c r="C231" t="n">
-        <v>38.1</v>
+        <v>29.19</v>
       </c>
       <c r="D231" t="n">
-        <v>77.56</v>
+        <v>68.66</v>
       </c>
       <c r="E231" t="n">
-        <v>62.45</v>
+        <v>59.89</v>
       </c>
       <c r="F231" t="n">
-        <v>68.28</v>
-      </c>
-      <c r="G231" t="n">
         <v>64.79000000000001</v>
       </c>
     </row>
@@ -6689,18 +6002,15 @@
         <v>39.52</v>
       </c>
       <c r="C232" t="n">
-        <v>38.33</v>
+        <v>29.98</v>
       </c>
       <c r="D232" t="n">
-        <v>77.84</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="E232" t="n">
-        <v>62.85</v>
+        <v>60.33</v>
       </c>
       <c r="F232" t="n">
-        <v>69.26000000000001</v>
-      </c>
-      <c r="G232" t="n">
         <v>65.25</v>
       </c>
     </row>
@@ -6714,18 +6024,15 @@
         <v>39.67</v>
       </c>
       <c r="C233" t="n">
-        <v>38.04</v>
+        <v>30.87</v>
       </c>
       <c r="D233" t="n">
-        <v>77.72</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="E233" t="n">
-        <v>63.27</v>
+        <v>60.77</v>
       </c>
       <c r="F233" t="n">
-        <v>70.54000000000001</v>
-      </c>
-      <c r="G233" t="n">
         <v>65.23</v>
       </c>
     </row>
@@ -6739,18 +6046,15 @@
         <v>39.57</v>
       </c>
       <c r="C234" t="n">
-        <v>37.89</v>
+        <v>31.52</v>
       </c>
       <c r="D234" t="n">
-        <v>77.47</v>
+        <v>71.09</v>
       </c>
       <c r="E234" t="n">
-        <v>63.41</v>
+        <v>60.94</v>
       </c>
       <c r="F234" t="n">
-        <v>71.09</v>
-      </c>
-      <c r="G234" t="n">
         <v>65.14</v>
       </c>
     </row>
@@ -6764,18 +6068,15 @@
         <v>39.57</v>
       </c>
       <c r="C235" t="n">
-        <v>37.96</v>
+        <v>32.16</v>
       </c>
       <c r="D235" t="n">
-        <v>77.53</v>
+        <v>71.73</v>
       </c>
       <c r="E235" t="n">
-        <v>63.63</v>
+        <v>61.25</v>
       </c>
       <c r="F235" t="n">
-        <v>71.73</v>
-      </c>
-      <c r="G235" t="n">
         <v>65.59</v>
       </c>
     </row>
@@ -6789,18 +6090,15 @@
         <v>39.57</v>
       </c>
       <c r="C236" t="n">
-        <v>38.21</v>
+        <v>32.15</v>
       </c>
       <c r="D236" t="n">
-        <v>77.79000000000001</v>
+        <v>71.72</v>
       </c>
       <c r="E236" t="n">
-        <v>63.83</v>
+        <v>61.46</v>
       </c>
       <c r="F236" t="n">
-        <v>71.72</v>
-      </c>
-      <c r="G236" t="n">
         <v>65.95</v>
       </c>
     </row>
@@ -6814,18 +6112,15 @@
         <v>39.62</v>
       </c>
       <c r="C237" t="n">
-        <v>38.3</v>
+        <v>32.39</v>
       </c>
       <c r="D237" t="n">
-        <v>77.92</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="E237" t="n">
-        <v>64.02</v>
+        <v>61.7</v>
       </c>
       <c r="F237" t="n">
-        <v>72.01000000000001</v>
-      </c>
-      <c r="G237" t="n">
         <v>66.33</v>
       </c>
     </row>
@@ -6839,18 +6134,15 @@
         <v>39.83</v>
       </c>
       <c r="C238" t="n">
-        <v>38.63</v>
+        <v>32.22</v>
       </c>
       <c r="D238" t="n">
-        <v>78.45999999999999</v>
+        <v>72.06</v>
       </c>
       <c r="E238" t="n">
-        <v>64.39</v>
+        <v>61.99</v>
       </c>
       <c r="F238" t="n">
-        <v>72.06</v>
-      </c>
-      <c r="G238" t="n">
         <v>66.43000000000001</v>
       </c>
     </row>
@@ -6864,18 +6156,15 @@
         <v>40.1</v>
       </c>
       <c r="C239" t="n">
-        <v>38.59</v>
+        <v>31.94</v>
       </c>
       <c r="D239" t="n">
-        <v>78.69</v>
+        <v>72.05</v>
       </c>
       <c r="E239" t="n">
-        <v>64.72</v>
+        <v>62.32</v>
       </c>
       <c r="F239" t="n">
-        <v>72.05</v>
-      </c>
-      <c r="G239" t="n">
         <v>66.70999999999999</v>
       </c>
     </row>
@@ -6889,18 +6178,15 @@
         <v>40.4</v>
       </c>
       <c r="C240" t="n">
-        <v>38.56</v>
+        <v>32.04</v>
       </c>
       <c r="D240" t="n">
-        <v>78.95999999999999</v>
+        <v>72.44</v>
       </c>
       <c r="E240" t="n">
-        <v>65.11</v>
+        <v>62.8</v>
       </c>
       <c r="F240" t="n">
-        <v>72.44</v>
-      </c>
-      <c r="G240" t="n">
         <v>67.41</v>
       </c>
     </row>
@@ -6914,18 +6200,15 @@
         <v>40.23</v>
       </c>
       <c r="C241" t="n">
-        <v>38.79</v>
+        <v>32.24</v>
       </c>
       <c r="D241" t="n">
-        <v>79.03</v>
+        <v>72.48</v>
       </c>
       <c r="E241" t="n">
-        <v>65.28</v>
+        <v>63.05</v>
       </c>
       <c r="F241" t="n">
-        <v>72.48</v>
-      </c>
-      <c r="G241" t="n">
         <v>67.87</v>
       </c>
     </row>
@@ -6939,18 +6222,15 @@
         <v>40.77</v>
       </c>
       <c r="C242" t="n">
-        <v>38.54</v>
+        <v>31.63</v>
       </c>
       <c r="D242" t="n">
-        <v>79.31</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="E242" t="n">
-        <v>65.65000000000001</v>
+        <v>63.47</v>
       </c>
       <c r="F242" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="G242" t="n">
         <v>68.44</v>
       </c>
     </row>
@@ -6964,18 +6244,15 @@
         <v>42.2</v>
       </c>
       <c r="C243" t="n">
-        <v>37.53</v>
+        <v>30.53</v>
       </c>
       <c r="D243" t="n">
-        <v>79.73</v>
+        <v>72.73</v>
       </c>
       <c r="E243" t="n">
-        <v>66.31999999999999</v>
+        <v>64.13</v>
       </c>
       <c r="F243" t="n">
-        <v>72.73</v>
-      </c>
-      <c r="G243" t="n">
         <v>68.78</v>
       </c>
     </row>
@@ -6989,18 +6266,15 @@
         <v>42.93</v>
       </c>
       <c r="C244" t="n">
-        <v>37.22</v>
+        <v>30.13</v>
       </c>
       <c r="D244" t="n">
-        <v>80.14</v>
+        <v>73.06</v>
       </c>
       <c r="E244" t="n">
-        <v>66.7</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="F244" t="n">
-        <v>73.06</v>
-      </c>
-      <c r="G244" t="n">
         <v>69.06999999999999</v>
       </c>
     </row>
@@ -7014,18 +6288,15 @@
         <v>43.69</v>
       </c>
       <c r="C245" t="n">
-        <v>37.62</v>
+        <v>30.56</v>
       </c>
       <c r="D245" t="n">
-        <v>81.31999999999999</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="E245" t="n">
-        <v>67.59</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="F245" t="n">
-        <v>74.26000000000001</v>
-      </c>
-      <c r="G245" t="n">
         <v>69.11</v>
       </c>
       <c r="H245" t="inlineStr">
@@ -7044,18 +6315,15 @@
         <v>44.02</v>
       </c>
       <c r="C246" t="n">
-        <v>37.51</v>
+        <v>30.64</v>
       </c>
       <c r="D246" t="n">
-        <v>81.53</v>
+        <v>74.66</v>
       </c>
       <c r="E246" t="n">
-        <v>67.90000000000001</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="F246" t="n">
-        <v>74.66</v>
-      </c>
-      <c r="G246" t="n">
         <v>69.34</v>
       </c>
     </row>
@@ -7069,18 +6337,15 @@
         <v>44.16</v>
       </c>
       <c r="C247" t="n">
-        <v>37.35</v>
+        <v>30.65</v>
       </c>
       <c r="D247" t="n">
-        <v>81.51000000000001</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="E247" t="n">
-        <v>67.95999999999999</v>
+        <v>65.56</v>
       </c>
       <c r="F247" t="n">
-        <v>74.81999999999999</v>
-      </c>
-      <c r="G247" t="n">
         <v>69.5</v>
       </c>
     </row>
@@ -7094,18 +6359,15 @@
         <v>44.49</v>
       </c>
       <c r="C248" t="n">
-        <v>36.84</v>
+        <v>30.66</v>
       </c>
       <c r="D248" t="n">
-        <v>81.33</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="E248" t="n">
-        <v>68.11</v>
+        <v>65.78</v>
       </c>
       <c r="F248" t="n">
-        <v>75.15000000000001</v>
-      </c>
-      <c r="G248" t="n">
         <v>69.7</v>
       </c>
     </row>
@@ -7119,18 +6381,15 @@
         <v>46.05</v>
       </c>
       <c r="C249" t="n">
-        <v>34.92</v>
+        <v>29.25</v>
       </c>
       <c r="D249" t="n">
-        <v>80.97</v>
+        <v>75.3</v>
       </c>
       <c r="E249" t="n">
-        <v>68.56</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="F249" t="n">
-        <v>75.3</v>
-      </c>
-      <c r="G249" t="n">
         <v>70.45</v>
       </c>
     </row>
@@ -7144,18 +6403,15 @@
         <v>46.73</v>
       </c>
       <c r="C250" t="n">
-        <v>34.37</v>
+        <v>29.25</v>
       </c>
       <c r="D250" t="n">
-        <v>81.09999999999999</v>
+        <v>75.97</v>
       </c>
       <c r="E250" t="n">
-        <v>69.01000000000001</v>
+        <v>67</v>
       </c>
       <c r="F250" t="n">
-        <v>75.97</v>
-      </c>
-      <c r="G250" t="n">
         <v>71.04000000000001</v>
       </c>
     </row>
@@ -7169,18 +6425,15 @@
         <v>47.02</v>
       </c>
       <c r="C251" t="n">
-        <v>33.98</v>
+        <v>29.03</v>
       </c>
       <c r="D251" t="n">
-        <v>81</v>
+        <v>76.05</v>
       </c>
       <c r="E251" t="n">
-        <v>69.18000000000001</v>
+        <v>67.36</v>
       </c>
       <c r="F251" t="n">
-        <v>76.05</v>
-      </c>
-      <c r="G251" t="n">
         <v>71.86</v>
       </c>
     </row>
@@ -7194,18 +6447,15 @@
         <v>47.18</v>
       </c>
       <c r="C252" t="n">
-        <v>34.77</v>
+        <v>28.96</v>
       </c>
       <c r="D252" t="n">
-        <v>81.95</v>
+        <v>76.14</v>
       </c>
       <c r="E252" t="n">
-        <v>69.58</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="F252" t="n">
-        <v>76.14</v>
-      </c>
-      <c r="G252" t="n">
         <v>72.81999999999999</v>
       </c>
     </row>
@@ -7219,18 +6469,15 @@
         <v>47.41</v>
       </c>
       <c r="C253" t="n">
-        <v>34.88</v>
+        <v>29.11</v>
       </c>
       <c r="D253" t="n">
-        <v>82.29000000000001</v>
+        <v>76.52</v>
       </c>
       <c r="E253" t="n">
-        <v>69.87</v>
+        <v>68.06</v>
       </c>
       <c r="F253" t="n">
-        <v>76.52</v>
-      </c>
-      <c r="G253" t="n">
         <v>73.26000000000001</v>
       </c>
     </row>
@@ -7244,18 +6491,15 @@
         <v>47.97</v>
       </c>
       <c r="C254" t="n">
-        <v>34.25</v>
+        <v>29.02</v>
       </c>
       <c r="D254" t="n">
-        <v>82.22</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="E254" t="n">
-        <v>70.11</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F254" t="n">
-        <v>76.98999999999999</v>
-      </c>
-      <c r="G254" t="n">
         <v>73.7</v>
       </c>
     </row>
@@ -7269,18 +6513,15 @@
         <v>48.61</v>
       </c>
       <c r="C255" t="n">
-        <v>33.74</v>
+        <v>28.62</v>
       </c>
       <c r="D255" t="n">
-        <v>82.36</v>
+        <v>77.23</v>
       </c>
       <c r="E255" t="n">
-        <v>70.59</v>
+        <v>68.83</v>
       </c>
       <c r="F255" t="n">
-        <v>77.23</v>
-      </c>
-      <c r="G255" t="n">
         <v>73.58</v>
       </c>
     </row>
@@ -7294,18 +6535,15 @@
         <v>49.12</v>
       </c>
       <c r="C256" t="n">
-        <v>33.69</v>
+        <v>28.31</v>
       </c>
       <c r="D256" t="n">
-        <v>82.8</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="E256" t="n">
-        <v>70.94</v>
+        <v>69.03</v>
       </c>
       <c r="F256" t="n">
-        <v>77.43000000000001</v>
-      </c>
-      <c r="G256" t="n">
         <v>73.28</v>
       </c>
     </row>
@@ -7319,18 +6557,15 @@
         <v>49.28</v>
       </c>
       <c r="C257" t="n">
-        <v>34.05</v>
+        <v>28.66</v>
       </c>
       <c r="D257" t="n">
-        <v>83.33</v>
+        <v>77.95</v>
       </c>
       <c r="E257" t="n">
-        <v>71.18000000000001</v>
+        <v>69.13</v>
       </c>
       <c r="F257" t="n">
-        <v>77.95</v>
-      </c>
-      <c r="G257" t="n">
         <v>73.05</v>
       </c>
     </row>
@@ -7344,18 +6579,15 @@
         <v>49.31</v>
       </c>
       <c r="C258" t="n">
-        <v>34.45</v>
+        <v>29.18</v>
       </c>
       <c r="D258" t="n">
-        <v>83.76000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="E258" t="n">
-        <v>71.45</v>
+        <v>69.37</v>
       </c>
       <c r="F258" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="G258" t="n">
         <v>73.34</v>
       </c>
     </row>
@@ -7369,18 +6601,15 @@
         <v>49.69</v>
       </c>
       <c r="C259" t="n">
-        <v>34.09</v>
+        <v>29.32</v>
       </c>
       <c r="D259" t="n">
-        <v>83.78</v>
+        <v>79.01000000000001</v>
       </c>
       <c r="E259" t="n">
-        <v>71.77</v>
+        <v>69.7</v>
       </c>
       <c r="F259" t="n">
-        <v>79.01000000000001</v>
-      </c>
-      <c r="G259" t="n">
         <v>73.44</v>
       </c>
     </row>
@@ -7394,18 +6623,15 @@
         <v>50.79</v>
       </c>
       <c r="C260" t="n">
-        <v>32.96</v>
+        <v>28.33</v>
       </c>
       <c r="D260" t="n">
-        <v>83.75</v>
+        <v>79.12</v>
       </c>
       <c r="E260" t="n">
-        <v>72.15000000000001</v>
+        <v>70.11</v>
       </c>
       <c r="F260" t="n">
-        <v>79.12</v>
-      </c>
-      <c r="G260" t="n">
         <v>73.55</v>
       </c>
     </row>
@@ -7419,18 +6645,15 @@
         <v>52.8</v>
       </c>
       <c r="C261" t="n">
-        <v>30.81</v>
+        <v>27.05</v>
       </c>
       <c r="D261" t="n">
-        <v>83.61</v>
+        <v>79.86</v>
       </c>
       <c r="E261" t="n">
-        <v>72.73</v>
+        <v>70.73</v>
       </c>
       <c r="F261" t="n">
-        <v>79.86</v>
-      </c>
-      <c r="G261" t="n">
         <v>73.62</v>
       </c>
     </row>
@@ -7444,18 +6667,15 @@
         <v>53.29</v>
       </c>
       <c r="C262" t="n">
-        <v>30.32</v>
+        <v>27.03</v>
       </c>
       <c r="D262" t="n">
-        <v>83.61</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="E262" t="n">
-        <v>73</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="F262" t="n">
-        <v>80.31999999999999</v>
-      </c>
-      <c r="G262" t="n">
         <v>73.93000000000001</v>
       </c>
     </row>
@@ -7469,18 +6689,15 @@
         <v>53.49</v>
       </c>
       <c r="C263" t="n">
-        <v>30.25</v>
+        <v>26.77</v>
       </c>
       <c r="D263" t="n">
-        <v>83.73999999999999</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="E263" t="n">
-        <v>73.18000000000001</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="F263" t="n">
-        <v>80.26000000000001</v>
-      </c>
-      <c r="G263" t="n">
         <v>74.14</v>
       </c>
     </row>
@@ -7494,18 +6711,15 @@
         <v>53.82</v>
       </c>
       <c r="C264" t="n">
-        <v>31.05</v>
+        <v>26.45</v>
       </c>
       <c r="D264" t="n">
-        <v>84.87</v>
+        <v>80.27</v>
       </c>
       <c r="E264" t="n">
-        <v>73.48</v>
+        <v>71.36</v>
       </c>
       <c r="F264" t="n">
-        <v>80.27</v>
-      </c>
-      <c r="G264" t="n">
         <v>74.26000000000001</v>
       </c>
     </row>
@@ -7519,18 +6733,15 @@
         <v>54.29</v>
       </c>
       <c r="C265" t="n">
-        <v>31.14</v>
+        <v>25.86</v>
       </c>
       <c r="D265" t="n">
-        <v>85.43000000000001</v>
+        <v>80.15000000000001</v>
       </c>
       <c r="E265" t="n">
-        <v>73.62</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="F265" t="n">
-        <v>80.15000000000001</v>
-      </c>
-      <c r="G265" t="n">
         <v>74.64</v>
       </c>
     </row>
@@ -7544,18 +6755,15 @@
         <v>54.6</v>
       </c>
       <c r="C266" t="n">
-        <v>30.79</v>
+        <v>25.74</v>
       </c>
       <c r="D266" t="n">
-        <v>85.39</v>
+        <v>80.34</v>
       </c>
       <c r="E266" t="n">
-        <v>73.72</v>
+        <v>71.59</v>
       </c>
       <c r="F266" t="n">
-        <v>80.34</v>
-      </c>
-      <c r="G266" t="n">
         <v>74.76000000000001</v>
       </c>
     </row>
@@ -7569,18 +6777,15 @@
         <v>54.99</v>
       </c>
       <c r="C267" t="n">
-        <v>30.23</v>
+        <v>25.86</v>
       </c>
       <c r="D267" t="n">
-        <v>85.22</v>
+        <v>80.84</v>
       </c>
       <c r="E267" t="n">
-        <v>73.93000000000001</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="F267" t="n">
-        <v>80.84</v>
-      </c>
-      <c r="G267" t="n">
         <v>75.38</v>
       </c>
     </row>
@@ -7594,18 +6799,15 @@
         <v>55.52</v>
       </c>
       <c r="C268" t="n">
-        <v>29.83</v>
+        <v>25.94</v>
       </c>
       <c r="D268" t="n">
-        <v>85.34999999999999</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="E268" t="n">
-        <v>74.3</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="F268" t="n">
-        <v>81.45999999999999</v>
-      </c>
-      <c r="G268" t="n">
         <v>75.3</v>
       </c>
     </row>
@@ -7619,18 +6821,15 @@
         <v>55.59</v>
       </c>
       <c r="C269" t="n">
-        <v>29.6</v>
+        <v>25.76</v>
       </c>
       <c r="D269" t="n">
-        <v>85.2</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="E269" t="n">
-        <v>74.48999999999999</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="F269" t="n">
-        <v>81.34999999999999</v>
-      </c>
-      <c r="G269" t="n">
         <v>75.04000000000001</v>
       </c>
     </row>
@@ -7644,18 +6843,15 @@
         <v>55.95</v>
       </c>
       <c r="C270" t="n">
-        <v>29.09</v>
+        <v>25.23</v>
       </c>
       <c r="D270" t="n">
-        <v>85.04000000000001</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="E270" t="n">
-        <v>74.84999999999999</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="F270" t="n">
-        <v>81.18000000000001</v>
-      </c>
-      <c r="G270" t="n">
         <v>74.86</v>
       </c>
     </row>
@@ -7669,18 +6865,15 @@
         <v>56.81</v>
       </c>
       <c r="C271" t="n">
-        <v>28.02</v>
+        <v>24.6</v>
       </c>
       <c r="D271" t="n">
-        <v>84.83</v>
+        <v>81.41</v>
       </c>
       <c r="E271" t="n">
-        <v>75.14</v>
+        <v>73.12</v>
       </c>
       <c r="F271" t="n">
-        <v>81.41</v>
-      </c>
-      <c r="G271" t="n">
         <v>74.73999999999999</v>
       </c>
     </row>
@@ -7694,18 +6887,15 @@
         <v>57.42</v>
       </c>
       <c r="C272" t="n">
-        <v>27.16</v>
+        <v>24.65</v>
       </c>
       <c r="D272" t="n">
-        <v>84.58</v>
+        <v>82.06999999999999</v>
       </c>
       <c r="E272" t="n">
-        <v>75.48999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F272" t="n">
-        <v>82.06999999999999</v>
-      </c>
-      <c r="G272" t="n">
         <v>75.16</v>
       </c>
     </row>
@@ -7719,18 +6909,15 @@
         <v>57.74</v>
       </c>
       <c r="C273" t="n">
-        <v>26.65</v>
+        <v>24.4</v>
       </c>
       <c r="D273" t="n">
-        <v>84.39</v>
+        <v>82.14</v>
       </c>
       <c r="E273" t="n">
-        <v>75.62</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="F273" t="n">
-        <v>82.14</v>
-      </c>
-      <c r="G273" t="n">
         <v>75.37</v>
       </c>
     </row>
@@ -7744,18 +6931,15 @@
         <v>57.83</v>
       </c>
       <c r="C274" t="n">
-        <v>26.43</v>
+        <v>24.53</v>
       </c>
       <c r="D274" t="n">
-        <v>84.26000000000001</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="E274" t="n">
-        <v>75.66</v>
+        <v>74.09</v>
       </c>
       <c r="F274" t="n">
-        <v>82.34999999999999</v>
-      </c>
-      <c r="G274" t="n">
         <v>76.42</v>
       </c>
     </row>
@@ -7769,18 +6953,15 @@
         <v>57.94</v>
       </c>
       <c r="C275" t="n">
-        <v>26.23</v>
+        <v>24.77</v>
       </c>
       <c r="D275" t="n">
-        <v>84.18000000000001</v>
+        <v>82.72</v>
       </c>
       <c r="E275" t="n">
-        <v>75.72</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="F275" t="n">
-        <v>82.72</v>
-      </c>
-      <c r="G275" t="n">
         <v>76.45999999999999</v>
       </c>
       <c r="H275" t="inlineStr">
@@ -7799,18 +6980,15 @@
         <v>58</v>
       </c>
       <c r="C276" t="n">
-        <v>26.16</v>
+        <v>24.87</v>
       </c>
       <c r="D276" t="n">
-        <v>84.16</v>
+        <v>82.87</v>
       </c>
       <c r="E276" t="n">
-        <v>75.93000000000001</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="F276" t="n">
-        <v>82.87</v>
-      </c>
-      <c r="G276" t="n">
         <v>76.84</v>
       </c>
     </row>
@@ -7824,18 +7002,15 @@
         <v>58.18</v>
       </c>
       <c r="C277" t="n">
-        <v>25.54</v>
+        <v>25.05</v>
       </c>
       <c r="D277" t="n">
-        <v>83.70999999999999</v>
+        <v>83.22</v>
       </c>
       <c r="E277" t="n">
-        <v>76.01000000000001</v>
+        <v>74.75</v>
       </c>
       <c r="F277" t="n">
-        <v>83.22</v>
-      </c>
-      <c r="G277" t="n">
         <v>77.39</v>
       </c>
     </row>
@@ -7849,18 +7024,15 @@
         <v>58.52</v>
       </c>
       <c r="C278" t="n">
-        <v>25.07</v>
+        <v>24.67</v>
       </c>
       <c r="D278" t="n">
-        <v>83.59</v>
+        <v>83.19</v>
       </c>
       <c r="E278" t="n">
-        <v>76.25</v>
+        <v>75.12</v>
       </c>
       <c r="F278" t="n">
-        <v>83.19</v>
-      </c>
-      <c r="G278" t="n">
         <v>77.90000000000001</v>
       </c>
     </row>
@@ -7874,18 +7046,15 @@
         <v>58.88</v>
       </c>
       <c r="C279" t="n">
-        <v>24.55</v>
+        <v>24.29</v>
       </c>
       <c r="D279" t="n">
-        <v>83.42</v>
+        <v>83.17</v>
       </c>
       <c r="E279" t="n">
-        <v>76.34999999999999</v>
+        <v>75.31</v>
       </c>
       <c r="F279" t="n">
-        <v>83.17</v>
-      </c>
-      <c r="G279" t="n">
         <v>78.23</v>
       </c>
     </row>
@@ -7899,18 +7068,15 @@
         <v>59.62</v>
       </c>
       <c r="C280" t="n">
-        <v>23.65</v>
+        <v>23.38</v>
       </c>
       <c r="D280" t="n">
-        <v>83.27</v>
+        <v>83</v>
       </c>
       <c r="E280" t="n">
-        <v>76.54000000000001</v>
+        <v>75.53</v>
       </c>
       <c r="F280" t="n">
-        <v>83</v>
-      </c>
-      <c r="G280" t="n">
         <v>78.26000000000001</v>
       </c>
     </row>
@@ -7924,18 +7090,15 @@
         <v>59.93</v>
       </c>
       <c r="C281" t="n">
-        <v>22.98</v>
+        <v>22.97</v>
       </c>
       <c r="D281" t="n">
         <v>82.90000000000001</v>
       </c>
       <c r="E281" t="n">
-        <v>76.54000000000001</v>
+        <v>75.59</v>
       </c>
       <c r="F281" t="n">
-        <v>82.56</v>
-      </c>
-      <c r="G281" t="n">
         <v>78.17</v>
       </c>
     </row>
@@ -7955,12 +7118,9 @@
         <v>83.38</v>
       </c>
       <c r="E282" t="n">
-        <v>76.75</v>
+        <v>75.72</v>
       </c>
       <c r="F282" t="n">
-        <v>82.36</v>
-      </c>
-      <c r="G282" t="n">
         <v>78</v>
       </c>
     </row>
@@ -7974,18 +7134,15 @@
         <v>59.87</v>
       </c>
       <c r="C283" t="n">
-        <v>23.77</v>
+        <v>23.37</v>
       </c>
       <c r="D283" t="n">
-        <v>83.64</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="E283" t="n">
-        <v>76.8</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="F283" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="G283" t="n">
         <v>78.41</v>
       </c>
     </row>
@@ -7999,18 +7156,15 @@
         <v>59.82</v>
       </c>
       <c r="C284" t="n">
-        <v>23.97</v>
+        <v>23.41</v>
       </c>
       <c r="D284" t="n">
-        <v>83.8</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="E284" t="n">
-        <v>76.91</v>
+        <v>75.84</v>
       </c>
       <c r="F284" t="n">
-        <v>82.22</v>
-      </c>
-      <c r="G284" t="n">
         <v>78.44</v>
       </c>
     </row>
@@ -8024,18 +7178,15 @@
         <v>59.61</v>
       </c>
       <c r="C285" t="n">
-        <v>24.74</v>
+        <v>24.01</v>
       </c>
       <c r="D285" t="n">
-        <v>84.34999999999999</v>
+        <v>83.62</v>
       </c>
       <c r="E285" t="n">
-        <v>77.20999999999999</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="F285" t="n">
-        <v>82.89</v>
-      </c>
-      <c r="G285" t="n">
         <v>78.51000000000001</v>
       </c>
     </row>
@@ -8049,18 +7200,15 @@
         <v>59.43</v>
       </c>
       <c r="C286" t="n">
-        <v>24.88</v>
+        <v>24.17</v>
       </c>
       <c r="D286" t="n">
-        <v>84.31</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="E286" t="n">
-        <v>77.19</v>
+        <v>76.09</v>
       </c>
       <c r="F286" t="n">
-        <v>83.06</v>
-      </c>
-      <c r="G286" t="n">
         <v>78.79000000000001</v>
       </c>
     </row>
@@ -8074,18 +7222,15 @@
         <v>59.38</v>
       </c>
       <c r="C287" t="n">
-        <v>24.99</v>
+        <v>24.57</v>
       </c>
       <c r="D287" t="n">
-        <v>84.37</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="E287" t="n">
-        <v>77.3</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="F287" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="G287" t="n">
         <v>78.91</v>
       </c>
     </row>
@@ -8099,18 +7244,15 @@
         <v>59.5</v>
       </c>
       <c r="C288" t="n">
-        <v>24.86</v>
+        <v>24.47</v>
       </c>
       <c r="D288" t="n">
-        <v>84.36</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="E288" t="n">
-        <v>77.5</v>
+        <v>76.39</v>
       </c>
       <c r="F288" t="n">
-        <v>83.34</v>
-      </c>
-      <c r="G288" t="n">
         <v>78.79000000000001</v>
       </c>
     </row>
@@ -8124,18 +7266,15 @@
         <v>59.6</v>
       </c>
       <c r="C289" t="n">
-        <v>24.67</v>
+        <v>24.12</v>
       </c>
       <c r="D289" t="n">
-        <v>84.27</v>
+        <v>83.72</v>
       </c>
       <c r="E289" t="n">
-        <v>77.47</v>
+        <v>76.39</v>
       </c>
       <c r="F289" t="n">
-        <v>83.02</v>
-      </c>
-      <c r="G289" t="n">
         <v>78.87</v>
       </c>
     </row>
@@ -8149,18 +7288,15 @@
         <v>59.6</v>
       </c>
       <c r="C290" t="n">
-        <v>24.9</v>
+        <v>23.87</v>
       </c>
       <c r="D290" t="n">
-        <v>84.5</v>
+        <v>83.47</v>
       </c>
       <c r="E290" t="n">
-        <v>77.53</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="F290" t="n">
-        <v>82.56999999999999</v>
-      </c>
-      <c r="G290" t="n">
         <v>78.81999999999999</v>
       </c>
     </row>
@@ -8174,18 +7310,15 @@
         <v>59.59</v>
       </c>
       <c r="C291" t="n">
-        <v>25.35</v>
+        <v>24.13</v>
       </c>
       <c r="D291" t="n">
-        <v>84.94</v>
+        <v>83.72</v>
       </c>
       <c r="E291" t="n">
-        <v>77.81</v>
+        <v>76.55</v>
       </c>
       <c r="F291" t="n">
-        <v>82.03</v>
-      </c>
-      <c r="G291" t="n">
         <v>78.65000000000001</v>
       </c>
     </row>
@@ -8199,18 +7332,15 @@
         <v>59.46</v>
       </c>
       <c r="C292" t="n">
-        <v>25.8</v>
+        <v>24.48</v>
       </c>
       <c r="D292" t="n">
-        <v>85.26000000000001</v>
+        <v>83.94</v>
       </c>
       <c r="E292" t="n">
-        <v>78.03</v>
+        <v>76.72</v>
       </c>
       <c r="F292" t="n">
-        <v>81.91</v>
-      </c>
-      <c r="G292" t="n">
         <v>78.73</v>
       </c>
     </row>
@@ -8224,18 +7354,15 @@
         <v>59.33</v>
       </c>
       <c r="C293" t="n">
-        <v>25.78</v>
+        <v>24.47</v>
       </c>
       <c r="D293" t="n">
-        <v>85.11</v>
+        <v>83.8</v>
       </c>
       <c r="E293" t="n">
-        <v>78.13</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F293" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="G293" t="n">
         <v>78.94</v>
       </c>
     </row>
@@ -8249,18 +7376,15 @@
         <v>59.19</v>
       </c>
       <c r="C294" t="n">
-        <v>25.8</v>
+        <v>24.78</v>
       </c>
       <c r="D294" t="n">
-        <v>84.98999999999999</v>
+        <v>83.97</v>
       </c>
       <c r="E294" t="n">
-        <v>78.11</v>
+        <v>76.97</v>
       </c>
       <c r="F294" t="n">
-        <v>82.01000000000001</v>
-      </c>
-      <c r="G294" t="n">
         <v>79.28</v>
       </c>
     </row>
@@ -8274,18 +7398,15 @@
         <v>59.05</v>
       </c>
       <c r="C295" t="n">
-        <v>26.16</v>
+        <v>24.81</v>
       </c>
       <c r="D295" t="n">
-        <v>85.20999999999999</v>
+        <v>83.86</v>
       </c>
       <c r="E295" t="n">
-        <v>78.18000000000001</v>
+        <v>77.02</v>
       </c>
       <c r="F295" t="n">
-        <v>82</v>
-      </c>
-      <c r="G295" t="n">
         <v>79.42</v>
       </c>
     </row>
@@ -8299,18 +7420,15 @@
         <v>59.28</v>
       </c>
       <c r="C296" t="n">
-        <v>26.22</v>
+        <v>24.65</v>
       </c>
       <c r="D296" t="n">
-        <v>85.5</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="E296" t="n">
-        <v>78.27</v>
+        <v>77.03</v>
       </c>
       <c r="F296" t="n">
-        <v>81.61</v>
-      </c>
-      <c r="G296" t="n">
         <v>79.31</v>
       </c>
     </row>
@@ -8324,18 +7442,15 @@
         <v>59.36</v>
       </c>
       <c r="C297" t="n">
-        <v>26.59</v>
+        <v>24.77</v>
       </c>
       <c r="D297" t="n">
-        <v>85.95</v>
+        <v>84.13</v>
       </c>
       <c r="E297" t="n">
-        <v>78.39</v>
+        <v>77.23</v>
       </c>
       <c r="F297" t="n">
-        <v>81.37</v>
-      </c>
-      <c r="G297" t="n">
         <v>80.18000000000001</v>
       </c>
     </row>
@@ -8349,18 +7464,15 @@
         <v>59.32</v>
       </c>
       <c r="C298" t="n">
-        <v>26.47</v>
+        <v>25</v>
       </c>
       <c r="D298" t="n">
-        <v>85.78</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E298" t="n">
-        <v>78.34999999999999</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="F298" t="n">
-        <v>81.03</v>
-      </c>
-      <c r="G298" t="n">
         <v>80.48999999999999</v>
       </c>
     </row>
@@ -8374,18 +7486,15 @@
         <v>59.23</v>
       </c>
       <c r="C299" t="n">
-        <v>26.91</v>
+        <v>25.35</v>
       </c>
       <c r="D299" t="n">
-        <v>86.14</v>
+        <v>84.58</v>
       </c>
       <c r="E299" t="n">
-        <v>78.42</v>
+        <v>77.3</v>
       </c>
       <c r="F299" t="n">
-        <v>80.89</v>
-      </c>
-      <c r="G299" t="n">
         <v>80.58</v>
       </c>
     </row>
@@ -8399,18 +7508,15 @@
         <v>59.12</v>
       </c>
       <c r="C300" t="n">
-        <v>26.99</v>
+        <v>25.71</v>
       </c>
       <c r="D300" t="n">
-        <v>86.11</v>
+        <v>84.83</v>
       </c>
       <c r="E300" t="n">
-        <v>78.48999999999999</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="F300" t="n">
-        <v>81.15000000000001</v>
-      </c>
-      <c r="G300" t="n">
         <v>80.81999999999999</v>
       </c>
     </row>
@@ -8424,18 +7530,15 @@
         <v>58.92</v>
       </c>
       <c r="C301" t="n">
-        <v>27.29</v>
+        <v>26.13</v>
       </c>
       <c r="D301" t="n">
-        <v>86.20999999999999</v>
+        <v>85.05</v>
       </c>
       <c r="E301" t="n">
-        <v>78.59999999999999</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="F301" t="n">
-        <v>81.54000000000001</v>
-      </c>
-      <c r="G301" t="n">
         <v>80.66</v>
       </c>
     </row>
@@ -8455,12 +7558,9 @@
         <v>86.13</v>
       </c>
       <c r="E302" t="n">
-        <v>78.88</v>
+        <v>77.75</v>
       </c>
       <c r="F302" t="n">
-        <v>81.91</v>
-      </c>
-      <c r="G302" t="n">
         <v>80.40000000000001</v>
       </c>
     </row>
@@ -8480,12 +7580,9 @@
         <v>86.56</v>
       </c>
       <c r="E303" t="n">
-        <v>79.09</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="F303" t="n">
-        <v>82.19</v>
-      </c>
-      <c r="G303" t="n">
         <v>80.3</v>
       </c>
     </row>
@@ -8505,12 +7602,9 @@
         <v>86.53</v>
       </c>
       <c r="E304" t="n">
-        <v>79.14</v>
+        <v>77.95</v>
       </c>
       <c r="F304" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="G304" t="n">
         <v>80.23</v>
       </c>
     </row>
@@ -8530,12 +7624,9 @@
         <v>86.52</v>
       </c>
       <c r="E305" t="n">
-        <v>79.01000000000001</v>
+        <v>77.81</v>
       </c>
       <c r="F305" t="n">
-        <v>81.86</v>
-      </c>
-      <c r="G305" t="n">
         <v>79.98999999999999</v>
       </c>
     </row>
@@ -8555,12 +7646,9 @@
         <v>86.97</v>
       </c>
       <c r="E306" t="n">
-        <v>79.03</v>
+        <v>77.81</v>
       </c>
       <c r="F306" t="n">
-        <v>81.59</v>
-      </c>
-      <c r="G306" t="n">
         <v>79.72</v>
       </c>
       <c r="H306" t="inlineStr">
@@ -8585,12 +7673,9 @@
         <v>87.48999999999999</v>
       </c>
       <c r="E307" t="n">
-        <v>79.05</v>
+        <v>77.83</v>
       </c>
       <c r="F307" t="n">
-        <v>81.61</v>
-      </c>
-      <c r="G307" t="n">
         <v>79.51000000000001</v>
       </c>
     </row>
@@ -8610,12 +7695,9 @@
         <v>87.25</v>
       </c>
       <c r="E308" t="n">
-        <v>78.98999999999999</v>
+        <v>77.72</v>
       </c>
       <c r="F308" t="n">
-        <v>82.01000000000001</v>
-      </c>
-      <c r="G308" t="n">
         <v>79.08</v>
       </c>
     </row>
@@ -8635,12 +7717,9 @@
         <v>87.09</v>
       </c>
       <c r="E309" t="n">
-        <v>78.91</v>
+        <v>77.63</v>
       </c>
       <c r="F309" t="n">
-        <v>82.39</v>
-      </c>
-      <c r="G309" t="n">
         <v>78.81999999999999</v>
       </c>
     </row>
@@ -8660,12 +7739,9 @@
         <v>87.38</v>
       </c>
       <c r="E310" t="n">
-        <v>78.90000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="F310" t="n">
-        <v>82.26000000000001</v>
-      </c>
-      <c r="G310" t="n">
         <v>78.91</v>
       </c>
     </row>
@@ -8685,12 +7761,9 @@
         <v>88.23999999999999</v>
       </c>
       <c r="E311" t="n">
-        <v>78.94</v>
+        <v>77.81</v>
       </c>
       <c r="F311" t="n">
-        <v>82</v>
-      </c>
-      <c r="G311" t="n">
         <v>78.86</v>
       </c>
     </row>
@@ -8710,12 +7783,9 @@
         <v>87.88</v>
       </c>
       <c r="E312" t="n">
-        <v>78.84999999999999</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="F312" t="n">
-        <v>81.98999999999999</v>
-      </c>
-      <c r="G312" t="n">
         <v>78.73999999999999</v>
       </c>
     </row>
@@ -8735,12 +7805,9 @@
         <v>87.55</v>
       </c>
       <c r="E313" t="n">
-        <v>78.73999999999999</v>
+        <v>77.66</v>
       </c>
       <c r="F313" t="n">
-        <v>82.05</v>
-      </c>
-      <c r="G313" t="n">
         <v>78.75</v>
       </c>
     </row>
@@ -8760,12 +7827,9 @@
         <v>87.43000000000001</v>
       </c>
       <c r="E314" t="n">
-        <v>78.67</v>
+        <v>77.67</v>
       </c>
       <c r="F314" t="n">
-        <v>82.38</v>
-      </c>
-      <c r="G314" t="n">
         <v>78.92</v>
       </c>
     </row>
@@ -8785,12 +7849,9 @@
         <v>87.36</v>
       </c>
       <c r="E315" t="n">
-        <v>78.68000000000001</v>
+        <v>77.58</v>
       </c>
       <c r="F315" t="n">
-        <v>82.43000000000001</v>
-      </c>
-      <c r="G315" t="n">
         <v>78.76000000000001</v>
       </c>
     </row>
@@ -8810,12 +7871,9 @@
         <v>87.27</v>
       </c>
       <c r="E316" t="n">
-        <v>78.69</v>
+        <v>77.53</v>
       </c>
       <c r="F316" t="n">
-        <v>82.55</v>
-      </c>
-      <c r="G316" t="n">
         <v>78.5</v>
       </c>
     </row>
@@ -8835,12 +7893,9 @@
         <v>87.06999999999999</v>
       </c>
       <c r="E317" t="n">
-        <v>78.75</v>
+        <v>77.44</v>
       </c>
       <c r="F317" t="n">
-        <v>82.41</v>
-      </c>
-      <c r="G317" t="n">
         <v>78.19</v>
       </c>
     </row>
@@ -8860,12 +7915,9 @@
         <v>86.97</v>
       </c>
       <c r="E318" t="n">
-        <v>78.81999999999999</v>
+        <v>77.36</v>
       </c>
       <c r="F318" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="G318" t="n">
         <v>77.86</v>
       </c>
     </row>
@@ -8885,12 +7937,9 @@
         <v>87.26000000000001</v>
       </c>
       <c r="E319" t="n">
-        <v>78.92</v>
+        <v>77.34</v>
       </c>
       <c r="F319" t="n">
-        <v>81.93000000000001</v>
-      </c>
-      <c r="G319" t="n">
         <v>77.65000000000001</v>
       </c>
     </row>
@@ -8910,12 +7959,9 @@
         <v>87.56</v>
       </c>
       <c r="E320" t="n">
-        <v>79.08</v>
+        <v>77.41</v>
       </c>
       <c r="F320" t="n">
-        <v>81.97</v>
-      </c>
-      <c r="G320" t="n">
         <v>77.65000000000001</v>
       </c>
     </row>
@@ -8935,12 +7981,9 @@
         <v>87.59</v>
       </c>
       <c r="E321" t="n">
-        <v>79.09999999999999</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="F321" t="n">
-        <v>82.23999999999999</v>
-      </c>
-      <c r="G321" t="n">
         <v>77.94</v>
       </c>
     </row>
@@ -8960,12 +8003,9 @@
         <v>87.23999999999999</v>
       </c>
       <c r="E322" t="n">
-        <v>79.13</v>
+        <v>77.63</v>
       </c>
       <c r="F322" t="n">
-        <v>82.43000000000001</v>
-      </c>
-      <c r="G322" t="n">
         <v>79.16</v>
       </c>
     </row>
@@ -8985,12 +8025,9 @@
         <v>86.88</v>
       </c>
       <c r="E323" t="n">
-        <v>79.19</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="F323" t="n">
-        <v>83.01000000000001</v>
-      </c>
-      <c r="G323" t="n">
         <v>79.54000000000001</v>
       </c>
     </row>
@@ -9004,18 +8041,15 @@
         <v>57.28</v>
       </c>
       <c r="C324" t="n">
-        <v>29.58</v>
+        <v>29.31</v>
       </c>
       <c r="D324" t="n">
-        <v>86.86</v>
+        <v>86.59</v>
       </c>
       <c r="E324" t="n">
-        <v>79.11</v>
+        <v>77.63</v>
       </c>
       <c r="F324" t="n">
-        <v>83.13</v>
-      </c>
-      <c r="G324" t="n">
         <v>79.48</v>
       </c>
     </row>
@@ -9029,18 +8063,15 @@
         <v>57.13</v>
       </c>
       <c r="C325" t="n">
-        <v>29.82</v>
+        <v>29.38</v>
       </c>
       <c r="D325" t="n">
-        <v>86.95</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="E325" t="n">
-        <v>79.09</v>
+        <v>77.58</v>
       </c>
       <c r="F325" t="n">
-        <v>82.98</v>
-      </c>
-      <c r="G325" t="n">
         <v>79.40000000000001</v>
       </c>
     </row>
@@ -9054,18 +8085,15 @@
         <v>56.8</v>
       </c>
       <c r="C326" t="n">
-        <v>30.06</v>
+        <v>29.68</v>
       </c>
       <c r="D326" t="n">
-        <v>86.86</v>
+        <v>86.48</v>
       </c>
       <c r="E326" t="n">
-        <v>79.09</v>
+        <v>77.56</v>
       </c>
       <c r="F326" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="G326" t="n">
         <v>79.22</v>
       </c>
     </row>
@@ -9079,18 +8107,15 @@
         <v>56.49</v>
       </c>
       <c r="C327" t="n">
-        <v>30.29</v>
+        <v>30.13</v>
       </c>
       <c r="D327" t="n">
-        <v>86.78</v>
+        <v>86.62</v>
       </c>
       <c r="E327" t="n">
-        <v>79.23999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="F327" t="n">
-        <v>83.04000000000001</v>
-      </c>
-      <c r="G327" t="n">
         <v>79.08</v>
       </c>
     </row>
@@ -9104,18 +8129,15 @@
         <v>56.32</v>
       </c>
       <c r="C328" t="n">
-        <v>30.68</v>
+        <v>30.01</v>
       </c>
       <c r="D328" t="n">
-        <v>87</v>
+        <v>86.33</v>
       </c>
       <c r="E328" t="n">
-        <v>79.20999999999999</v>
+        <v>77.64</v>
       </c>
       <c r="F328" t="n">
-        <v>83.09</v>
-      </c>
-      <c r="G328" t="n">
         <v>79.13</v>
       </c>
     </row>
@@ -9129,18 +8151,15 @@
         <v>56.42</v>
       </c>
       <c r="C329" t="n">
-        <v>30.62</v>
+        <v>29.53</v>
       </c>
       <c r="D329" t="n">
-        <v>87.05</v>
+        <v>85.95</v>
       </c>
       <c r="E329" t="n">
-        <v>79.13</v>
+        <v>77.52</v>
       </c>
       <c r="F329" t="n">
-        <v>83.09</v>
-      </c>
-      <c r="G329" t="n">
         <v>79.02</v>
       </c>
     </row>
@@ -9154,18 +8173,15 @@
         <v>56.49</v>
       </c>
       <c r="C330" t="n">
-        <v>30.64</v>
+        <v>29.1</v>
       </c>
       <c r="D330" t="n">
-        <v>87.13</v>
+        <v>85.59</v>
       </c>
       <c r="E330" t="n">
-        <v>79.05</v>
+        <v>77.37</v>
       </c>
       <c r="F330" t="n">
-        <v>83.06</v>
-      </c>
-      <c r="G330" t="n">
         <v>78.73</v>
       </c>
     </row>
@@ -9179,18 +8195,15 @@
         <v>56.69</v>
       </c>
       <c r="C331" t="n">
-        <v>30.34</v>
+        <v>28.56</v>
       </c>
       <c r="D331" t="n">
-        <v>87.03</v>
+        <v>85.25</v>
       </c>
       <c r="E331" t="n">
-        <v>78.93000000000001</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="F331" t="n">
-        <v>82.91</v>
-      </c>
-      <c r="G331" t="n">
         <v>78.69</v>
       </c>
     </row>
@@ -9204,18 +8217,15 @@
         <v>56.47</v>
       </c>
       <c r="C332" t="n">
-        <v>30.31</v>
+        <v>28.51</v>
       </c>
       <c r="D332" t="n">
-        <v>86.77</v>
+        <v>84.98</v>
       </c>
       <c r="E332" t="n">
-        <v>78.75</v>
+        <v>77.09</v>
       </c>
       <c r="F332" t="n">
-        <v>83.02</v>
-      </c>
-      <c r="G332" t="n">
         <v>78.47</v>
       </c>
     </row>
@@ -9229,18 +8239,15 @@
         <v>56.1</v>
       </c>
       <c r="C333" t="n">
-        <v>30.65</v>
+        <v>29.03</v>
       </c>
       <c r="D333" t="n">
-        <v>86.75</v>
+        <v>85.12</v>
       </c>
       <c r="E333" t="n">
-        <v>78.59999999999999</v>
+        <v>76.94</v>
       </c>
       <c r="F333" t="n">
-        <v>82.98</v>
-      </c>
-      <c r="G333" t="n">
         <v>78.44</v>
       </c>
     </row>
@@ -9254,18 +8261,15 @@
         <v>55.72</v>
       </c>
       <c r="C334" t="n">
-        <v>30.87</v>
+        <v>29.71</v>
       </c>
       <c r="D334" t="n">
-        <v>86.59999999999999</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="E334" t="n">
-        <v>78.44</v>
+        <v>76.84</v>
       </c>
       <c r="F334" t="n">
-        <v>82.77</v>
-      </c>
-      <c r="G334" t="n">
         <v>78.56</v>
       </c>
     </row>
@@ -9279,18 +8283,15 @@
         <v>55.39</v>
       </c>
       <c r="C335" t="n">
-        <v>31.38</v>
+        <v>29.67</v>
       </c>
       <c r="D335" t="n">
-        <v>86.76000000000001</v>
+        <v>85.05</v>
       </c>
       <c r="E335" t="n">
-        <v>78.20999999999999</v>
+        <v>76.66</v>
       </c>
       <c r="F335" t="n">
-        <v>82.67</v>
-      </c>
-      <c r="G335" t="n">
         <v>79.02</v>
       </c>
     </row>
@@ -9304,18 +8305,15 @@
         <v>54.95</v>
       </c>
       <c r="C336" t="n">
-        <v>31.84</v>
+        <v>30.15</v>
       </c>
       <c r="D336" t="n">
-        <v>86.78</v>
+        <v>85.09</v>
       </c>
       <c r="E336" t="n">
-        <v>78.06999999999999</v>
+        <v>76.58</v>
       </c>
       <c r="F336" t="n">
-        <v>82.75</v>
-      </c>
-      <c r="G336" t="n">
         <v>79.36</v>
       </c>
     </row>
@@ -9329,18 +8327,15 @@
         <v>54.52</v>
       </c>
       <c r="C337" t="n">
-        <v>32.22</v>
+        <v>30.57</v>
       </c>
       <c r="D337" t="n">
-        <v>86.73</v>
+        <v>85.09</v>
       </c>
       <c r="E337" t="n">
-        <v>77.91</v>
+        <v>76.47</v>
       </c>
       <c r="F337" t="n">
-        <v>82.89</v>
-      </c>
-      <c r="G337" t="n">
         <v>79.52</v>
       </c>
       <c r="H337" t="inlineStr">
@@ -9359,18 +8354,15 @@
         <v>54.53</v>
       </c>
       <c r="C338" t="n">
-        <v>31.92</v>
+        <v>30.53</v>
       </c>
       <c r="D338" t="n">
-        <v>86.45</v>
+        <v>85.06</v>
       </c>
       <c r="E338" t="n">
-        <v>77.86</v>
+        <v>76.55</v>
       </c>
       <c r="F338" t="n">
-        <v>83.16</v>
-      </c>
-      <c r="G338" t="n">
         <v>79.92</v>
       </c>
     </row>
@@ -9384,18 +8376,15 @@
         <v>54.41</v>
       </c>
       <c r="C339" t="n">
-        <v>31.69</v>
+        <v>31.01</v>
       </c>
       <c r="D339" t="n">
-        <v>86.09999999999999</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="E339" t="n">
-        <v>77.91</v>
+        <v>76.67</v>
       </c>
       <c r="F339" t="n">
-        <v>83.56999999999999</v>
-      </c>
-      <c r="G339" t="n">
         <v>79.92</v>
       </c>
     </row>
@@ -9409,18 +8398,15 @@
         <v>54.22</v>
       </c>
       <c r="C340" t="n">
-        <v>31.74</v>
+        <v>31.26</v>
       </c>
       <c r="D340" t="n">
-        <v>85.95999999999999</v>
+        <v>85.47</v>
       </c>
       <c r="E340" t="n">
-        <v>77.84999999999999</v>
+        <v>76.63</v>
       </c>
       <c r="F340" t="n">
-        <v>83.67</v>
-      </c>
-      <c r="G340" t="n">
         <v>79.84999999999999</v>
       </c>
     </row>
@@ -9434,18 +8420,15 @@
         <v>54.02</v>
       </c>
       <c r="C341" t="n">
-        <v>32.19</v>
+        <v>31.12</v>
       </c>
       <c r="D341" t="n">
-        <v>86.20999999999999</v>
+        <v>85.14</v>
       </c>
       <c r="E341" t="n">
-        <v>77.75</v>
+        <v>76.44</v>
       </c>
       <c r="F341" t="n">
-        <v>83.70999999999999</v>
-      </c>
-      <c r="G341" t="n">
         <v>79.7</v>
       </c>
     </row>
@@ -9459,18 +8442,15 @@
         <v>54.28</v>
       </c>
       <c r="C342" t="n">
-        <v>31.96</v>
+        <v>30.7</v>
       </c>
       <c r="D342" t="n">
-        <v>86.23999999999999</v>
+        <v>84.98</v>
       </c>
       <c r="E342" t="n">
-        <v>77.69</v>
+        <v>76.36</v>
       </c>
       <c r="F342" t="n">
-        <v>83.68000000000001</v>
-      </c>
-      <c r="G342" t="n">
         <v>79.59</v>
       </c>
     </row>
@@ -9484,18 +8464,15 @@
         <v>53.92</v>
       </c>
       <c r="C343" t="n">
-        <v>32.48</v>
+        <v>30.91</v>
       </c>
       <c r="D343" t="n">
-        <v>86.40000000000001</v>
+        <v>84.83</v>
       </c>
       <c r="E343" t="n">
-        <v>77.7</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="F343" t="n">
-        <v>84.5</v>
-      </c>
-      <c r="G343" t="n">
         <v>79.39</v>
       </c>
     </row>
@@ -9509,18 +8486,15 @@
         <v>53.8</v>
       </c>
       <c r="C344" t="n">
-        <v>32.61</v>
+        <v>30.9</v>
       </c>
       <c r="D344" t="n">
-        <v>86.42</v>
+        <v>84.7</v>
       </c>
       <c r="E344" t="n">
-        <v>77.58</v>
+        <v>76.14</v>
       </c>
       <c r="F344" t="n">
-        <v>84.64</v>
-      </c>
-      <c r="G344" t="n">
         <v>79.20999999999999</v>
       </c>
     </row>
@@ -9534,18 +8508,15 @@
         <v>53.53</v>
       </c>
       <c r="C345" t="n">
-        <v>32.61</v>
+        <v>31.08</v>
       </c>
       <c r="D345" t="n">
-        <v>86.15000000000001</v>
+        <v>84.62</v>
       </c>
       <c r="E345" t="n">
-        <v>77.34999999999999</v>
+        <v>75.92</v>
       </c>
       <c r="F345" t="n">
-        <v>84.36</v>
-      </c>
-      <c r="G345" t="n">
         <v>78.98999999999999</v>
       </c>
     </row>
@@ -9559,18 +8530,15 @@
         <v>53.07</v>
       </c>
       <c r="C346" t="n">
-        <v>32.84</v>
+        <v>31.38</v>
       </c>
       <c r="D346" t="n">
-        <v>85.91</v>
+        <v>84.45</v>
       </c>
       <c r="E346" t="n">
-        <v>77.13</v>
+        <v>75.72</v>
       </c>
       <c r="F346" t="n">
-        <v>83.95</v>
-      </c>
-      <c r="G346" t="n">
         <v>78.84999999999999</v>
       </c>
     </row>
@@ -9584,18 +8552,15 @@
         <v>52.71</v>
       </c>
       <c r="C347" t="n">
-        <v>33.36</v>
+        <v>31.74</v>
       </c>
       <c r="D347" t="n">
-        <v>86.06999999999999</v>
+        <v>84.44</v>
       </c>
       <c r="E347" t="n">
-        <v>77.18000000000001</v>
+        <v>75.78</v>
       </c>
       <c r="F347" t="n">
-        <v>83.86</v>
-      </c>
-      <c r="G347" t="n">
         <v>79.11</v>
       </c>
     </row>
@@ -9609,18 +8574,15 @@
         <v>52.21</v>
       </c>
       <c r="C348" t="n">
-        <v>33.79</v>
+        <v>32.21</v>
       </c>
       <c r="D348" t="n">
-        <v>86</v>
+        <v>84.42</v>
       </c>
       <c r="E348" t="n">
-        <v>77.02</v>
+        <v>75.63</v>
       </c>
       <c r="F348" t="n">
-        <v>83.52</v>
-      </c>
-      <c r="G348" t="n">
         <v>79.02</v>
       </c>
     </row>
@@ -9634,18 +8596,15 @@
         <v>51.85</v>
       </c>
       <c r="C349" t="n">
-        <v>33.94</v>
+        <v>32.79</v>
       </c>
       <c r="D349" t="n">
-        <v>85.8</v>
+        <v>84.64</v>
       </c>
       <c r="E349" t="n">
-        <v>76.70999999999999</v>
+        <v>75.39</v>
       </c>
       <c r="F349" t="n">
-        <v>83.19</v>
-      </c>
-      <c r="G349" t="n">
         <v>79.23999999999999</v>
       </c>
     </row>
@@ -9659,18 +8618,15 @@
         <v>51.69</v>
       </c>
       <c r="C350" t="n">
-        <v>33.74</v>
+        <v>33.03</v>
       </c>
       <c r="D350" t="n">
-        <v>85.44</v>
+        <v>84.73</v>
       </c>
       <c r="E350" t="n">
-        <v>76.63</v>
+        <v>75.36</v>
       </c>
       <c r="F350" t="n">
-        <v>83.29000000000001</v>
-      </c>
-      <c r="G350" t="n">
         <v>79.06</v>
       </c>
     </row>
@@ -9684,18 +8640,15 @@
         <v>51.4</v>
       </c>
       <c r="C351" t="n">
-        <v>34.03</v>
+        <v>33.22</v>
       </c>
       <c r="D351" t="n">
-        <v>85.43000000000001</v>
+        <v>84.62</v>
       </c>
       <c r="E351" t="n">
-        <v>76.45999999999999</v>
+        <v>75.17</v>
       </c>
       <c r="F351" t="n">
-        <v>83.02</v>
-      </c>
-      <c r="G351" t="n">
         <v>79</v>
       </c>
     </row>
@@ -9715,12 +8668,9 @@
         <v>85.40000000000001</v>
       </c>
       <c r="E352" t="n">
-        <v>76.42</v>
+        <v>75.17</v>
       </c>
       <c r="F352" t="n">
-        <v>82.75</v>
-      </c>
-      <c r="G352" t="n">
         <v>78.89</v>
       </c>
     </row>
@@ -9740,12 +8690,9 @@
         <v>85.27</v>
       </c>
       <c r="E353" t="n">
-        <v>76.25</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="F353" t="n">
-        <v>82.56999999999999</v>
-      </c>
-      <c r="G353" t="n">
         <v>78.68000000000001</v>
       </c>
     </row>
@@ -9765,12 +8712,9 @@
         <v>85.56999999999999</v>
       </c>
       <c r="E354" t="n">
-        <v>76.20999999999999</v>
+        <v>75</v>
       </c>
       <c r="F354" t="n">
-        <v>82.69</v>
-      </c>
-      <c r="G354" t="n">
         <v>78.31999999999999</v>
       </c>
     </row>
@@ -9790,12 +8734,9 @@
         <v>86.16</v>
       </c>
       <c r="E355" t="n">
-        <v>76.18000000000001</v>
+        <v>74.94</v>
       </c>
       <c r="F355" t="n">
-        <v>82.7</v>
-      </c>
-      <c r="G355" t="n">
         <v>78.11</v>
       </c>
     </row>
@@ -9815,12 +8756,9 @@
         <v>85.58</v>
       </c>
       <c r="E356" t="n">
-        <v>75.89</v>
+        <v>74.70999999999999</v>
       </c>
       <c r="F356" t="n">
-        <v>82.86</v>
-      </c>
-      <c r="G356" t="n">
         <v>78.12</v>
       </c>
     </row>
@@ -9840,12 +8778,9 @@
         <v>85.36</v>
       </c>
       <c r="E357" t="n">
-        <v>75.72</v>
+        <v>74.45</v>
       </c>
       <c r="F357" t="n">
-        <v>82.81</v>
-      </c>
-      <c r="G357" t="n">
         <v>77.86</v>
       </c>
     </row>
@@ -9865,12 +8800,9 @@
         <v>85.37</v>
       </c>
       <c r="E358" t="n">
-        <v>75.63</v>
+        <v>74.23</v>
       </c>
       <c r="F358" t="n">
-        <v>82.56</v>
-      </c>
-      <c r="G358" t="n">
         <v>77.52</v>
       </c>
     </row>
@@ -9884,18 +8816,15 @@
         <v>49.97</v>
       </c>
       <c r="C359" t="n">
-        <v>35.48</v>
+        <v>35.42</v>
       </c>
       <c r="D359" t="n">
-        <v>85.44</v>
+        <v>85.38</v>
       </c>
       <c r="E359" t="n">
-        <v>75.75</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="F359" t="n">
-        <v>82.23</v>
-      </c>
-      <c r="G359" t="n">
         <v>77.19</v>
       </c>
     </row>
@@ -9915,12 +8844,9 @@
         <v>85.56</v>
       </c>
       <c r="E360" t="n">
-        <v>75.78</v>
+        <v>74.05</v>
       </c>
       <c r="F360" t="n">
-        <v>81.91</v>
-      </c>
-      <c r="G360" t="n">
         <v>76.81999999999999</v>
       </c>
     </row>
@@ -9940,12 +8866,9 @@
         <v>85.7</v>
       </c>
       <c r="E361" t="n">
-        <v>75.62</v>
+        <v>73.88</v>
       </c>
       <c r="F361" t="n">
-        <v>81.81</v>
-      </c>
-      <c r="G361" t="n">
         <v>76.56</v>
       </c>
     </row>
@@ -9965,12 +8888,9 @@
         <v>85.43000000000001</v>
       </c>
       <c r="E362" t="n">
-        <v>75.36</v>
+        <v>73.61</v>
       </c>
       <c r="F362" t="n">
-        <v>81.48</v>
-      </c>
-      <c r="G362" t="n">
         <v>76.29000000000001</v>
       </c>
     </row>
@@ -9990,12 +8910,9 @@
         <v>84.93000000000001</v>
       </c>
       <c r="E363" t="n">
-        <v>75.05</v>
+        <v>73.41</v>
       </c>
       <c r="F363" t="n">
-        <v>81.29000000000001</v>
-      </c>
-      <c r="G363" t="n">
         <v>76.44</v>
       </c>
     </row>
@@ -10015,12 +8932,9 @@
         <v>84.42</v>
       </c>
       <c r="E364" t="n">
-        <v>74.81999999999999</v>
+        <v>73.28</v>
       </c>
       <c r="F364" t="n">
-        <v>81.39</v>
-      </c>
-      <c r="G364" t="n">
         <v>76.73999999999999</v>
       </c>
     </row>
@@ -10034,18 +8948,15 @@
         <v>49.44</v>
       </c>
       <c r="C365" t="n">
-        <v>34.93</v>
+        <v>34.65</v>
       </c>
       <c r="D365" t="n">
-        <v>84.37</v>
+        <v>84.09</v>
       </c>
       <c r="E365" t="n">
-        <v>74.64</v>
+        <v>73.08</v>
       </c>
       <c r="F365" t="n">
-        <v>81.27</v>
-      </c>
-      <c r="G365" t="n">
         <v>76.54000000000001</v>
       </c>
     </row>
@@ -10059,19 +8970,16 @@
         <v>49.92</v>
       </c>
       <c r="C366" t="n">
-        <v>34.65</v>
+        <v>31.94</v>
       </c>
       <c r="D366" t="n">
-        <v>84.56999999999999</v>
+        <v>81.86</v>
       </c>
       <c r="E366" t="n">
-        <v>74.28</v>
+        <v>72.61</v>
       </c>
       <c r="F366" t="n">
-        <v>81.37</v>
-      </c>
-      <c r="G366" t="n">
-        <v>8.369999999999999</v>
+        <v>76.23999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -10086,7 +8994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6118"/>
+  <dimension ref="A1:D6119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95740,12 +94648,26 @@
         <v>46295</v>
       </c>
       <c r="B6118" t="n">
-        <v>8.368399999999999</v>
+        <v>76.2358</v>
       </c>
       <c r="C6118" t="n">
-        <v>1463.0745</v>
+        <v>13328.4868</v>
       </c>
       <c r="D6118" t="n">
+        <v>17483.2455</v>
+      </c>
+    </row>
+    <row r="6119">
+      <c r="A6119" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B6119" t="n">
+        <v>76.1215</v>
+      </c>
+      <c r="C6119" t="n">
+        <v>13308.5115</v>
+      </c>
+      <c r="D6119" t="n">
         <v>17483.2455</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/colombia_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/colombia_hydro_reservoirs.xlsx
@@ -152,7 +152,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Colombia reservoirs (national) - water year (Oct-Sep), data to 2026-10-01</a:t>
+              <a:t>Colombia reservoirs (national) - water year (Oct-Sep), data to 2026-10-07</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -813,7 +813,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Daily, from 2010-01-01 to 2026-10-01. Updated daily by .github/workflows/colombia_hydro_reservoirs.yml;</t>
+          <t>Daily, from 2010-01-01 to 2026-10-07. Updated daily by .github/workflows/colombia_hydro_reservoirs.yml;</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
         <v>81.15000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>76.12</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -940,6 +940,9 @@
       <c r="F3" t="n">
         <v>81.13</v>
       </c>
+      <c r="G3" t="n">
+        <v>76.18000000000001</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -962,6 +965,9 @@
       <c r="F4" t="n">
         <v>81.17</v>
       </c>
+      <c r="G4" t="n">
+        <v>76.26000000000001</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -984,6 +990,9 @@
       <c r="F5" t="n">
         <v>80.97</v>
       </c>
+      <c r="G5" t="n">
+        <v>76.22</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1006,6 +1015,9 @@
       <c r="F6" t="n">
         <v>81.03</v>
       </c>
+      <c r="G6" t="n">
+        <v>75.16</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1028,6 +1040,9 @@
       <c r="F7" t="n">
         <v>81.04000000000001</v>
       </c>
+      <c r="G7" t="n">
+        <v>74.95</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1050,6 +1065,9 @@
       <c r="F8" t="n">
         <v>80.95999999999999</v>
       </c>
+      <c r="G8" t="n">
+        <v>0.59</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8693,7 +8711,7 @@
         <v>75.04000000000001</v>
       </c>
       <c r="F353" t="n">
-        <v>78.68000000000001</v>
+        <v>78.7</v>
       </c>
     </row>
     <row r="354">
@@ -8712,10 +8730,10 @@
         <v>85.56999999999999</v>
       </c>
       <c r="E354" t="n">
-        <v>75</v>
+        <v>75.01000000000001</v>
       </c>
       <c r="F354" t="n">
-        <v>78.31999999999999</v>
+        <v>78.34999999999999</v>
       </c>
     </row>
     <row r="355">
@@ -8737,7 +8755,7 @@
         <v>74.94</v>
       </c>
       <c r="F355" t="n">
-        <v>78.11</v>
+        <v>78.14</v>
       </c>
     </row>
     <row r="356">
@@ -8759,7 +8777,7 @@
         <v>74.70999999999999</v>
       </c>
       <c r="F356" t="n">
-        <v>78.12</v>
+        <v>78.15000000000001</v>
       </c>
     </row>
     <row r="357">
@@ -8778,10 +8796,10 @@
         <v>85.36</v>
       </c>
       <c r="E357" t="n">
-        <v>74.45</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="F357" t="n">
-        <v>77.86</v>
+        <v>77.89</v>
       </c>
     </row>
     <row r="358">
@@ -8800,10 +8818,10 @@
         <v>85.37</v>
       </c>
       <c r="E358" t="n">
-        <v>74.23</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="F358" t="n">
-        <v>77.52</v>
+        <v>77.55</v>
       </c>
     </row>
     <row r="359">
@@ -8822,10 +8840,10 @@
         <v>85.38</v>
       </c>
       <c r="E359" t="n">
-        <v>74.09999999999999</v>
+        <v>74.11</v>
       </c>
       <c r="F359" t="n">
-        <v>77.19</v>
+        <v>77.20999999999999</v>
       </c>
     </row>
     <row r="360">
@@ -8844,10 +8862,10 @@
         <v>85.56</v>
       </c>
       <c r="E360" t="n">
-        <v>74.05</v>
+        <v>74.06</v>
       </c>
       <c r="F360" t="n">
-        <v>76.81999999999999</v>
+        <v>76.84</v>
       </c>
     </row>
     <row r="361">
@@ -8866,10 +8884,10 @@
         <v>85.7</v>
       </c>
       <c r="E361" t="n">
-        <v>73.88</v>
+        <v>73.89</v>
       </c>
       <c r="F361" t="n">
-        <v>76.56</v>
+        <v>76.58</v>
       </c>
     </row>
     <row r="362">
@@ -8888,10 +8906,10 @@
         <v>85.43000000000001</v>
       </c>
       <c r="E362" t="n">
-        <v>73.61</v>
+        <v>73.62</v>
       </c>
       <c r="F362" t="n">
-        <v>76.29000000000001</v>
+        <v>76.31999999999999</v>
       </c>
     </row>
     <row r="363">
@@ -8913,7 +8931,7 @@
         <v>73.41</v>
       </c>
       <c r="F363" t="n">
-        <v>76.44</v>
+        <v>76.45999999999999</v>
       </c>
     </row>
     <row r="364">
@@ -8935,7 +8953,7 @@
         <v>73.28</v>
       </c>
       <c r="F364" t="n">
-        <v>76.73999999999999</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="365">
@@ -8957,7 +8975,7 @@
         <v>73.08</v>
       </c>
       <c r="F365" t="n">
-        <v>76.54000000000001</v>
+        <v>76.56</v>
       </c>
     </row>
     <row r="366">
@@ -8976,10 +8994,10 @@
         <v>81.86</v>
       </c>
       <c r="E366" t="n">
-        <v>72.61</v>
+        <v>72.62</v>
       </c>
       <c r="F366" t="n">
-        <v>76.23999999999999</v>
+        <v>76.26000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -8994,7 +9012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6119"/>
+  <dimension ref="A1:D6125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -94466,13 +94484,13 @@
         <v>46282</v>
       </c>
       <c r="B6105" t="n">
-        <v>78.68170000000001</v>
+        <v>78.7032</v>
       </c>
       <c r="C6105" t="n">
-        <v>13756.1176</v>
+        <v>13755.4703</v>
       </c>
       <c r="D6105" t="n">
-        <v>17483.2455</v>
+        <v>17477.6503</v>
       </c>
     </row>
     <row r="6106">
@@ -94480,13 +94498,13 @@
         <v>46283</v>
       </c>
       <c r="B6106" t="n">
-        <v>78.32089999999999</v>
+        <v>78.3488</v>
       </c>
       <c r="C6106" t="n">
-        <v>13693.0344</v>
+        <v>13693.5259</v>
       </c>
       <c r="D6106" t="n">
-        <v>17483.2455</v>
+        <v>17477.6503</v>
       </c>
     </row>
     <row r="6107">
@@ -94494,13 +94512,13 @@
         <v>46284</v>
       </c>
       <c r="B6107" t="n">
-        <v>78.11320000000001</v>
+        <v>78.1382</v>
       </c>
       <c r="C6107" t="n">
         <v>13656.7213</v>
       </c>
       <c r="D6107" t="n">
-        <v>17483.2455</v>
+        <v>17477.6503</v>
       </c>
     </row>
     <row r="6108">
@@ -94508,13 +94526,13 @@
         <v>46285</v>
       </c>
       <c r="B6108" t="n">
-        <v>78.1216</v>
+        <v>78.1467</v>
       </c>
       <c r="C6108" t="n">
         <v>13658.1983</v>
       </c>
       <c r="D6108" t="n">
-        <v>17483.2455</v>
+        <v>17477.6503</v>
       </c>
     </row>
     <row r="6109">
@@ -94522,13 +94540,13 @@
         <v>46286</v>
       </c>
       <c r="B6109" t="n">
-        <v>77.8608</v>
+        <v>77.8858</v>
       </c>
       <c r="C6109" t="n">
         <v>13612.6016</v>
       </c>
       <c r="D6109" t="n">
-        <v>17483.2455</v>
+        <v>17477.6503</v>
       </c>
     </row>
     <row r="6110">
@@ -94536,13 +94554,13 @@
         <v>46287</v>
       </c>
       <c r="B6110" t="n">
-        <v>77.52200000000001</v>
+        <v>77.5484</v>
       </c>
       <c r="C6110" t="n">
-        <v>13553.3538</v>
+        <v>13553.6451</v>
       </c>
       <c r="D6110" t="n">
-        <v>17483.2455</v>
+        <v>17477.6503</v>
       </c>
     </row>
     <row r="6111">
@@ -94550,13 +94568,13 @@
         <v>46288</v>
       </c>
       <c r="B6111" t="n">
-        <v>77.18600000000001</v>
+        <v>77.2106</v>
       </c>
       <c r="C6111" t="n">
-        <v>13494.6195</v>
+        <v>13494.6006</v>
       </c>
       <c r="D6111" t="n">
-        <v>17483.2455</v>
+        <v>17477.6503</v>
       </c>
     </row>
     <row r="6112">
@@ -94564,13 +94582,13 @@
         <v>46289</v>
       </c>
       <c r="B6112" t="n">
-        <v>76.8163</v>
+        <v>76.8398</v>
       </c>
       <c r="C6112" t="n">
-        <v>13429.9804</v>
+        <v>13429.7915</v>
       </c>
       <c r="D6112" t="n">
-        <v>17483.2455</v>
+        <v>17477.6503</v>
       </c>
     </row>
     <row r="6113">
@@ -94578,13 +94596,13 @@
         <v>46290</v>
       </c>
       <c r="B6113" t="n">
-        <v>76.55589999999999</v>
+        <v>76.58150000000001</v>
       </c>
       <c r="C6113" t="n">
-        <v>13384.46</v>
+        <v>13384.6435</v>
       </c>
       <c r="D6113" t="n">
-        <v>17483.2455</v>
+        <v>17477.6503</v>
       </c>
     </row>
     <row r="6114">
@@ -94592,13 +94610,13 @@
         <v>46291</v>
       </c>
       <c r="B6114" t="n">
-        <v>76.29179999999999</v>
+        <v>76.3164</v>
       </c>
       <c r="C6114" t="n">
-        <v>13338.2869</v>
+        <v>13338.3114</v>
       </c>
       <c r="D6114" t="n">
-        <v>17483.2455</v>
+        <v>17477.6503</v>
       </c>
     </row>
     <row r="6115">
@@ -94606,13 +94624,13 @@
         <v>46292</v>
       </c>
       <c r="B6115" t="n">
-        <v>76.4366</v>
+        <v>76.4611</v>
       </c>
       <c r="C6115" t="n">
         <v>13363.6045</v>
       </c>
       <c r="D6115" t="n">
-        <v>17483.2455</v>
+        <v>17477.6503</v>
       </c>
     </row>
     <row r="6116">
@@ -94620,13 +94638,13 @@
         <v>46293</v>
       </c>
       <c r="B6116" t="n">
-        <v>76.73650000000001</v>
+        <v>76.76139999999999</v>
       </c>
       <c r="C6116" t="n">
-        <v>13416.0283</v>
+        <v>13416.0949</v>
       </c>
       <c r="D6116" t="n">
-        <v>17483.2455</v>
+        <v>17477.6503</v>
       </c>
     </row>
     <row r="6117">
@@ -94634,13 +94652,13 @@
         <v>46294</v>
       </c>
       <c r="B6117" t="n">
-        <v>76.5378</v>
+        <v>76.56270000000001</v>
       </c>
       <c r="C6117" t="n">
-        <v>13381.2922</v>
+        <v>13381.3588</v>
       </c>
       <c r="D6117" t="n">
-        <v>17483.2455</v>
+        <v>17477.6503</v>
       </c>
     </row>
     <row r="6118">
@@ -94648,13 +94666,13 @@
         <v>46295</v>
       </c>
       <c r="B6118" t="n">
-        <v>76.2358</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="C6118" t="n">
-        <v>13328.4868</v>
+        <v>13328.4535</v>
       </c>
       <c r="D6118" t="n">
-        <v>17483.2455</v>
+        <v>17477.6503</v>
       </c>
     </row>
     <row r="6119">
@@ -94662,13 +94680,97 @@
         <v>46296</v>
       </c>
       <c r="B6119" t="n">
-        <v>76.1215</v>
+        <v>76.1459</v>
       </c>
       <c r="C6119" t="n">
         <v>13308.5115</v>
       </c>
       <c r="D6119" t="n">
-        <v>17483.2455</v>
+        <v>17477.6503</v>
+      </c>
+    </row>
+    <row r="6120">
+      <c r="A6120" s="3" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B6120" t="n">
+        <v>76.1759</v>
+      </c>
+      <c r="C6120" t="n">
+        <v>13313.7645</v>
+      </c>
+      <c r="D6120" t="n">
+        <v>17477.6503</v>
+      </c>
+    </row>
+    <row r="6121">
+      <c r="A6121" s="3" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B6121" t="n">
+        <v>76.2561</v>
+      </c>
+      <c r="C6121" t="n">
+        <v>13318.5393</v>
+      </c>
+      <c r="D6121" t="n">
+        <v>17465.5381</v>
+      </c>
+    </row>
+    <row r="6122">
+      <c r="A6122" s="3" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B6122" t="n">
+        <v>76.2163</v>
+      </c>
+      <c r="C6122" t="n">
+        <v>13311.58</v>
+      </c>
+      <c r="D6122" t="n">
+        <v>17465.5381</v>
+      </c>
+    </row>
+    <row r="6123">
+      <c r="A6123" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B6123" t="n">
+        <v>75.1581</v>
+      </c>
+      <c r="C6123" t="n">
+        <v>13267.3078</v>
+      </c>
+      <c r="D6123" t="n">
+        <v>17652.5431</v>
+      </c>
+    </row>
+    <row r="6124">
+      <c r="A6124" s="3" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B6124" t="n">
+        <v>74.94670000000001</v>
+      </c>
+      <c r="C6124" t="n">
+        <v>13186.2614</v>
+      </c>
+      <c r="D6124" t="n">
+        <v>17594.1928</v>
+      </c>
+    </row>
+    <row r="6125">
+      <c r="A6125" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B6125" t="n">
+        <v>0.5884</v>
+      </c>
+      <c r="C6125" t="n">
+        <v>104.248</v>
+      </c>
+      <c r="D6125" t="n">
+        <v>17716.4887</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/colombia_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/colombia_hydro_reservoirs.xlsx
@@ -152,7 +152,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Colombia reservoirs (national) - water year (Oct-Sep), data to 2026-10-07</a:t>
+              <a:t>Colombia reservoirs (national) - water year (Oct-Sep), data to 2026-10-06</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -813,7 +813,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Daily, from 2010-01-01 to 2026-10-07. Updated daily by .github/workflows/colombia_hydro_reservoirs.yml;</t>
+          <t>Daily, from 2010-01-01 to 2026-10-06. Updated daily by .github/workflows/colombia_hydro_reservoirs.yml;</t>
         </is>
       </c>
     </row>
@@ -1065,9 +1065,6 @@
       <c r="F8" t="n">
         <v>80.95999999999999</v>
       </c>
-      <c r="G8" t="n">
-        <v>0.59</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9012,7 +9009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6125"/>
+  <dimension ref="A1:D6124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -94759,20 +94756,6 @@
         <v>17594.1928</v>
       </c>
     </row>
-    <row r="6125">
-      <c r="A6125" s="3" t="n">
-        <v>46302</v>
-      </c>
-      <c r="B6125" t="n">
-        <v>0.5884</v>
-      </c>
-      <c r="C6125" t="n">
-        <v>104.248</v>
-      </c>
-      <c r="D6125" t="n">
-        <v>17716.4887</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/colombia_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/colombia_hydro_reservoirs.xlsx
@@ -152,7 +152,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Colombia reservoirs (national) - water year (Oct-Sep), data to 2026-10-06</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Colombia reservoirs (national) - water year (Oct-Sep), data to 2026-10-26</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -264,7 +265,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -813,7 +814,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Daily, from 2010-01-01 to 2026-10-06. Updated daily by .github/workflows/colombia_hydro_reservoirs.yml;</t>
+          <t>Daily, from 2010-01-01 to 2026-10-26. Updated daily by .github/workflows/colombia_hydro_reservoirs.yml;</t>
         </is>
       </c>
     </row>
@@ -911,7 +912,7 @@
         <v>81.15000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>76.15000000000001</v>
+        <v>76.12</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -941,7 +942,7 @@
         <v>81.13</v>
       </c>
       <c r="G3" t="n">
-        <v>76.18000000000001</v>
+        <v>76.15000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -966,7 +967,7 @@
         <v>81.17</v>
       </c>
       <c r="G4" t="n">
-        <v>76.26000000000001</v>
+        <v>76.18000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -991,7 +992,7 @@
         <v>80.97</v>
       </c>
       <c r="G5" t="n">
-        <v>76.22</v>
+        <v>76.14</v>
       </c>
     </row>
     <row r="6">
@@ -1016,7 +1017,7 @@
         <v>81.03</v>
       </c>
       <c r="G6" t="n">
-        <v>75.16</v>
+        <v>75.08</v>
       </c>
     </row>
     <row r="7">
@@ -1041,7 +1042,7 @@
         <v>81.04000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>74.95</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1065,6 +1066,9 @@
       <c r="F8" t="n">
         <v>80.95999999999999</v>
       </c>
+      <c r="G8" t="n">
+        <v>74.81</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1087,6 +1091,9 @@
       <c r="F9" t="n">
         <v>81.14</v>
       </c>
+      <c r="G9" t="n">
+        <v>74.8</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1109,6 +1116,9 @@
       <c r="F10" t="n">
         <v>81.02</v>
       </c>
+      <c r="G10" t="n">
+        <v>74.87</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1131,6 +1141,9 @@
       <c r="F11" t="n">
         <v>81.26000000000001</v>
       </c>
+      <c r="G11" t="n">
+        <v>74.95</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1153,6 +1166,9 @@
       <c r="F12" t="n">
         <v>81.45999999999999</v>
       </c>
+      <c r="G12" t="n">
+        <v>75.08</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1175,6 +1191,9 @@
       <c r="F13" t="n">
         <v>82.28</v>
       </c>
+      <c r="G13" t="n">
+        <v>75.42</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1197,6 +1216,9 @@
       <c r="F14" t="n">
         <v>82.45999999999999</v>
       </c>
+      <c r="G14" t="n">
+        <v>75.68000000000001</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1219,6 +1241,9 @@
       <c r="F15" t="n">
         <v>82.37</v>
       </c>
+      <c r="G15" t="n">
+        <v>75.84999999999999</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1241,6 +1266,9 @@
       <c r="F16" t="n">
         <v>82.23999999999999</v>
       </c>
+      <c r="G16" t="n">
+        <v>75.89</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1263,6 +1291,9 @@
       <c r="F17" t="n">
         <v>82.34999999999999</v>
       </c>
+      <c r="G17" t="n">
+        <v>75.98</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1285,6 +1316,9 @@
       <c r="F18" t="n">
         <v>82.58</v>
       </c>
+      <c r="G18" t="n">
+        <v>75.98999999999999</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1307,6 +1341,9 @@
       <c r="F19" t="n">
         <v>82.91</v>
       </c>
+      <c r="G19" t="n">
+        <v>76.28</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1329,6 +1366,9 @@
       <c r="F20" t="n">
         <v>83.25</v>
       </c>
+      <c r="G20" t="n">
+        <v>76.17</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1351,6 +1391,9 @@
       <c r="F21" t="n">
         <v>83.36</v>
       </c>
+      <c r="G21" t="n">
+        <v>76.09999999999999</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1373,6 +1416,9 @@
       <c r="F22" t="n">
         <v>83.44</v>
       </c>
+      <c r="G22" t="n">
+        <v>76.38</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1395,6 +1441,9 @@
       <c r="F23" t="n">
         <v>83.48</v>
       </c>
+      <c r="G23" t="n">
+        <v>76.56</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1417,6 +1466,9 @@
       <c r="F24" t="n">
         <v>83.43000000000001</v>
       </c>
+      <c r="G24" t="n">
+        <v>76.51000000000001</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1439,6 +1491,9 @@
       <c r="F25" t="n">
         <v>83.51000000000001</v>
       </c>
+      <c r="G25" t="n">
+        <v>76.58</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1461,6 +1516,9 @@
       <c r="F26" t="n">
         <v>83.59999999999999</v>
       </c>
+      <c r="G26" t="n">
+        <v>76.7</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1483,6 +1541,9 @@
       <c r="F27" t="n">
         <v>83.8</v>
       </c>
+      <c r="G27" t="n">
+        <v>76.84</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8815,10 +8876,10 @@
         <v>85.37</v>
       </c>
       <c r="E358" t="n">
-        <v>74.23999999999999</v>
+        <v>74.23</v>
       </c>
       <c r="F358" t="n">
-        <v>77.55</v>
+        <v>77.52</v>
       </c>
     </row>
     <row r="359">
@@ -8837,10 +8898,10 @@
         <v>85.38</v>
       </c>
       <c r="E359" t="n">
-        <v>74.11</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="F359" t="n">
-        <v>77.20999999999999</v>
+        <v>77.19</v>
       </c>
     </row>
     <row r="360">
@@ -8859,10 +8920,10 @@
         <v>85.56</v>
       </c>
       <c r="E360" t="n">
-        <v>74.06</v>
+        <v>74.05</v>
       </c>
       <c r="F360" t="n">
-        <v>76.84</v>
+        <v>76.81999999999999</v>
       </c>
     </row>
     <row r="361">
@@ -8881,10 +8942,10 @@
         <v>85.7</v>
       </c>
       <c r="E361" t="n">
-        <v>73.89</v>
+        <v>73.88</v>
       </c>
       <c r="F361" t="n">
-        <v>76.58</v>
+        <v>76.56</v>
       </c>
     </row>
     <row r="362">
@@ -8903,10 +8964,10 @@
         <v>85.43000000000001</v>
       </c>
       <c r="E362" t="n">
-        <v>73.62</v>
+        <v>73.61</v>
       </c>
       <c r="F362" t="n">
-        <v>76.31999999999999</v>
+        <v>76.29000000000001</v>
       </c>
     </row>
     <row r="363">
@@ -8928,7 +8989,7 @@
         <v>73.41</v>
       </c>
       <c r="F363" t="n">
-        <v>76.45999999999999</v>
+        <v>76.44</v>
       </c>
     </row>
     <row r="364">
@@ -8950,7 +9011,7 @@
         <v>73.28</v>
       </c>
       <c r="F364" t="n">
-        <v>76.76000000000001</v>
+        <v>76.73999999999999</v>
       </c>
     </row>
     <row r="365">
@@ -8972,7 +9033,7 @@
         <v>73.08</v>
       </c>
       <c r="F365" t="n">
-        <v>76.56</v>
+        <v>76.54000000000001</v>
       </c>
     </row>
     <row r="366">
@@ -8991,10 +9052,10 @@
         <v>81.86</v>
       </c>
       <c r="E366" t="n">
-        <v>72.62</v>
+        <v>72.61</v>
       </c>
       <c r="F366" t="n">
-        <v>76.26000000000001</v>
+        <v>76.23999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -9009,7 +9070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6124"/>
+  <dimension ref="A1:D6144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -94551,13 +94612,13 @@
         <v>46287</v>
       </c>
       <c r="B6110" t="n">
-        <v>77.5484</v>
+        <v>77.5236</v>
       </c>
       <c r="C6110" t="n">
         <v>13553.6451</v>
       </c>
       <c r="D6110" t="n">
-        <v>17477.6503</v>
+        <v>17483.2455</v>
       </c>
     </row>
     <row r="6111">
@@ -94565,13 +94626,13 @@
         <v>46288</v>
       </c>
       <c r="B6111" t="n">
-        <v>77.2106</v>
+        <v>77.1859</v>
       </c>
       <c r="C6111" t="n">
         <v>13494.6006</v>
       </c>
       <c r="D6111" t="n">
-        <v>17477.6503</v>
+        <v>17483.2455</v>
       </c>
     </row>
     <row r="6112">
@@ -94579,13 +94640,13 @@
         <v>46289</v>
       </c>
       <c r="B6112" t="n">
-        <v>76.8398</v>
+        <v>76.8152</v>
       </c>
       <c r="C6112" t="n">
         <v>13429.7915</v>
       </c>
       <c r="D6112" t="n">
-        <v>17477.6503</v>
+        <v>17483.2455</v>
       </c>
     </row>
     <row r="6113">
@@ -94593,13 +94654,13 @@
         <v>46290</v>
       </c>
       <c r="B6113" t="n">
-        <v>76.58150000000001</v>
+        <v>76.557</v>
       </c>
       <c r="C6113" t="n">
         <v>13384.6435</v>
       </c>
       <c r="D6113" t="n">
-        <v>17477.6503</v>
+        <v>17483.2455</v>
       </c>
     </row>
     <row r="6114">
@@ -94607,13 +94668,13 @@
         <v>46291</v>
       </c>
       <c r="B6114" t="n">
-        <v>76.3164</v>
+        <v>76.292</v>
       </c>
       <c r="C6114" t="n">
         <v>13338.3114</v>
       </c>
       <c r="D6114" t="n">
-        <v>17477.6503</v>
+        <v>17483.2455</v>
       </c>
     </row>
     <row r="6115">
@@ -94621,13 +94682,13 @@
         <v>46292</v>
       </c>
       <c r="B6115" t="n">
-        <v>76.4611</v>
+        <v>76.4366</v>
       </c>
       <c r="C6115" t="n">
         <v>13363.6045</v>
       </c>
       <c r="D6115" t="n">
-        <v>17477.6503</v>
+        <v>17483.2455</v>
       </c>
     </row>
     <row r="6116">
@@ -94635,13 +94696,13 @@
         <v>46293</v>
       </c>
       <c r="B6116" t="n">
-        <v>76.76139999999999</v>
+        <v>76.73690000000001</v>
       </c>
       <c r="C6116" t="n">
         <v>13416.0949</v>
       </c>
       <c r="D6116" t="n">
-        <v>17477.6503</v>
+        <v>17483.2455</v>
       </c>
     </row>
     <row r="6117">
@@ -94649,13 +94710,13 @@
         <v>46294</v>
       </c>
       <c r="B6117" t="n">
-        <v>76.56270000000001</v>
+        <v>76.5382</v>
       </c>
       <c r="C6117" t="n">
         <v>13381.3588</v>
       </c>
       <c r="D6117" t="n">
-        <v>17477.6503</v>
+        <v>17483.2455</v>
       </c>
     </row>
     <row r="6118">
@@ -94663,13 +94724,13 @@
         <v>46295</v>
       </c>
       <c r="B6118" t="n">
-        <v>76.26000000000001</v>
+        <v>76.23560000000001</v>
       </c>
       <c r="C6118" t="n">
         <v>13328.4535</v>
       </c>
       <c r="D6118" t="n">
-        <v>17477.6503</v>
+        <v>17483.2455</v>
       </c>
     </row>
     <row r="6119">
@@ -94677,13 +94738,13 @@
         <v>46296</v>
       </c>
       <c r="B6119" t="n">
-        <v>76.1459</v>
+        <v>76.1215</v>
       </c>
       <c r="C6119" t="n">
         <v>13308.5115</v>
       </c>
       <c r="D6119" t="n">
-        <v>17477.6503</v>
+        <v>17483.2455</v>
       </c>
     </row>
     <row r="6120">
@@ -94691,13 +94752,13 @@
         <v>46297</v>
       </c>
       <c r="B6120" t="n">
-        <v>76.1759</v>
+        <v>76.1516</v>
       </c>
       <c r="C6120" t="n">
         <v>13313.7645</v>
       </c>
       <c r="D6120" t="n">
-        <v>17477.6503</v>
+        <v>17483.2455</v>
       </c>
     </row>
     <row r="6121">
@@ -94705,13 +94766,13 @@
         <v>46298</v>
       </c>
       <c r="B6121" t="n">
-        <v>76.2561</v>
+        <v>76.1789</v>
       </c>
       <c r="C6121" t="n">
         <v>13318.5393</v>
       </c>
       <c r="D6121" t="n">
-        <v>17465.5381</v>
+        <v>17483.2455</v>
       </c>
     </row>
     <row r="6122">
@@ -94719,13 +94780,13 @@
         <v>46299</v>
       </c>
       <c r="B6122" t="n">
-        <v>76.2163</v>
+        <v>76.1391</v>
       </c>
       <c r="C6122" t="n">
         <v>13311.58</v>
       </c>
       <c r="D6122" t="n">
-        <v>17465.5381</v>
+        <v>17483.2455</v>
       </c>
     </row>
     <row r="6123">
@@ -94733,13 +94794,13 @@
         <v>46300</v>
       </c>
       <c r="B6123" t="n">
-        <v>75.1581</v>
+        <v>75.0827</v>
       </c>
       <c r="C6123" t="n">
         <v>13267.3078</v>
       </c>
       <c r="D6123" t="n">
-        <v>17652.5431</v>
+        <v>17670.2505</v>
       </c>
     </row>
     <row r="6124">
@@ -94747,13 +94808,293 @@
         <v>46301</v>
       </c>
       <c r="B6124" t="n">
-        <v>74.94670000000001</v>
+        <v>74.89830000000001</v>
       </c>
       <c r="C6124" t="n">
-        <v>13186.2614</v>
+        <v>13234.7201</v>
       </c>
       <c r="D6124" t="n">
-        <v>17594.1928</v>
+        <v>17670.2505</v>
+      </c>
+    </row>
+    <row r="6125">
+      <c r="A6125" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B6125" t="n">
+        <v>74.8109</v>
+      </c>
+      <c r="C6125" t="n">
+        <v>13215.0928</v>
+      </c>
+      <c r="D6125" t="n">
+        <v>17664.6553</v>
+      </c>
+    </row>
+    <row r="6126">
+      <c r="A6126" s="3" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B6126" t="n">
+        <v>74.7961</v>
+      </c>
+      <c r="C6126" t="n">
+        <v>13212.4764</v>
+      </c>
+      <c r="D6126" t="n">
+        <v>17664.6553</v>
+      </c>
+    </row>
+    <row r="6127">
+      <c r="A6127" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B6127" t="n">
+        <v>74.8715</v>
+      </c>
+      <c r="C6127" t="n">
+        <v>13225.7963</v>
+      </c>
+      <c r="D6127" t="n">
+        <v>17664.6553</v>
+      </c>
+    </row>
+    <row r="6128">
+      <c r="A6128" s="3" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B6128" t="n">
+        <v>74.9494</v>
+      </c>
+      <c r="C6128" t="n">
+        <v>13239.5584</v>
+      </c>
+      <c r="D6128" t="n">
+        <v>17664.6553</v>
+      </c>
+    </row>
+    <row r="6129">
+      <c r="A6129" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B6129" t="n">
+        <v>75.0829</v>
+      </c>
+      <c r="C6129" t="n">
+        <v>13263.1427</v>
+      </c>
+      <c r="D6129" t="n">
+        <v>17664.6553</v>
+      </c>
+    </row>
+    <row r="6130">
+      <c r="A6130" s="3" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B6130" t="n">
+        <v>75.4238</v>
+      </c>
+      <c r="C6130" t="n">
+        <v>13323.3631</v>
+      </c>
+      <c r="D6130" t="n">
+        <v>17664.6553</v>
+      </c>
+    </row>
+    <row r="6131">
+      <c r="A6131" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B6131" t="n">
+        <v>75.68219999999999</v>
+      </c>
+      <c r="C6131" t="n">
+        <v>13369.0023</v>
+      </c>
+      <c r="D6131" t="n">
+        <v>17664.6553</v>
+      </c>
+    </row>
+    <row r="6132">
+      <c r="A6132" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B6132" t="n">
+        <v>75.8519</v>
+      </c>
+      <c r="C6132" t="n">
+        <v>13398.9721</v>
+      </c>
+      <c r="D6132" t="n">
+        <v>17664.6553</v>
+      </c>
+    </row>
+    <row r="6133">
+      <c r="A6133" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B6133" t="n">
+        <v>75.8901</v>
+      </c>
+      <c r="C6133" t="n">
+        <v>13405.7317</v>
+      </c>
+      <c r="D6133" t="n">
+        <v>17664.6553</v>
+      </c>
+    </row>
+    <row r="6134">
+      <c r="A6134" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B6134" t="n">
+        <v>75.9804</v>
+      </c>
+      <c r="C6134" t="n">
+        <v>13421.6711</v>
+      </c>
+      <c r="D6134" t="n">
+        <v>17664.6553</v>
+      </c>
+    </row>
+    <row r="6135">
+      <c r="A6135" s="3" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B6135" t="n">
+        <v>75.9927</v>
+      </c>
+      <c r="C6135" t="n">
+        <v>13423.8537</v>
+      </c>
+      <c r="D6135" t="n">
+        <v>17664.6553</v>
+      </c>
+    </row>
+    <row r="6136">
+      <c r="A6136" s="3" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B6136" t="n">
+        <v>76.2773</v>
+      </c>
+      <c r="C6136" t="n">
+        <v>13474.1283</v>
+      </c>
+      <c r="D6136" t="n">
+        <v>17664.6553</v>
+      </c>
+    </row>
+    <row r="6137">
+      <c r="A6137" s="3" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B6137" t="n">
+        <v>76.16840000000001</v>
+      </c>
+      <c r="C6137" t="n">
+        <v>13454.8933</v>
+      </c>
+      <c r="D6137" t="n">
+        <v>17664.6553</v>
+      </c>
+    </row>
+    <row r="6138">
+      <c r="A6138" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B6138" t="n">
+        <v>76.1035</v>
+      </c>
+      <c r="C6138" t="n">
+        <v>13443.4208</v>
+      </c>
+      <c r="D6138" t="n">
+        <v>17664.6553</v>
+      </c>
+    </row>
+    <row r="6139">
+      <c r="A6139" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B6139" t="n">
+        <v>76.3817</v>
+      </c>
+      <c r="C6139" t="n">
+        <v>13492.5581</v>
+      </c>
+      <c r="D6139" t="n">
+        <v>17664.6553</v>
+      </c>
+    </row>
+    <row r="6140">
+      <c r="A6140" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B6140" t="n">
+        <v>76.56</v>
+      </c>
+      <c r="C6140" t="n">
+        <v>13524.0629</v>
+      </c>
+      <c r="D6140" t="n">
+        <v>17664.6553</v>
+      </c>
+    </row>
+    <row r="6141">
+      <c r="A6141" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B6141" t="n">
+        <v>76.51439999999999</v>
+      </c>
+      <c r="C6141" t="n">
+        <v>13516.0081</v>
+      </c>
+      <c r="D6141" t="n">
+        <v>17664.6553</v>
+      </c>
+    </row>
+    <row r="6142">
+      <c r="A6142" s="3" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B6142" t="n">
+        <v>76.5753</v>
+      </c>
+      <c r="C6142" t="n">
+        <v>13526.759</v>
+      </c>
+      <c r="D6142" t="n">
+        <v>17664.6553</v>
+      </c>
+    </row>
+    <row r="6143">
+      <c r="A6143" s="3" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B6143" t="n">
+        <v>76.6957</v>
+      </c>
+      <c r="C6143" t="n">
+        <v>13548.0238</v>
+      </c>
+      <c r="D6143" t="n">
+        <v>17664.6553</v>
+      </c>
+    </row>
+    <row r="6144">
+      <c r="A6144" s="3" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B6144" t="n">
+        <v>76.83929999999999</v>
+      </c>
+      <c r="C6144" t="n">
+        <v>13573.4022</v>
+      </c>
+      <c r="D6144" t="n">
+        <v>17664.6553</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/colombia_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/colombia_hydro_reservoirs.xlsx
@@ -153,7 +153,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Colombia reservoirs (national) - water year (Oct-Sep), data to 2026-10-26</a:t>
+              <a:t>Colombia reservoirs (national) - water year (Oct-Sep), data to 2026-10-27</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -814,7 +814,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Daily, from 2010-01-01 to 2026-10-26. Updated daily by .github/workflows/colombia_hydro_reservoirs.yml;</t>
+          <t>Daily, from 2010-01-01 to 2026-10-27. Updated daily by .github/workflows/colombia_hydro_reservoirs.yml;</t>
         </is>
       </c>
     </row>
@@ -1566,6 +1566,9 @@
       <c r="F28" t="n">
         <v>84.12</v>
       </c>
+      <c r="G28" t="n">
+        <v>77.02</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9070,7 +9073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6144"/>
+  <dimension ref="A1:D6145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95097,6 +95100,20 @@
         <v>17664.6553</v>
       </c>
     </row>
+    <row r="6145">
+      <c r="A6145" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B6145" t="n">
+        <v>77.0153</v>
+      </c>
+      <c r="C6145" t="n">
+        <v>13604.4939</v>
+      </c>
+      <c r="D6145" t="n">
+        <v>17664.6553</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/colombia_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/colombia_hydro_reservoirs.xlsx
@@ -153,7 +153,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Colombia reservoirs (national) - water year (Oct-Sep), data to 2026-10-27</a:t>
+              <a:t>Colombia reservoirs (national) - water year (Oct-Sep), data to 2026-10-28</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -814,7 +814,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Daily, from 2010-01-01 to 2026-10-27. Updated daily by .github/workflows/colombia_hydro_reservoirs.yml;</t>
+          <t>Daily, from 2010-01-01 to 2026-10-28. Updated daily by .github/workflows/colombia_hydro_reservoirs.yml;</t>
         </is>
       </c>
     </row>
@@ -1591,6 +1591,9 @@
       <c r="F29" t="n">
         <v>83.94</v>
       </c>
+      <c r="G29" t="n">
+        <v>77.06</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9073,7 +9076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6145"/>
+  <dimension ref="A1:D6146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95114,6 +95117,20 @@
         <v>17664.6553</v>
       </c>
     </row>
+    <row r="6146">
+      <c r="A6146" s="3" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B6146" t="n">
+        <v>77.0568</v>
+      </c>
+      <c r="C6146" t="n">
+        <v>13611.8225</v>
+      </c>
+      <c r="D6146" t="n">
+        <v>17664.6553</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/colombia_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/colombia_hydro_reservoirs.xlsx
@@ -153,7 +153,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Colombia reservoirs (national) - water year (Oct-Sep), data to 2026-10-28</a:t>
+              <a:t>Colombia reservoirs (national) - water year (Oct-Sep), data to 2026-10-29</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -814,7 +814,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Daily, from 2010-01-01 to 2026-10-28. Updated daily by .github/workflows/colombia_hydro_reservoirs.yml;</t>
+          <t>Daily, from 2010-01-01 to 2026-10-29. Updated daily by .github/workflows/colombia_hydro_reservoirs.yml;</t>
         </is>
       </c>
     </row>
@@ -1616,6 +1616,9 @@
       <c r="F30" t="n">
         <v>83.87</v>
       </c>
+      <c r="G30" t="n">
+        <v>77.12</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9076,7 +9079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6146"/>
+  <dimension ref="A1:D6147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95122,12 +95125,26 @@
         <v>46323</v>
       </c>
       <c r="B6146" t="n">
-        <v>77.0568</v>
+        <v>77.0616</v>
       </c>
       <c r="C6146" t="n">
-        <v>13611.8225</v>
+        <v>13612.6619</v>
       </c>
       <c r="D6146" t="n">
+        <v>17664.6553</v>
+      </c>
+    </row>
+    <row r="6147">
+      <c r="A6147" s="3" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B6147" t="n">
+        <v>77.1155</v>
+      </c>
+      <c r="C6147" t="n">
+        <v>13622.1891</v>
+      </c>
+      <c r="D6147" t="n">
         <v>17664.6553</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/colombia_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/colombia_hydro_reservoirs.xlsx
@@ -153,7 +153,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Colombia reservoirs (national) - water year (Oct-Sep), data to 2026-10-29</a:t>
+              <a:t>Colombia reservoirs (national) - water year (Oct-Sep), data to 2026-10-30</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -814,7 +814,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Daily, from 2010-01-01 to 2026-10-29. Updated daily by .github/workflows/colombia_hydro_reservoirs.yml;</t>
+          <t>Daily, from 2010-01-01 to 2026-10-30. Updated daily by .github/workflows/colombia_hydro_reservoirs.yml;</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1641,9 @@
       <c r="F31" t="n">
         <v>83.73999999999999</v>
       </c>
+      <c r="G31" t="n">
+        <v>77.09</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9079,7 +9082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6147"/>
+  <dimension ref="A1:D6148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95148,6 +95151,20 @@
         <v>17664.6553</v>
       </c>
     </row>
+    <row r="6148">
+      <c r="A6148" s="3" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B6148" t="n">
+        <v>77.0903</v>
+      </c>
+      <c r="C6148" t="n">
+        <v>13617.7296</v>
+      </c>
+      <c r="D6148" t="n">
+        <v>17664.6553</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
